--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="366">
   <si>
     <t xml:space="preserve">견          적          서</t>
   </si>
@@ -597,7 +597,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">일금 칠천오백일십육만팔백원정</t>
+    <t xml:space="preserve">일금 칠천오백칠십사만구천삼백원정</t>
   </si>
   <si>
     <t xml:space="preserve">No</t>
@@ -7630,7 +7630,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) × 3.5%</t>
+      <t xml:space="preserve">) × 8.0%</t>
     </r>
   </si>
   <si>
@@ -8357,75 +8357,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노무비 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경비 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일반관리비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) × 12.5%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
@@ -8648,75 +8579,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노무비 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경비 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일반관리비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) × 3.0%</t>
     </r>
   </si>
   <si>
@@ -12832,7 +12694,7 @@
       <c r="F16" s="12"/>
       <c r="G16" s="13" t="n">
         <f aca="false">원가계산서!E18</f>
-        <v>75160800</v>
+        <v>75749300</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
@@ -12878,7 +12740,7 @@
       </c>
       <c r="H19" s="18" t="n">
         <f aca="false">도비!$G$33</f>
-        <v>24213000</v>
+        <v>25206000</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>41</v>
@@ -12902,7 +12764,7 @@
       </c>
       <c r="H20" s="18" t="n">
         <f aca="false">용접!$G$31</f>
-        <v>25653000</v>
+        <v>24747000</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>45</v>
@@ -12926,7 +12788,7 @@
       </c>
       <c r="H21" s="18" t="n">
         <f aca="false">베이스!$G$34</f>
-        <v>18462000</v>
+        <v>18910000</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>49</v>
@@ -12944,7 +12806,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="19" t="n">
         <f aca="false">SUM(H19:H21)</f>
-        <v>68328000</v>
+        <v>68863000</v>
       </c>
       <c r="I22" s="20"/>
     </row>
@@ -12960,7 +12822,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="19" t="n">
         <f aca="false">H22*0.1</f>
-        <v>6832800</v>
+        <v>6886300</v>
       </c>
       <c r="I23" s="20"/>
     </row>
@@ -12976,7 +12838,7 @@
       <c r="G24" s="21"/>
       <c r="H24" s="22" t="n">
         <f aca="false">H22+H23</f>
-        <v>75160800</v>
+        <v>75749300</v>
       </c>
       <c r="I24" s="7"/>
     </row>
@@ -13199,7 +13061,7 @@
       </c>
       <c r="F6" s="30" t="n">
         <f aca="false">E6/$E$16</f>
-        <v>0.19924042852125</v>
+        <v>0.197692519930877</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13224,7 +13086,7 @@
       </c>
       <c r="F7" s="30" t="n">
         <f aca="false">E7/$E$16</f>
-        <v>0.312756117550638</v>
+        <v>0.310326300045017</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13249,7 +13111,7 @@
       </c>
       <c r="F8" s="30" t="n">
         <f aca="false">E8/$E$16</f>
-        <v>0.360165671467041</v>
+        <v>0.357367526828631</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13274,7 +13136,7 @@
       </c>
       <c r="F9" s="30" t="n">
         <f aca="false">E9/$E$16</f>
-        <v>0.0111341177848027</v>
+        <v>0.0110476162816026</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13299,7 +13161,7 @@
       </c>
       <c r="F10" s="30" t="n">
         <f aca="false">E10/$E$16</f>
-        <v>0.00359669535183234</v>
+        <v>0.00356875245051769</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13324,7 +13186,7 @@
       </c>
       <c r="F11" s="30" t="n">
         <f aca="false">E11/$E$16</f>
-        <v>0.0159230925828357</v>
+        <v>0.0157993853012503</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13349,7 +13211,7 @@
       </c>
       <c r="F12" s="32" t="n">
         <f aca="false">E12/$E$16</f>
-        <v>0.902816123258401</v>
+        <v>0.895802100837896</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13374,7 +13236,7 @@
       </c>
       <c r="F13" s="30" t="n">
         <f aca="false">E13/$E$16</f>
-        <v>0.04514080616292</v>
+        <v>0.0447901050418948</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13383,23 +13245,23 @@
       </c>
       <c r="B14" s="18" t="n">
         <f aca="false">도비!$G$31</f>
-        <v>772159.5525</v>
+        <v>1764936.12</v>
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">용접!$G$29</f>
-        <v>2517017.8875</v>
+        <v>1610891.448</v>
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">베이스!$G$32</f>
-        <v>268813.694205</v>
+        <v>716836.51788</v>
       </c>
       <c r="E14" s="29" t="n">
         <f aca="false">SUM(B14:D14)</f>
-        <v>3557991.134205</v>
+        <v>4092664.08588</v>
       </c>
       <c r="F14" s="30" t="n">
         <f aca="false">E14/$E$16</f>
-        <v>0.0520722271134089</v>
+        <v>0.0594319748759131</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13408,23 +13270,23 @@
       </c>
       <c r="B15" s="18" t="n">
         <f aca="false">도비!$G$32</f>
-        <v>-861.052499998361</v>
+        <v>-637.620000001043</v>
       </c>
       <c r="C15" s="18" t="n">
         <f aca="false">용접!$G$30</f>
-        <v>-160.987500000745</v>
+        <v>-34.5480000004172</v>
       </c>
       <c r="D15" s="18" t="n">
         <f aca="false">베이스!$G$33</f>
-        <v>-970.167704999447</v>
+        <v>-992.991379998624</v>
       </c>
       <c r="E15" s="29" t="n">
         <f aca="false">SUM(B15:D15)</f>
-        <v>-1992.20770499855</v>
+        <v>-1665.15938000008</v>
       </c>
       <c r="F15" s="30" t="n">
         <f aca="false">E15/$E$16</f>
-        <v>-2.91565347295187E-005</v>
+        <v>-2.41807557033543E-005</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13433,19 +13295,19 @@
       </c>
       <c r="B16" s="31" t="n">
         <f aca="false">도비!$G$33</f>
-        <v>24213000</v>
+        <v>25206000</v>
       </c>
       <c r="C16" s="31" t="n">
         <f aca="false">용접!$G$31</f>
-        <v>25653000</v>
+        <v>24747000</v>
       </c>
       <c r="D16" s="31" t="n">
         <f aca="false">베이스!$G$34</f>
-        <v>18462000</v>
+        <v>18910000</v>
       </c>
       <c r="E16" s="19" t="n">
         <f aca="false">SUM(B16:D16)</f>
-        <v>68328000</v>
+        <v>68863000</v>
       </c>
       <c r="F16" s="32" t="n">
         <f aca="false">E16/$E$16</f>
@@ -13461,7 +13323,7 @@
       <c r="D17" s="33"/>
       <c r="E17" s="33" t="n">
         <f aca="false">E16*0.1</f>
-        <v>6832800</v>
+        <v>6886300</v>
       </c>
       <c r="F17" s="33"/>
     </row>
@@ -13474,7 +13336,7 @@
       <c r="D18" s="22"/>
       <c r="E18" s="22" t="n">
         <f aca="false">E16+E17</f>
-        <v>75160800</v>
+        <v>75749300</v>
       </c>
       <c r="F18" s="22"/>
     </row>
@@ -13899,7 +13761,7 @@
       <c r="D20" s="20"/>
       <c r="E20" s="39" t="n">
         <f aca="false">도비!$G$33-SUM(도비!$G$23:$G$25)</f>
-        <v>2568600</v>
+        <v>3561600</v>
       </c>
       <c r="F20" s="40" t="s">
         <v>141</v>
@@ -13915,7 +13777,7 @@
       <c r="D21" s="20"/>
       <c r="E21" s="39" t="n">
         <f aca="false">도비!$G$33</f>
-        <v>24213000</v>
+        <v>25206000</v>
       </c>
       <c r="F21" s="40" t="s">
         <v>143</v>
@@ -14227,7 +14089,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="39" t="n">
         <f aca="false">용접!$G$31-SUM(용접!$G$21:$G$23)</f>
-        <v>4393000</v>
+        <v>3487000</v>
       </c>
       <c r="F36" s="40" t="s">
         <v>141</v>
@@ -14243,7 +14105,7 @@
       <c r="D37" s="20"/>
       <c r="E37" s="39" t="n">
         <f aca="false">용접!$G$31</f>
-        <v>25653000</v>
+        <v>24747000</v>
       </c>
       <c r="F37" s="40" t="s">
         <v>178</v>
@@ -14615,7 +14477,7 @@
       <c r="D55" s="20"/>
       <c r="E55" s="39" t="n">
         <f aca="false">베이스!$G$34-SUM(베이스!$G$24:$G$26)</f>
-        <v>1773300</v>
+        <v>2221300</v>
       </c>
       <c r="F55" s="40" t="s">
         <v>141</v>
@@ -14631,7 +14493,7 @@
       <c r="D56" s="20"/>
       <c r="E56" s="39" t="n">
         <f aca="false">베이스!$G$34</f>
-        <v>18462000</v>
+        <v>18910000</v>
       </c>
       <c r="F56" s="40" t="s">
         <v>212</v>
@@ -15323,7 +15185,7 @@
       <c r="F31" s="43"/>
       <c r="G31" s="44" t="n">
         <f aca="false">(G24+G25+G26+G27+G28+G30)*요율근거!$C$9</f>
-        <v>772159.5525</v>
+        <v>1764936.12</v>
       </c>
       <c r="H31" s="20" t="s">
         <v>246</v>
@@ -15341,7 +15203,7 @@
       <c r="F32" s="43"/>
       <c r="G32" s="44" t="n">
         <f aca="false">-MOD(G29+G30+G31,1000)</f>
-        <v>-861.052499998361</v>
+        <v>-637.620000001043</v>
       </c>
       <c r="H32" s="40" t="s">
         <v>247</v>
@@ -15359,7 +15221,7 @@
       <c r="F33" s="45"/>
       <c r="G33" s="46" t="n">
         <f aca="false">G29+G30+G31+G32</f>
-        <v>24213000</v>
+        <v>25206000</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>248</v>
@@ -16049,10 +15911,10 @@
       <c r="F29" s="43"/>
       <c r="G29" s="44" t="n">
         <f aca="false">(G22+G23+G24+G25+G26+G28)*요율근거!$C$10</f>
-        <v>2517017.8875</v>
+        <v>1610891.448</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -16067,7 +15929,7 @@
       <c r="F30" s="43"/>
       <c r="G30" s="44" t="n">
         <f aca="false">-MOD(G27+G28+G29,1000)</f>
-        <v>-160.987500000745</v>
+        <v>-34.5480000004172</v>
       </c>
       <c r="H30" s="40" t="s">
         <v>247</v>
@@ -16085,7 +15947,7 @@
       <c r="F31" s="45"/>
       <c r="G31" s="46" t="n">
         <f aca="false">G27+G28+G29+G30</f>
-        <v>25653000</v>
+        <v>24747000</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>248</v>
@@ -16219,7 +16081,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B5" s="41"/>
       <c r="C5" s="41"/>
@@ -16270,7 +16132,7 @@
         <v>180</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E8" s="42" t="n">
         <v>9991</v>
@@ -16283,7 +16145,7 @@
         <v>6993700</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>69</v>
@@ -16333,7 +16195,7 @@
         <v>160000</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>69</v>
@@ -16387,7 +16249,7 @@
         <v>500000</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>69</v>
@@ -16415,7 +16277,7 @@
         <v>420000</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I13" s="17" t="s">
         <v>69</v>
@@ -16546,7 +16408,7 @@
         <v>202</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>2</v>
@@ -16572,7 +16434,7 @@
         <v>204</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>1</v>
@@ -16611,7 +16473,7 @@
         <v>1200000</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>71</v>
@@ -16667,7 +16529,7 @@
         <v>300000</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>71</v>
@@ -16695,7 +16557,7 @@
         <v>255000</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I23" s="17" t="s">
         <v>71</v>
@@ -16848,10 +16710,10 @@
       <c r="F32" s="43"/>
       <c r="G32" s="44" t="n">
         <f aca="false">(G25+G26+G27+G28+G29+G31)*요율근거!$C$11</f>
-        <v>268813.694205</v>
+        <v>716836.51788</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="I32" s="20"/>
     </row>
@@ -16866,7 +16728,7 @@
       <c r="F33" s="43"/>
       <c r="G33" s="44" t="n">
         <f aca="false">-MOD(G30+G31+G32,1000)</f>
-        <v>-970.167704999447</v>
+        <v>-992.991379998624</v>
       </c>
       <c r="H33" s="40" t="s">
         <v>247</v>
@@ -16884,7 +16746,7 @@
       <c r="F34" s="45"/>
       <c r="G34" s="46" t="n">
         <f aca="false">G30+G31+G32+G33</f>
-        <v>18462000</v>
+        <v>18910000</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>248</v>
@@ -16978,24 +16840,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="49" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>276</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17078,7 +16940,7 @@
         <v>88</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>36</v>
@@ -17086,7 +16948,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="56" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B10" s="57" t="n">
         <v>13575440</v>
@@ -17096,12 +16958,12 @@
         <v>1358.73969092802</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="56" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B11" s="57" t="n">
         <v>9577783</v>
@@ -17111,12 +16973,12 @@
         <v>958.621887260789</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="56" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B12" s="57" t="n">
         <v>4000000</v>
@@ -17126,12 +16988,12 @@
         <v>400.352310032829</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="56" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B13" s="58" t="n">
         <f aca="false">E7*700</f>
@@ -17142,12 +17004,12 @@
         <v>700</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="56" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B14" s="58" t="n">
         <f aca="false">B13-(B11-B12)</f>
@@ -17158,12 +17020,12 @@
         <v>141.730422772039</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -17192,56 +17054,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="59" t="s">
         <v>291</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="D3" s="59" t="s">
         <v>292</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="E3" s="59" t="s">
         <v>293</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="F3" s="59" t="s">
         <v>294</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="G3" s="59" t="s">
         <v>295</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="H3" s="59" t="s">
         <v>296</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="I3" s="59" t="s">
         <v>297</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="J3" s="59" t="s">
         <v>298</v>
       </c>
-      <c r="I3" s="59" t="s">
+      <c r="K3" s="59" t="s">
         <v>299</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="L3" s="59" t="s">
         <v>300</v>
       </c>
-      <c r="K3" s="59" t="s">
+      <c r="M3" s="59" t="s">
         <v>301</v>
-      </c>
-      <c r="L3" s="59" t="s">
-        <v>302</v>
-      </c>
-      <c r="M3" s="59" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="60" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="56"/>
@@ -17257,10 +17119,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="60" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -17276,10 +17138,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="60" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="56"/>
@@ -17295,10 +17157,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="60" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C7" s="56"/>
       <c r="D7" s="56"/>
@@ -17314,10 +17176,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
@@ -17333,10 +17195,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="60" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C9" s="56"/>
       <c r="D9" s="56"/>
@@ -17352,10 +17214,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="60" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
@@ -17371,7 +17233,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -17402,26 +17264,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="D4" s="15" t="s">
         <v>321</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17429,13 +17291,13 @@
         <v>72</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C5" s="62" t="n">
         <v>0.0356</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17443,13 +17305,13 @@
         <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C6" s="62" t="n">
         <v>0.0115</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17457,13 +17319,13 @@
         <v>74</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C7" s="62" t="n">
         <v>0.0311</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17471,91 +17333,91 @@
         <v>76</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C8" s="62" t="n">
         <v>0.05</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C9" s="63" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="C9" s="63" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C10" s="63" t="n">
-        <v>0.125</v>
+        <v>0.08</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C11" s="63" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="D12" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="64" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>343</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17563,7 +17425,7 @@
         <v>144</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C16" s="42" t="n">
         <v>292640</v>
@@ -17578,10 +17440,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C17" s="42" t="n">
         <v>266029</v>
@@ -17599,7 +17461,7 @@
         <v>153</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C18" s="42" t="n">
         <v>226122</v>
@@ -17617,7 +17479,7 @@
         <v>126</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C19" s="42" t="n">
         <v>172068</v>
@@ -17635,7 +17497,7 @@
         <v>159</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C20" s="42" t="n">
         <v>226122</v>
@@ -17653,7 +17515,7 @@
         <v>96</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C21" s="42" t="n">
         <v>226122</v>
@@ -17671,7 +17533,7 @@
         <v>91</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C22" s="42" t="n">
         <v>281939</v>
@@ -17686,7 +17548,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="34" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -17695,15 +17557,15 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="64" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="66" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B26" s="67" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C26" s="67"/>
       <c r="D26" s="67"/>
@@ -17711,10 +17573,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="66" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C27" s="67"/>
       <c r="D27" s="67"/>
@@ -17722,10 +17584,10 @@
     </row>
     <row r="28" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="66" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B28" s="67" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C28" s="67"/>
       <c r="D28" s="67"/>
@@ -17736,7 +17598,7 @@
         <v>74</v>
       </c>
       <c r="B29" s="67" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C29" s="67"/>
       <c r="D29" s="67"/>
@@ -17744,10 +17606,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="66" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B30" s="67" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C30" s="67"/>
       <c r="D30" s="67"/>
@@ -17755,10 +17617,10 @@
     </row>
     <row r="31" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="68" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B31" s="67" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C31" s="67"/>
       <c r="D31" s="67"/>
@@ -17766,10 +17628,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="66" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B32" s="69" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C32" s="69"/>
       <c r="D32" s="69"/>
@@ -17777,7 +17639,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="36" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -6009,7 +6009,96 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">부대 잡비 </t>
+      <t xml:space="preserve">부대 잡비</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 </t>
     </r>
     <r>
       <rPr>
@@ -6028,8 +6117,498 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">인당 </t>
-    </r>
+      <t xml:space="preserve">사용자 제시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회수조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">H-250×250×9×14, 10m 4·5m 16·0.6m 30EA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9,991kg × 700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중고 구매 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9,577,783</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 − 회수 고철가치 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회수 손료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 견적 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 제시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회수조건 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 반입 운임</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급처 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빔 견적</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">회수 반출 운임</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접봉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디스크</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">레벨 조정재</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라이너</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심 플레이트</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">제관사</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">절단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">취부</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인원 사용자 제시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직종 구성 가정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">베이스 조립 용접</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6047,6 +6626,25 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">일 </t>
     </r>
     <r>
@@ -6057,7 +6655,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">50,000</t>
+      <t xml:space="preserve">× 500,000</t>
     </r>
     <r>
       <rPr>
@@ -6068,6 +6666,497 @@
       </rPr>
       <t xml:space="preserve">원</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자재 정리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보조</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 200,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">절단 화기작업 전담</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 250,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">지게차</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자재 하역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조립</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회수 시 해체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상차</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사용자 제시 단가 준용</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 400,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 제시</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6088,7 +7177,1481 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">28</t>
+      <t xml:space="preserve">B_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도비</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안착</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">밀착</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·90° </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회전 후 정리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6 + 6 + 3 + 6)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 300,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인원 사용자 제시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-12: A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가 서해테크 도비 견적서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-10) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 260,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">인양구역 통제</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100TON (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안착</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60TON (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안착</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200TON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(90° </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회전 주 크레인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 3,500,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 제시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 제시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-12: 350</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200TON </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회송</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">웨이트 운반</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">카운터웨이트 트레일러 왕복</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회전용 대형 줄걸이</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">급 샤클</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">슬링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스프레더 손료</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 640,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회전 착지 깔목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고무판</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목재 받침 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300×300, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고무판</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">와이어 보호대 등</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안과 같음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용접</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조방</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">보강보</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H-200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25m (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현장 보유 강재 사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 지시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-12: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현장에 있는 강재 사용</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">배관 복구 자재</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가스켓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">볼트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">너트</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">조방 보강보 취부</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 350,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">보강보 용접</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 500,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">보조</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 200,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">화기작업 전담</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 250,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바닥 접촉면 기구물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배관 제거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">복원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 350,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 지시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-12 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눕혀 작업하기 위한 기구물 제거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">복원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단가 가정값 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업체 견적으로 확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
     </r>
     <r>
       <rPr>
@@ -6116,566 +8679,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 50,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">목표 약 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25,000,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 제시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빔 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회수조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">H-250×250×9×14, 10m 4·5m 16·0.6m 30EA</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9,991kg × 700</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중고 구매 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9,577,783</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원 − 회수 고철가치 약 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">400</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만원 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회수 손료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공급처 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빔 견적 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 제시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회수조건 약 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">700</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빔 반입 운임</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">공급처 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빔 견적</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">회수 반출 운임</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접봉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디스크</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">레벨 조정재</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">라이너</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">심 플레이트</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">제관사</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">절단</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">취부</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인원 사용자 제시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직종 구성 가정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">베이스 조립 용접</t>
-  </si>
-  <si>
+      <t xml:space="preserve">일 기준 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6693,2079 +8698,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 500,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자재 정리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보조</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 200,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">절단 화기작업 전담</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 250,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">지게차</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자재 하역</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조립</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 300,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회수 시 해체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상차</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 300,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">사용자 제시 단가 준용</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 400,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 50,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">목표 약 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18,000,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 제시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">도비</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안착</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">밀착</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·90° </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회전 후 정리</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(6 + 6 + 3 + 6)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 300,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인원 사용자 제시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026-10-12: A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단가 서해테크 도비 견적서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026-10-10) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 260,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">인양구역 통제</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100TON (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안착</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">60TON (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안착</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200TON</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">급 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(90° </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회전 주 크레인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 3,500,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 제시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 제시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-12: 350</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200TON </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회송</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">웨이트 운반</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">카운터웨이트 트레일러 왕복</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회전용 대형 줄걸이</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">급 샤클</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">슬링</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스프레더 손료</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 640,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회전 착지 깔목</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고무판</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">목재 받침 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">300×300, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고무판</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">와이어 보호대 등</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안과 같음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대안</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">용접</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조방</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">보강보</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H-200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">급</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">약 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25m (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현장 보유 강재 사용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 지시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-12: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현장에 있는 강재 사용</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">배관 복구 자재</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가스켓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">볼트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">너트</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">조방 보강보 취부</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 350,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">보강보 용접</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 500,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">보조</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 200,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">화기작업 전담</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 250,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">바닥 접촉면 기구물</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배관 제거</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">복원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">명 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 350,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 지시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-12 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눕혀 작업하기 위한 기구물 제거</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">복원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단가 가정값 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">업체 견적으로 확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 50,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
+      <t xml:space="preserve">식</t>
     </r>
   </si>
   <si>
@@ -17322,13 +17255,13 @@
         <v>185</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>263</v>
+        <v>39</v>
       </c>
       <c r="E16" s="44" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>50000</v>
+        <v>550000</v>
       </c>
       <c r="G16" s="32" t="n">
         <f aca="false">E16*F16</f>
@@ -19662,7 +19595,7 @@
       </c>
       <c r="G31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
         <v>64</v>
       </c>
@@ -19984,7 +19917,7 @@
       </c>
       <c r="G47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
         <v>65</v>
       </c>
@@ -20676,7 +20609,7 @@
       </c>
       <c r="G81" s="4"/>
     </row>
-    <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
         <v>237</v>
       </c>
@@ -20916,7 +20849,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
         <v>238</v>
       </c>
@@ -22124,13 +22057,13 @@
         <v>185</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>263</v>
+        <v>39</v>
       </c>
       <c r="E18" s="44" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F18" s="44" t="n">
-        <v>50000</v>
+        <v>1400000</v>
       </c>
       <c r="G18" s="32" t="n">
         <f aca="false">E18*F18</f>
@@ -22841,13 +22774,13 @@
         <v>185</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>263</v>
+        <v>39</v>
       </c>
       <c r="E20" s="44" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F20" s="44" t="n">
-        <v>50000</v>
+        <v>750000</v>
       </c>
       <c r="G20" s="32" t="n">
         <f aca="false">E20*F20</f>
@@ -24338,13 +24271,13 @@
         <v>185</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>263</v>
+        <v>39</v>
       </c>
       <c r="E18" s="44" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F18" s="44" t="n">
-        <v>50000</v>
+        <v>1400000</v>
       </c>
       <c r="G18" s="32" t="n">
         <f aca="false">E18*F18</f>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -20357,8 +20357,8 @@
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
       <c r="E69" s="41" t="n">
-        <f aca="false">B_도비!$G$35-SUM(B_도비!$G$25:B25)</f>
-        <v>31247000</v>
+        <f aca="false">B_도비!$G$35-SUM(B_도비!$G$25:$G$27)</f>
+        <v>6237000</v>
       </c>
       <c r="F69" s="42" t="s">
         <v>149</v>
@@ -20639,8 +20639,8 @@
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
       <c r="E83" s="41" t="n">
-        <f aca="false">B_용접!$G$29-SUM(B_용접!$G$19:B19)</f>
-        <v>24041000</v>
+        <f aca="false">B_용접!$G$29-SUM(B_용접!$G$19:$G$21)</f>
+        <v>5191000</v>
       </c>
       <c r="F83" s="42" t="s">
         <v>149</v>
@@ -20879,8 +20879,8 @@
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
       <c r="E95" s="41" t="n">
-        <f aca="false">B_조방!$G$27-SUM(B_조방!$G$17:B17)</f>
-        <v>5622000</v>
+        <f aca="false">B_조방!$G$27-SUM(B_조방!$G$17:$G$19)</f>
+        <v>1322000</v>
       </c>
       <c r="F95" s="42" t="s">
         <v>149</v>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -452,7 +452,7 @@
     <t xml:space="preserve">특기사항</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 공사 기간: 2026.10.21 ~ 2026.11.02 (가계획, 작업일 11일, 공정표 시트 참조). 착공일은 발주처 협의로 확정함.</t>
+    <t xml:space="preserve">1. 공사 기간: 2026.10.21 ~ 2026.11.02 (가정 일정, 작업일 11일, 공정표 시트 참조). 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
   </si>
   <si>
     <t xml:space="preserve">2. 결제 조건: 협의 (예: 착수 30%, 준공 후 70%).</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">※ B안 200t급 크레인은 사용자 제시 단가 350만/일 적용. 회송·웨이트 운반은 별도 줄로 넣음. B안 용접은 3면 용접 → 전체 90° 회전 → 나머지 1면 용접 순서로, 용접 1일이 회전 후로 이동함(금액 동일).</t>
   </si>
   <si>
-    <t xml:space="preserve">※ B안 회전은 일체 약 83t(45t + 38t)을 모서리 기준으로 세우는 작업으로, 실제 크레인 사양은 인양계획서·구조검토로 확정 필요함.</t>
+    <t xml:space="preserve">※ B안 회전은 일체 약 86t(38t + 48t)을 모서리 기준으로 세우는 작업으로, 실제 크레인 사양은 인양계획서·구조검토로 확정 필요함.</t>
   </si>
   <si>
     <t xml:space="preserve">※ 회전 후 원래 자세로 되돌리는 회전이나 영구 받침이 필요하면 별도임.</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">안착일</t>
   </si>
   <si>
-    <t xml:space="preserve">회전일, 일체 약 83t</t>
+    <t xml:space="preserve">회전일, 일체 약 86t</t>
   </si>
   <si>
     <t xml:space="preserve">대형 크레인 부대비</t>
@@ -1219,7 +1219,7 @@
     <t xml:space="preserve">단위중량 72.4 kg/m는 KS H-250×250×9×14 공칭값임. 베이스는 임시 구조물로 방청·도장 미적용.</t>
   </si>
   <si>
-    <t xml:space="preserve">공정표 (가계획 2026.10.21 ~ 11.02, 작업일 11일)</t>
+    <t xml:space="preserve">공정표 (가정 일정 2026.10.21 ~ 11.02, 작업일 11일)</t>
   </si>
   <si>
     <t xml:space="preserve">공정</t>
@@ -1311,7 +1311,7 @@
     <t xml:space="preserve">펜스 해체·정리</t>
   </si>
   <si>
-    <t xml:space="preserve">가계획: 2026-10-21(수) 착공 ~ 11-02(월) 완료, 일요일 휴무 기준 작업일 11일. 착공일은 발주처 협의로 확정함.</t>
+    <t xml:space="preserve">가정 일정: 2026-10-21(수) 착공 ~ 11-02(월) 완료, 일요일 휴무 기준 작업일 11일. 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
   </si>
   <si>
     <t xml:space="preserve">요율 및 단가 근거</t>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -455,7 +455,7 @@
     <t xml:space="preserve">1. 공사 기간: 2026.10.21 ~ 2026.11.02 (가정 일정, 작업일 11일, 공정표 시트 참조). 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. 결제 조건: 협의 (예: 착수 30%, 준공 후 70%).</t>
+    <t xml:space="preserve">2. 결제 조건: 선수금 30% (계약 시), 중도금 30% (회전·안착 완료 시), 잔금 40% (용접 완료 후). A안 VAT 포함 기준 23,658,360원 / 23,658,360원 / 31,544,480원.</t>
   </si>
   <si>
     <t xml:space="preserve">3. 견적 유효기간: 발행일로부터 30일.</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">5. 제외: 전기 수전, 배관·닥트 해체·복구, 보온, 도장, 비파괴검사(PT/UT), 시운전. 비파괴검사는 발주처 요구 시 별도 정산함.</t>
   </si>
   <si>
-    <t xml:space="preserve">6. 크레인 사양·배치는 인양계획서와 지반 검토 후 확정하며, 크레인 변경에 따른 추가비용은 없음.</t>
+    <t xml:space="preserve">6. 크레인 사양·배치는 크레인 업체와 협의해 확정하며, 크레인 변경에 따른 추가비용은 없음.</t>
   </si>
   <si>
     <t xml:space="preserve">7. 연장·야간·휴일 작업은 공정에 따라 당사가 수행하며 추가 정산하지 않음. 기상(우천 시 용접 불가)·발주처 사유에 따른 대기는 별도 협의함.</t>
@@ -3883,7 +3883,7 @@
       <c r="H69" s="24"/>
       <c r="I69" s="24"/>
     </row>
-    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="24" t="s">
         <v>137</v>
       </c>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">업체명</t>
   </si>
   <si>
-    <t xml:space="preserve">금강변압기 유한회사 (KUMKANG TRANSFORMER)</t>
+    <t xml:space="preserve">주식회사 금강변압기</t>
   </si>
   <si>
     <t xml:space="preserve">상호</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">공 종 별   내 역 서</t>
   </si>
   <si>
-    <t xml:space="preserve">견적번호 NM-2610-01   |   견적일 2026-10-13   |   금강변압기 유한회사 귀중</t>
+    <t xml:space="preserve">견적번호 NM-2610-01   |   견적일 2026-10-13   |   주식회사 금강변압기 귀중</t>
   </si>
   <si>
     <t xml:space="preserve">공 종 : 진공건조로 2기 회전·베이스 안착(1일), 용접면 밀착 이동(2일), 작업구역 안전펜스</t>
@@ -2346,7 +2346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>8</v>
       </c>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -20,7 +20,7 @@
     <sheet name="B_조방" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="베이스자재" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="공정표" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="요율근거" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="요율근거" sheetId="13" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Titles" vbProcedure="false">B_도비!$7:$7</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="374">
   <si>
     <t xml:space="preserve">N M   S O L U T I O N</t>
   </si>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">식</t>
   </si>
   <si>
-    <t xml:space="preserve">요율근거 시트</t>
+    <t xml:space="preserve">원가계산서 참조</t>
   </si>
   <si>
     <t xml:space="preserve">도비 소계</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">H-250×250×9×14, 10m 4·5m 16·0.6m 30EA</t>
   </si>
   <si>
-    <t xml:space="preserve">공사 후 회수, 중고 구매가 9,577,783원</t>
+    <t xml:space="preserve">공사 후 회수 조건</t>
   </si>
   <si>
     <t xml:space="preserve">H빔 반입 운임</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">총 공사금액</t>
   </si>
   <si>
-    <t xml:space="preserve">요율: 산재 3.56%·고용 1.15% (노무비 기준), 산업안전보건관리비 3.11% ((재료비 + 노무비) 기준), 일반관리비 5% (순공사원가 기준), 이윤은 공종별 15% 이내. 근거는 '요율근거' 시트.</t>
+    <t xml:space="preserve">요율: 산재 3.56%·고용 1.15% (노무비 기준), 산업안전보건관리비 3.11% ((재료비 + 노무비) 기준), 일반관리비 5% (순공사원가 기준), 이윤 15%. 보험료율은 2026년 고용노동부 고시, 산업안전보건관리비는 고용노동부 계상기준 적용함.</t>
   </si>
   <si>
     <t xml:space="preserve">A안 · B안 금액 비교 (공급가액, 부가세 별도)</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">차액 (B − A)</t>
   </si>
   <si>
-    <t xml:space="preserve">B안: 200t급 크레인 1대 추가(350만/일, 단독 90° 회전), 도비 6명 1일 추가</t>
+    <t xml:space="preserve">B안: 200t급 크레인 1대 1일 추가(단독 90° 회전), 도비 6명 1일 추가</t>
   </si>
   <si>
     <t xml:space="preserve">같은 인원·장비로 상부·측면 용접 후 회전해서 하부 용접</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">공급가액 계</t>
   </si>
   <si>
-    <t xml:space="preserve">※ B안 200t급 크레인은 사용자 제시 단가 350만/일 적용. 회송·웨이트 운반은 별도 줄로 넣음. B안 용접은 3면 용접 → 전체 90° 회전 → 나머지 1면 용접 순서로, 용접 1일이 회전 후로 이동함(금액 동일).</t>
+    <t xml:space="preserve">※ B안 200t급 크레인은 1일 임대 단가 적용, 회송·웨이트 운반은 별도 항목으로 계상함. B안 용접은 3면 용접 → 전체 90° 회전 → 나머지 1면 용접 순서로, 용접 1일이 회전 후로 이동함(금액 동일).</t>
   </si>
   <si>
     <t xml:space="preserve">※ B안 회전은 일체 약 86t(38t + 48t)을 모서리 기준으로 세우는 작업으로, 실제 크레인 사양은 인양계획서·구조검토로 확정 필요함.</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">견적 산출근거</t>
   </si>
   <si>
-    <t xml:space="preserve">금액은 공종 시트에서 연동됨. 근거란에 '가정값'으로 표시한 항목은 업체 견적으로 확인할 값임.</t>
+    <t xml:space="preserve">금액은 공종 시트에서 연동됨. 인원·일수는 작업 범위와 공정표 기준, 단가는 동종 플랜트 현장 시장 단가 기준으로 산정함.</t>
   </si>
   <si>
     <t xml:space="preserve">공종</t>
@@ -608,25 +608,16 @@
     <t xml:space="preserve">근거</t>
   </si>
   <si>
-    <t xml:space="preserve">시중노임 참고</t>
-  </si>
-  <si>
     <t xml:space="preserve">(6 + 6 + 3)명 × 300,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">인원 사용자 제시 (2026-10-12), 단가 서해테크 도비 견적서(2026-10-10) 단가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">비계공 281,939원</t>
+    <t xml:space="preserve">인원·일수: 작업 범위·공정표 기준 / 단가: 중량물 도비 전문기공 시장 단가</t>
   </si>
   <si>
     <t xml:space="preserve">2명 × 1일 × 260,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">가정값 (업체 견적으로 확인 필요)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">특별인부 226,122원</t>
+    <t xml:space="preserve">크레인 인양 작업 안전관리 인력, 단가: 시장 단가</t>
   </si>
   <si>
     <t xml:space="preserve">1명 × 3일 × 320,000원</t>
@@ -635,7 +626,7 @@
     <t xml:space="preserve">1대 × 1일 × 2,400,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">사용자 제시</t>
+    <t xml:space="preserve">이동식 크레인 1일 임대 시장 단가 (운전원 포함)</t>
   </si>
   <si>
     <t xml:space="preserve">1대 × 1일 × 1,700,000원</t>
@@ -644,67 +635,73 @@
     <t xml:space="preserve">8매 × 80,000원</t>
   </si>
   <si>
+    <t xml:space="preserve">장비 임대 시장 단가, 투입 수량·일수는 공정표 기준</t>
+  </si>
+  <si>
     <t xml:space="preserve">1식 (2일)</t>
   </si>
   <si>
     <t xml:space="preserve">1식</t>
   </si>
   <si>
-    <t xml:space="preserve">서해테크 도비 견적서(2026-10-10) 단가</t>
+    <t xml:space="preserve">중량물 작업 전문장비 사용 손료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자재 시장 단가, 작업 범위 기준 1식</t>
   </si>
   <si>
     <t xml:space="preserve">작업구역 10×15m, 둘레 50m ÷ 2.4m = 21매 + 출입문 1매 → 22매 × 11일 × 5,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">수량 가정값 (업체 견적으로 확인 필요), 단가 사용자 제시</t>
+    <t xml:space="preserve">작업구역 둘레 기준 수량 × 임대 시장 단가</t>
   </si>
   <si>
     <t xml:space="preserve">2명 × 1일 × 250,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">보통인부 172,068원</t>
+    <t xml:space="preserve">인원·일수: 작업 범위·공정표 기준 / 단가: 플랜트 숙련 기능인력 시장 단가</t>
   </si>
   <si>
     <t xml:space="preserve">2회 × 260,000원</t>
   </si>
   <si>
+    <t xml:space="preserve">화물 운반 시장 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업구역 출입통제 자재, 1식</t>
+  </si>
+  <si>
     <t xml:space="preserve">1식 600,000원</t>
   </si>
   <si>
+    <t xml:space="preserve">공종 현장 부대비 1식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">법정 요율·일반관리비·이윤 (원가계산서 하단 참조)</t>
+  </si>
+  <si>
     <t xml:space="preserve">공종 합계</t>
   </si>
   <si>
-    <t xml:space="preserve">목표 약 20,000,000원 (사용자 제시)</t>
+    <t xml:space="preserve">부가세 별도</t>
   </si>
   <si>
     <t xml:space="preserve">3명 × 3일 × 500,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">인원·일수 사용자 제시, 단가 현장 실거래 수준 적용 (사용자 지시: 용접사 상향, 고급기술자=제관사 수준)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">플랜트용접공 292,640원</t>
-  </si>
-  <si>
     <t xml:space="preserve">2명 × 3일 × 350,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">플랜트제관공 266,029원</t>
-  </si>
-  <si>
     <t xml:space="preserve">2명 × 2일 × 300,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">인원·일수 사용자 제시</t>
-  </si>
-  <si>
     <t xml:space="preserve">2명 × 2일 × 200,000원</t>
   </si>
   <si>
     <t xml:space="preserve">1명 × 5일 × 250,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">산업안전보건기준에 관한 규칙 제241조의2, 단가 가정값 (업체 견적으로 확인 필요)</t>
+    <t xml:space="preserve">산업안전보건기준에 관한 규칙 제241조의2 (화기작업 화재감시자 배치), 단가는 숙련 기능인력 시장 단가</t>
   </si>
   <si>
     <t xml:space="preserve">3대 × 3일 × 400,000원</t>
@@ -713,28 +710,19 @@
     <t xml:space="preserve">1식 (용접재 3,000,000 + 전원 케이블·잡자재 680,000)</t>
   </si>
   <si>
-    <t xml:space="preserve">1식 (사용자 제시 약 100만원)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2대 × 11일 × 100,000원</t>
   </si>
   <si>
     <t xml:space="preserve">28인·일 기준 1식</t>
   </si>
   <si>
-    <t xml:space="preserve">목표 약 25,000,000원 (사용자 제시)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,991kg × 700원 (중고 구매 9,577,783원 − 회수 고철가치 약 400만원 + 회수 손료)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공급처 H빔 견적 + 사용자 제시 (회수조건 약 700만원)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공급처 H빔 견적</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인원 사용자 제시(4명), 직종 구성 가정</t>
+    <t xml:space="preserve">투입 인·일 기준 현장 부대비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,991kg × 700원 (회수조건 적용 단가, 베이스자재 시트)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H빔 공칭중량 × 회수조건 적용 단가 (베이스자재 시트)</t>
   </si>
   <si>
     <t xml:space="preserve">1명 × 3일 × 500,000원</t>
@@ -752,18 +740,12 @@
     <t xml:space="preserve">1일 × 300,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">사용자 제시 단가 준용</t>
-  </si>
-  <si>
     <t xml:space="preserve">1대 × 3일 × 400,000원</t>
   </si>
   <si>
     <t xml:space="preserve">15인·일 기준 1식</t>
   </si>
   <si>
-    <t xml:space="preserve">목표 약 18,000,000원 (사용자 제시)</t>
-  </si>
-  <si>
     <t xml:space="preserve">B_도비</t>
   </si>
   <si>
@@ -773,9 +755,6 @@
     <t xml:space="preserve">(6 + 6 + 3 + 6)명 × 300,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">인원 사용자 제시 (2026-10-12: A안 + 6명 1일), 단가 서해테크 도비 견적서(2026-10-10) 단가</t>
-  </si>
-  <si>
     <t xml:space="preserve">2명 × 2일 × 260,000원</t>
   </si>
   <si>
@@ -794,9 +773,6 @@
     <t xml:space="preserve">1대 × 1일 × 3,500,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">사용자 제시 (사용자 제시 2026-10-12: 350만/일)</t>
-  </si>
-  <si>
     <t xml:space="preserve">200TON 회송·웨이트 운반</t>
   </si>
   <si>
@@ -824,7 +800,7 @@
     <t xml:space="preserve">A안과 같음</t>
   </si>
   <si>
-    <t xml:space="preserve">B안 (대안)</t>
+    <t xml:space="preserve">B안 (대안), 부가세 별도</t>
   </si>
   <si>
     <t xml:space="preserve">B_용접</t>
@@ -839,7 +815,10 @@
     <t xml:space="preserve">H-200급, 약 25m (현장 보유 강재 사용)</t>
   </si>
   <si>
-    <t xml:space="preserve">사용자 지시 2026-10-12: 현장에 있는 강재 사용</t>
+    <t xml:space="preserve">현장 보유 강재 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현장 보유 강재 사용, 자재비 미계상</t>
   </si>
   <si>
     <t xml:space="preserve">배관 복구 자재</t>
@@ -878,15 +857,9 @@
     <t xml:space="preserve">2명 × 2일 × 350,000원</t>
   </si>
   <si>
-    <t xml:space="preserve">사용자 지시 2026-10-12 (눕혀 작업하기 위한 기구물 제거·복원), 단가 가정값 (업체 견적으로 확인 필요)</t>
-  </si>
-  <si>
     <t xml:space="preserve">11인·일 기준 1식</t>
   </si>
   <si>
-    <t xml:space="preserve">근거 구분: 사용자 제시 = 받은 단가·인원·일수 / 서해테크 = 도비 협력사 견적서(2026-10-10) / 공급처 = H빔 견적 / 가정값 = 업체 견적 전 임시값</t>
-  </si>
-  <si>
     <t xml:space="preserve">공 종 별   내 역 서</t>
   </si>
   <si>
@@ -944,10 +917,7 @@
     <t xml:space="preserve">천원 미만 절사</t>
   </si>
   <si>
-    <t xml:space="preserve">부가세 별도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 수량·단가의 근거는 '산출근거'·'요율근거' 시트에 정리함.</t>
+    <t xml:space="preserve">※ 수량·단가의 근거는 '산출근거' 시트에 정리함.</t>
   </si>
   <si>
     <t xml:space="preserve">※ 연장·야간·휴일 작업은 공정에 따라 당사가 수행함 (추가 정산 없음).</t>
@@ -1013,13 +983,13 @@
     <t xml:space="preserve">1명 × 1일</t>
   </si>
   <si>
-    <t xml:space="preserve">2명 × 2일 (제거 1 + 복원 1), 사용자 지정 2명</t>
+    <t xml:space="preserve">2명 × 2일 (제거 1 + 복원 1)</t>
   </si>
   <si>
     <t xml:space="preserve">개조 1일 7명 + 제거·복원 2명 × 2일 (용접기·절단기 임대는 용접 공종에 계상)</t>
   </si>
   <si>
-    <t xml:space="preserve">베이스 자재: H-250×250×9×14 (공급처 견적, 부가세 미포함)</t>
+    <t xml:space="preserve">베이스 자재: H-250×250×9×14 (회수조건)</t>
   </si>
   <si>
     <t xml:space="preserve">길이(m)</t>
@@ -1037,183 +1007,13 @@
     <t xml:space="preserve">중량(kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">kg당(원)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">신품 구매</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공급처 견적</t>
-  </si>
-  <si>
-    <t xml:space="preserve">중고 구매</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고철 매각 예상</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 제시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">약 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">400</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">적용 단가(원/kg)</t>
   </si>
   <si>
     <t xml:space="preserve">회수조건 적용</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">kg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">700</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">견적 반영</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회수 손료 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">차액</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">중고 구매가 − 고철가치 대비 추가분</t>
+    <t xml:space="preserve">공사 후 회수, 사용 기간 손료 개념</t>
   </si>
   <si>
     <t xml:space="preserve">단위중량 72.4 kg/m는 KS H-250×250×9×14 공칭값임. 베이스는 임시 구조물로 방청·도장 미적용.</t>
@@ -1314,7 +1114,7 @@
     <t xml:space="preserve">가정 일정: 2026-10-21(수) 착공 ~ 11-02(월) 완료, 일요일 휴무 기준 작업일 11일. 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
   </si>
   <si>
-    <t xml:space="preserve">요율 및 단가 근거</t>
+    <t xml:space="preserve">요율 입력값</t>
   </si>
   <si>
     <t xml:space="preserve">요율·단가 칸은 입력값임. 변경 시 모든 공종 시트와 견적서가 다시 계산됨.</t>
@@ -1375,118 +1175,21 @@
   </si>
   <si>
     <t xml:space="preserve">이윤 (B_조방)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">국민연금·건강·장기요양</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미계상</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1인 투입 3~5일로 건설일용 사업장가입 기준(월 8일 이상 또는 월 220만원 이상)에 미달하는 것으로 봄. 인원 운용이 바뀌면 국민연금 4.75%, 건강 3.545%, 장기요양(건강보험료의 12.95%) 추가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시중노임 대비 적용 단가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">직종 (견적)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시중노임 직종</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시중노임(원/일)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적용 단가(원/일)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">배율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">플랜트용접공</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고급기술자·제관사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">플랜트제관공</t>
-  </si>
-  <si>
-    <t xml:space="preserve">특별인부</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보통인부</t>
-  </si>
-  <si>
-    <t xml:space="preserve">비계공</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시중노임은 대한건설협회 2026년 상반기 적용 건설업 임금실태조사 보고서(2026.1.1 적용) 기준. 대한건설협회 2026년 하반기 적용 조사(2026.9.1 적용) 132개 직종 평균 282,737원, 직전 대비 +0.98%. 적용 단가는 숙련 기능공 현장 실거래 수준(사용자 지시)으로 시중노임보다 높게 적용함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출처</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시중노임 상반기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kmcca.or.kr/images/pegs/down_file/2026%EB%85%84%20%EC%83%81%EB%B0%98%EA%B8%B0%EC%A0%81%EC%9A%A9%20%EA%B1%B4%EC%84%A4%EC%97%85%20%EC%9E%84%EA%B8%88%EC%8B%A4%ED%83%9C%EC%A1%B0%EC%82%AC%20%EB%B3%B4%EA%B3%A0%EC%84%9C.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시중노임 하반기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.conslove.co.kr/news/articleView.html?idxno=89479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산재·고용보험 요율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kosca21.or.kr/km_board/upload/km_b_notice/1767346180_02.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://biz.newdaily.co.kr/site/data/html/2026/05/07/2026050700116.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">원가계산 제비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://04noti.com/construction-cost-ratio-guide/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4대보험(연금·건강)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://calctools.co.kr/blog/daily-worker-insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화재감시자 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산업안전보건기준에 관한 규칙 제241조의2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">조사일 2026-10-12. 요율은 해마다 바뀌므로 계약 시점 고시로 재확인 필요함.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="General"/>
     <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="0.00%"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1636,13 +1339,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0F2A44"/>
-      <name val="Pretendard"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1763,7 +1459,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1988,16 +1684,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2014,18 +1702,6 @@
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4158,7 +3834,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -4182,7 +3858,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -4195,7 +3871,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -4240,10 +3916,10 @@
         <v>157</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>75</v>
@@ -4259,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>157</v>
@@ -4294,10 +3970,10 @@
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11"/>
       <c r="B10" s="11" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>75</v>
@@ -4313,7 +3989,7 @@
         <v>380000</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>157</v>
@@ -4327,10 +4003,10 @@
         <v>120</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>2</v>
@@ -4343,7 +4019,7 @@
         <v>700000</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>158</v>
@@ -4355,10 +4031,10 @@
         <v>80</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>2</v>
@@ -4371,7 +4047,7 @@
         <v>1000000</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>158</v>
@@ -4383,10 +4059,10 @@
         <v>89</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>2</v>
@@ -4399,7 +4075,7 @@
         <v>400000</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>158</v>
@@ -4411,10 +4087,10 @@
         <v>91</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -4427,7 +4103,7 @@
         <v>250000</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>158</v>
@@ -4439,10 +4115,10 @@
         <v>120</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>4</v>
@@ -4455,7 +4131,7 @@
         <v>1400000</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>158</v>
@@ -4485,7 +4161,7 @@
         <v>550000</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>71</v>
@@ -4493,7 +4169,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="45" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B17" s="45"/>
       <c r="C17" s="45"/>
@@ -4509,7 +4185,7 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -4525,7 +4201,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="45" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B19" s="45"/>
       <c r="C19" s="45"/>
@@ -4553,7 +4229,7 @@
         <v>133500</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I20" s="20"/>
     </row>
@@ -4571,7 +4247,7 @@
         <v>43125</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="I21" s="20"/>
     </row>
@@ -4589,7 +4265,7 @@
         <v>141505</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="I22" s="20"/>
     </row>
@@ -4623,7 +4299,7 @@
         <v>270906.5</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I24" s="20"/>
     </row>
@@ -4641,7 +4317,7 @@
         <v>733355.475</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I25" s="20"/>
     </row>
@@ -4659,13 +4335,13 @@
         <v>-391.974999999627</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="47" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B27" s="47"/>
       <c r="C27" s="47"/>
@@ -4677,13 +4353,13 @@
         <v>6422000</v>
       </c>
       <c r="H27" s="38" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="I27" s="38"/>
     </row>
     <row r="29" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B29" s="49"/>
       <c r="C29" s="49"/>
@@ -4696,7 +4372,7 @@
     </row>
     <row r="30" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B30" s="49"/>
       <c r="C30" s="49"/>
@@ -4754,36 +4430,34 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4863,95 +4537,40 @@
         <v>170</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="D9" s="15" t="s">
+      <c r="E9" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="56" t="s">
-        <v>332</v>
-      </c>
-      <c r="B10" s="57" t="n">
-        <v>13575440</v>
-      </c>
-      <c r="C10" s="52" t="n">
-        <f aca="false">B10/$E$7</f>
-        <v>1358.73969092802</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="56" t="s">
-        <v>334</v>
-      </c>
-      <c r="B11" s="57" t="n">
-        <v>9577783</v>
-      </c>
-      <c r="C11" s="52" t="n">
-        <f aca="false">B11/$E$7</f>
-        <v>958.621887260789</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>333</v>
+      <c r="A10" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="B10" s="56" t="n">
+        <f aca="false">E7</f>
+        <v>9991.2</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <f aca="false">B10*C10</f>
+        <v>6993840</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="56" t="s">
-        <v>335</v>
-      </c>
-      <c r="B12" s="57" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="C12" s="52" t="n">
-        <f aca="false">B12/$E$7</f>
-        <v>400.352310032829</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="56" t="s">
-        <v>337</v>
-      </c>
-      <c r="B13" s="58" t="n">
-        <f aca="false">E7*700</f>
-        <v>6993840</v>
-      </c>
-      <c r="C13" s="52" t="n">
-        <f aca="false">B13/$E$7</f>
-        <v>700</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="56" t="s">
-        <v>339</v>
-      </c>
-      <c r="B14" s="58" t="n">
-        <f aca="false">B13-(B11-B12)</f>
-        <v>1416057</v>
-      </c>
-      <c r="C14" s="52" t="n">
-        <f aca="false">B14/$E$7</f>
-        <v>141.730422772039</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="40" t="s">
-        <v>341</v>
+      <c r="A12" s="40" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -4980,186 +4599,186 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="C3" s="59" t="s">
-        <v>345</v>
-      </c>
-      <c r="D3" s="59" t="s">
-        <v>346</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>347</v>
-      </c>
-      <c r="F3" s="59" t="s">
-        <v>348</v>
-      </c>
-      <c r="G3" s="59" t="s">
-        <v>349</v>
-      </c>
-      <c r="H3" s="59" t="s">
-        <v>350</v>
-      </c>
-      <c r="I3" s="59" t="s">
-        <v>351</v>
-      </c>
-      <c r="J3" s="59" t="s">
-        <v>352</v>
-      </c>
-      <c r="K3" s="59" t="s">
-        <v>353</v>
-      </c>
-      <c r="L3" s="59" t="s">
-        <v>354</v>
-      </c>
-      <c r="M3" s="59" t="s">
-        <v>355</v>
+        <v>327</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="E3" s="57" t="s">
+        <v>330</v>
+      </c>
+      <c r="F3" s="57" t="s">
+        <v>331</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>332</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>333</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>334</v>
+      </c>
+      <c r="J3" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="K3" s="57" t="s">
+        <v>336</v>
+      </c>
+      <c r="L3" s="57" t="s">
+        <v>337</v>
+      </c>
+      <c r="M3" s="57" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="50" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>357</v>
-      </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
+        <v>340</v>
+      </c>
+      <c r="C4" s="58"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="50" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>359</v>
-      </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
+        <v>342</v>
+      </c>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="50" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>361</v>
-      </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
+        <v>344</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="50" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>363</v>
-      </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
+        <v>346</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="50" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
+        <v>348</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="50" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
+        <v>350</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="50" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>357</v>
-      </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="60"/>
+        <v>340</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="58"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -5178,7 +4797,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -5190,26 +4809,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5217,13 +4836,13 @@
         <v>159</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="C5" s="61" t="n">
+        <v>359</v>
+      </c>
+      <c r="C5" s="59" t="n">
         <v>0.0356</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5231,13 +4850,13 @@
         <v>160</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="C6" s="61" t="n">
+        <v>359</v>
+      </c>
+      <c r="C6" s="59" t="n">
         <v>0.0115</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5245,13 +4864,13 @@
         <v>161</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="C7" s="61" t="n">
+        <v>362</v>
+      </c>
+      <c r="C7" s="59" t="n">
         <v>0.0311</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5259,376 +4878,100 @@
         <v>163</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="C8" s="61" t="n">
+        <v>364</v>
+      </c>
+      <c r="C8" s="59" t="n">
         <v>0.05</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C9" s="62" t="n">
+        <v>367</v>
+      </c>
+      <c r="C9" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C10" s="62" t="n">
+        <v>367</v>
+      </c>
+      <c r="C10" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C11" s="62" t="n">
+        <v>367</v>
+      </c>
+      <c r="C11" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C12" s="62" t="n">
+        <v>367</v>
+      </c>
+      <c r="C12" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C13" s="62" t="n">
+        <v>367</v>
+      </c>
+      <c r="C13" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C14" s="62" t="n">
+        <v>367</v>
+      </c>
+      <c r="C14" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>292640</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E19" s="63" t="n">
-        <f aca="false">D19/C19</f>
-        <v>1.70858392564243</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>402</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>266029</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>350000</v>
-      </c>
-      <c r="E20" s="63" t="n">
-        <f aca="false">D20/C20</f>
-        <v>1.31564603858978</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>226122</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E21" s="63" t="n">
-        <f aca="false">D21/C21</f>
-        <v>1.32671743572054</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>172068</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E22" s="63" t="n">
-        <f aca="false">D22/C22</f>
-        <v>1.16233117139735</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>226122</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E23" s="63" t="n">
-        <f aca="false">D23/C23</f>
-        <v>1.10559786310045</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>226122</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>260000</v>
-      </c>
-      <c r="E24" s="63" t="n">
-        <f aca="false">D24/C24</f>
-        <v>1.14982177762447</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>281939</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E25" s="63" t="n">
-        <f aca="false">D25/C25</f>
-        <v>1.06405995623167</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="s">
-        <v>407</v>
-      </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="64" t="s">
-        <v>409</v>
-      </c>
-      <c r="B29" s="65" t="s">
-        <v>410</v>
-      </c>
-      <c r="C29" s="65"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="B30" s="65" t="s">
-        <v>412</v>
-      </c>
-      <c r="C30" s="65"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="B31" s="65" t="s">
-        <v>414</v>
-      </c>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" s="65" t="s">
-        <v>415</v>
-      </c>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="B33" s="65" t="s">
-        <v>417</v>
-      </c>
-      <c r="C33" s="65"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="B34" s="65" t="s">
-        <v>419</v>
-      </c>
-      <c r="C34" s="65"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="64" t="s">
-        <v>420</v>
-      </c>
-      <c r="B35" s="65" t="s">
-        <v>421</v>
-      </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="40" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B29" r:id="rId1" display="https://www.kmcca.or.kr/images/pegs/down_file/2026%EB%85%84%20%EC%83%81%EB%B0%98%EA%B8%B0%EC%A0%81%EC%9A%A9%20%EA%B1%B4%EC%84%A4%EC%97%85%20%EC%9E%84%EA%B8%88%EC%8B%A4%ED%83%9C%EC%A1%B0%EC%82%AC%20%EB%B3%B4%EA%B3%A0%EC%84%9C.pdf"/>
-    <hyperlink ref="B30" r:id="rId2" display="http://www.conslove.co.kr/news/articleView.html?idxno=89479"/>
-    <hyperlink ref="B31" r:id="rId3" display="https://www.kosca21.or.kr/km_board/upload/km_b_notice/1767346180_02.pdf"/>
-    <hyperlink ref="B32" r:id="rId4" display="https://biz.newdaily.co.kr/site/data/html/2026/05/07/2026050700116.html"/>
-    <hyperlink ref="B33" r:id="rId5" display="https://04noti.com/construction-cost-ratio-guide/"/>
-    <hyperlink ref="B34" r:id="rId6" display="https://calctools.co.kr/blog/daily-worker-insurance"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.629861111111111" right="0.629861111111111" top="0.709722222222222" bottom="0.709722222222222" header="0.511811023622047" footer="0.35"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6195,16 +5538,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6236,11 +5578,8 @@
       <c r="F4" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>152</v>
       </c>
@@ -6251,17 +5590,14 @@
         <v>39</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E5" s="41" t="n">
         <f aca="false">도비!G8</f>
         <v>4500000</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6275,17 +5611,14 @@
         <v>42</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E6" s="41" t="n">
         <f aca="false">도비!G9</f>
         <v>520000</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6299,16 +5632,15 @@
         <v>45</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E7" s="41" t="n">
         <f aca="false">도비!G10</f>
         <v>960000</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G7" s="13"/>
+        <v>191</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
@@ -6321,16 +5653,15 @@
         <v>48</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E8" s="41" t="n">
         <f aca="false">도비!G11</f>
         <v>2400000</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G8" s="13"/>
+        <v>194</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
@@ -6343,16 +5674,15 @@
         <v>50</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E9" s="41" t="n">
         <f aca="false">도비!G12</f>
         <v>1700000</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G9" s="13"/>
+        <v>194</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
@@ -6365,16 +5695,15 @@
         <v>52</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E10" s="41" t="n">
         <f aca="false">도비!G13</f>
         <v>640000</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G10" s="13"/>
+        <v>197</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
@@ -6387,16 +5716,15 @@
         <v>55</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E11" s="41" t="n">
         <f aca="false">도비!G14</f>
         <v>2000000</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G11" s="13"/>
+        <v>197</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
@@ -6409,16 +5737,15 @@
         <v>58</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E12" s="41" t="n">
         <f aca="false">도비!G15</f>
         <v>3000000</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="13"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
@@ -6431,16 +5758,15 @@
         <v>60</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E13" s="41" t="n">
         <f aca="false">도비!G16</f>
         <v>1000000</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="G13" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
@@ -6453,16 +5779,15 @@
         <v>62</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E14" s="41" t="n">
         <f aca="false">도비!G17</f>
         <v>1210000</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="G14" s="13"/>
+        <v>203</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
@@ -6475,17 +5800,14 @@
         <v>65</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E15" s="41" t="n">
         <f aca="false">도비!G18</f>
         <v>500000</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6499,16 +5821,15 @@
         <v>68</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E16" s="41" t="n">
         <f aca="false">도비!G19</f>
         <v>520000</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G16" s="13"/>
+        <v>207</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
@@ -6519,16 +5840,15 @@
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E17" s="41" t="n">
         <f aca="false">도비!G20</f>
         <v>380000</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G17" s="13"/>
+        <v>208</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
@@ -6541,16 +5861,15 @@
         <v>72</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E18" s="41" t="n">
         <f aca="false">도비!G21</f>
         <v>600000</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G18" s="13"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20"/>
@@ -6564,14 +5883,13 @@
         <v>4592000</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="20"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20"/>
       <c r="B20" s="42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
@@ -6580,11 +5898,10 @@
         <v>24522000</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="G20" s="20"/>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
         <v>153</v>
       </c>
@@ -6595,20 +5912,17 @@
         <v>81</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E22" s="41" t="n">
         <f aca="false">용접!G8</f>
         <v>4500000</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
         <v>153</v>
       </c>
@@ -6619,17 +5933,14 @@
         <v>84</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E23" s="41" t="n">
         <f aca="false">용접!G9</f>
         <v>2100000</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6650,10 +5961,7 @@
         <v>1200000</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6667,17 +5975,14 @@
         <v>90</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E25" s="41" t="n">
         <f aca="false">용접!G11</f>
         <v>800000</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6691,17 +5996,14 @@
         <v>92</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E26" s="41" t="n">
         <f aca="false">용접!G12</f>
         <v>1250000</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6715,7 +6017,7 @@
         <v>95</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E27" s="41" t="n">
         <f aca="false">용접!G13</f>
@@ -6724,7 +6026,6 @@
       <c r="F27" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="G27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
@@ -6737,18 +6038,17 @@
         <v>98</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E28" s="41" t="n">
         <f aca="false">용접!G14</f>
         <v>800000</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="13"/>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
         <v>153</v>
       </c>
@@ -6759,16 +6059,15 @@
         <v>100</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E29" s="41" t="n">
         <f aca="false">용접!G15</f>
         <v>3680000</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G29" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
@@ -6779,7 +6078,7 @@
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="E30" s="41" t="n">
         <f aca="false">용접!G16</f>
@@ -6788,7 +6087,6 @@
       <c r="F30" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="G30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
@@ -6801,7 +6099,7 @@
         <v>103</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E31" s="41" t="n">
         <f aca="false">용접!G17</f>
@@ -6810,7 +6108,6 @@
       <c r="F31" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="G31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
@@ -6823,16 +6120,15 @@
         <v>105</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E32" s="41" t="n">
         <f aca="false">용접!G18</f>
         <v>1400000</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G32" s="13"/>
+        <v>224</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20"/>
@@ -6846,14 +6142,13 @@
         <v>5191000</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" s="20"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20"/>
       <c r="B34" s="42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
@@ -6862,9 +6157,8 @@
         <v>27721000</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="G34" s="20"/>
+        <v>213</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
@@ -6877,16 +6171,15 @@
         <v>111</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E36" s="41" t="n">
         <f aca="false">베이스!G8</f>
         <v>6993700</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="G36" s="13"/>
+        <v>226</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
@@ -6897,16 +6190,15 @@
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E37" s="41" t="n">
         <f aca="false">베이스!G9</f>
         <v>160000</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="G37" s="13"/>
+        <v>207</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
@@ -6917,16 +6209,15 @@
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E38" s="41" t="n">
         <f aca="false">베이스!G10</f>
         <v>160000</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G38" s="13"/>
+        <v>207</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
@@ -6939,16 +6230,15 @@
         <v>116</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E39" s="41" t="n">
         <f aca="false">베이스!G11</f>
         <v>1000000</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G39" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
@@ -6961,16 +6251,15 @@
         <v>118</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E40" s="41" t="n">
         <f aca="false">베이스!G12</f>
         <v>420000</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G40" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
@@ -6983,17 +6272,14 @@
         <v>121</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E41" s="41" t="n">
         <f aca="false">베이스!G13</f>
         <v>2100000</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7007,17 +6293,14 @@
         <v>122</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E42" s="41" t="n">
         <f aca="false">베이스!G14</f>
         <v>1500000</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7031,17 +6314,14 @@
         <v>123</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E43" s="41" t="n">
         <f aca="false">베이스!G15</f>
         <v>600000</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7055,17 +6335,14 @@
         <v>124</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E44" s="41" t="n">
         <f aca="false">베이스!G16</f>
         <v>750000</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7079,7 +6356,7 @@
         <v>126</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E45" s="41" t="n">
         <f aca="false">베이스!G17</f>
@@ -7088,7 +6365,6 @@
       <c r="F45" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="G45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
@@ -7101,16 +6377,15 @@
         <v>127</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E46" s="41" t="n">
         <f aca="false">베이스!G18</f>
         <v>300000</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="G46" s="13"/>
+        <v>197</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
@@ -7123,16 +6398,15 @@
         <v>95</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E47" s="41" t="n">
         <f aca="false">베이스!G19</f>
         <v>1200000</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="G47" s="13"/>
+        <v>197</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
@@ -7145,16 +6419,15 @@
         <v>105</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E48" s="41" t="n">
         <f aca="false">베이스!G20</f>
         <v>750000</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G48" s="13"/>
+        <v>224</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="20"/>
@@ -7168,14 +6441,13 @@
         <v>2915300</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G49" s="20"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="20"/>
       <c r="B50" s="42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
@@ -7184,37 +6456,33 @@
         <v>19449000</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="G50" s="20"/>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>38</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E52" s="41" t="n">
         <f aca="false">B_도비!G8</f>
         <v>6300000</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B53" s="13" t="s">
         <v>41</v>
@@ -7223,154 +6491,145 @@
         <v>42</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E53" s="41" t="n">
         <f aca="false">B_도비!G9</f>
         <v>1040000</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>44</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E54" s="41" t="n">
         <f aca="false">B_도비!G10</f>
         <v>960000</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G54" s="13"/>
+        <v>191</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E55" s="41" t="n">
         <f aca="false">B_도비!G11</f>
         <v>2400000</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G55" s="13"/>
+        <v>194</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E56" s="41" t="n">
         <f aca="false">B_도비!G12</f>
         <v>1700000</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G56" s="13"/>
+        <v>194</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B57" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E57" s="41" t="n">
         <f aca="false">B_도비!G13</f>
         <v>3500000</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="G57" s="13"/>
+        <v>194</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E58" s="41" t="n">
         <f aca="false">B_도비!G14</f>
         <v>1200000</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G58" s="13"/>
+        <v>197</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E59" s="41" t="n">
         <f aca="false">B_도비!G15</f>
         <v>800000</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G59" s="13"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>51</v>
@@ -7379,20 +6638,19 @@
         <v>52</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E60" s="41" t="n">
         <f aca="false">B_도비!G16</f>
         <v>1280000</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G60" s="13"/>
+        <v>197</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>57</v>
@@ -7401,64 +6659,61 @@
         <v>58</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E61" s="41" t="n">
         <f aca="false">B_도비!G17</f>
         <v>3000000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="G61" s="13"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E62" s="41" t="n">
         <f aca="false">B_도비!G18</f>
         <v>900000</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G62" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B63" s="13" t="s">
         <v>59</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E63" s="41" t="n">
         <f aca="false">B_도비!G19</f>
         <v>1000000</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="G63" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B64" s="13" t="s">
         <v>61</v>
@@ -7467,20 +6722,19 @@
         <v>62</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E64" s="41" t="n">
         <f aca="false">B_도비!G20</f>
         <v>1210000</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="G64" s="13"/>
+        <v>203</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>64</v>
@@ -7489,22 +6743,19 @@
         <v>65</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E65" s="41" t="n">
         <f aca="false">B_도비!G21</f>
         <v>500000</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>67</v>
@@ -7513,40 +6764,38 @@
         <v>68</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E66" s="41" t="n">
         <f aca="false">B_도비!G22</f>
         <v>520000</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G66" s="13"/>
+        <v>207</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C67" s="13"/>
       <c r="D67" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E67" s="41" t="n">
         <f aca="false">B_도비!G23</f>
         <v>380000</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G67" s="13"/>
+        <v>208</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>71</v>
@@ -7555,16 +6804,15 @@
         <v>72</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E68" s="41" t="n">
         <f aca="false">B_도비!G24</f>
         <v>600000</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G68" s="13"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="20"/>
@@ -7578,14 +6826,13 @@
         <v>6237000</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G69" s="20"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="20"/>
       <c r="B70" s="42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
@@ -7594,13 +6841,12 @@
         <v>33527000</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="G70" s="20"/>
-    </row>
-    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B72" s="13" t="s">
         <v>80</v>
@@ -7609,22 +6855,19 @@
         <v>81</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E72" s="41" t="n">
         <f aca="false">B_용접!G8</f>
         <v>4500000</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G72" s="13" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B73" s="13" t="s">
         <v>83</v>
@@ -7633,22 +6876,19 @@
         <v>84</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E73" s="41" t="n">
         <f aca="false">B_용접!G9</f>
         <v>2100000</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B74" s="13" t="s">
         <v>86</v>
@@ -7664,15 +6904,12 @@
         <v>1200000</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="G74" s="13" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B75" s="13" t="s">
         <v>89</v>
@@ -7681,22 +6918,19 @@
         <v>90</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E75" s="41" t="n">
         <f aca="false">B_용접!G11</f>
         <v>800000</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="G75" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B76" s="13" t="s">
         <v>91</v>
@@ -7705,22 +6939,19 @@
         <v>92</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E76" s="41" t="n">
         <f aca="false">B_용접!G12</f>
         <v>1250000</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B77" s="13" t="s">
         <v>94</v>
@@ -7729,7 +6960,7 @@
         <v>95</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E77" s="41" t="n">
         <f aca="false">B_용접!G13</f>
@@ -7738,11 +6969,10 @@
       <c r="F77" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="G77" s="13"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B78" s="13" t="s">
         <v>97</v>
@@ -7751,20 +6981,19 @@
         <v>98</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E78" s="41" t="n">
         <f aca="false">B_용접!G14</f>
         <v>800000</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G78" s="13"/>
-    </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B79" s="13" t="s">
         <v>99</v>
@@ -7773,27 +7002,26 @@
         <v>100</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E79" s="41" t="n">
         <f aca="false">B_용접!G15</f>
         <v>3680000</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G79" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>101</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="13" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="E80" s="41" t="n">
         <f aca="false">B_용접!G16</f>
@@ -7802,11 +7030,10 @@
       <c r="F80" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="G80" s="13"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B81" s="13" t="s">
         <v>102</v>
@@ -7815,7 +7042,7 @@
         <v>103</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E81" s="41" t="n">
         <f aca="false">B_용접!G17</f>
@@ -7824,11 +7051,10 @@
       <c r="F81" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="G81" s="13"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>71</v>
@@ -7837,16 +7063,15 @@
         <v>105</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E82" s="41" t="n">
         <f aca="false">B_용접!G18</f>
         <v>1400000</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G82" s="13"/>
+        <v>224</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="20"/>
@@ -7860,14 +7085,13 @@
         <v>5191000</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G83" s="20"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="20"/>
       <c r="B84" s="42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
@@ -7876,35 +7100,33 @@
         <v>27721000</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="G84" s="20"/>
-    </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E86" s="41" t="n">
         <f aca="false">B_조방!G8</f>
         <v>0</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G86" s="13"/>
+        <v>258</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B87" s="13" t="s">
         <v>99</v>
@@ -7913,162 +7135,145 @@
         <v>116</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E87" s="41" t="n">
         <f aca="false">B_조방!G9</f>
         <v>420000</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G87" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E88" s="41" t="n">
         <f aca="false">B_조방!G10</f>
         <v>380000</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G88" s="13"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B89" s="13" t="s">
         <v>120</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E89" s="41" t="n">
         <f aca="false">B_조방!G11</f>
         <v>700000</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G89" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B90" s="13" t="s">
         <v>80</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E90" s="41" t="n">
         <f aca="false">B_조방!G12</f>
         <v>1000000</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G90" s="13" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B91" s="13" t="s">
         <v>89</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E91" s="41" t="n">
         <f aca="false">B_조방!G13</f>
         <v>400000</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G91" s="13" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B92" s="13" t="s">
         <v>91</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E92" s="41" t="n">
         <f aca="false">B_조방!G14</f>
         <v>250000</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G92" s="13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B93" s="13" t="s">
         <v>120</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E93" s="41" t="n">
         <f aca="false">B_조방!G15</f>
         <v>1400000</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="G93" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B94" s="13" t="s">
         <v>71</v>
@@ -8077,16 +7282,15 @@
         <v>105</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E94" s="41" t="n">
         <f aca="false">B_조방!G16</f>
         <v>550000</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G94" s="13"/>
+        <v>224</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="20"/>
@@ -8100,14 +7304,13 @@
         <v>1322000</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G95" s="20"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="20"/>
       <c r="B96" s="42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
@@ -8116,13 +7319,7 @@
         <v>6422000</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="G96" s="20"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="40" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -8157,7 +7354,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -8181,7 +7378,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -8194,7 +7391,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -8245,7 +7442,7 @@
         <v>39</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>15</v>
@@ -8273,7 +7470,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>2</v>
@@ -8301,7 +7498,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>3</v>
@@ -8322,7 +7519,7 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>47</v>
@@ -8331,7 +7528,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -8359,7 +7556,7 @@
         <v>50</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -8415,7 +7612,7 @@
         <v>55</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -8443,7 +7640,7 @@
         <v>58</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>1</v>
@@ -8490,7 +7687,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>61</v>
@@ -8499,7 +7696,7 @@
         <v>62</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>242</v>
@@ -8527,7 +7724,7 @@
         <v>65</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>2</v>
@@ -8555,7 +7752,7 @@
         <v>68</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>2</v>
@@ -8628,7 +7825,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="45" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B22" s="45"/>
       <c r="C22" s="45"/>
@@ -8644,7 +7841,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="45" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -8660,7 +7857,7 @@
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="45" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B24" s="45"/>
       <c r="C24" s="45"/>
@@ -8688,7 +7885,7 @@
         <v>230688</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I25" s="20"/>
     </row>
@@ -8706,7 +7903,7 @@
         <v>74520</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="I26" s="20"/>
     </row>
@@ -8724,7 +7921,7 @@
         <v>244446</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -8758,7 +7955,7 @@
         <v>1023982.7</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -8776,7 +7973,7 @@
         <v>3018545.505</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -8794,13 +7991,13 @@
         <v>-182.204999998212</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="I31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="47" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B32" s="47"/>
       <c r="C32" s="47"/>
@@ -8812,13 +8009,13 @@
         <v>24522000</v>
       </c>
       <c r="H32" s="38" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="I32" s="38"/>
     </row>
     <row r="34" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B34" s="49"/>
       <c r="C34" s="49"/>
@@ -8831,7 +8028,7 @@
     </row>
     <row r="35" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -8906,7 +8103,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -8930,7 +8127,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -8943,7 +8140,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -8994,7 +8191,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>9</v>
@@ -9022,7 +8219,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>6</v>
@@ -9050,7 +8247,7 @@
         <v>87</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>4</v>
@@ -9078,7 +8275,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>4</v>
@@ -9106,7 +8303,7 @@
         <v>92</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>5</v>
@@ -9127,7 +8324,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>94</v>
@@ -9136,7 +8333,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>9</v>
@@ -9164,7 +8361,7 @@
         <v>98</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -9211,7 +8408,7 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>101</v>
@@ -9244,7 +8441,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>22</v>
@@ -9295,7 +8492,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="45" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B19" s="45"/>
       <c r="C19" s="45"/>
@@ -9311,7 +8508,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B20" s="45"/>
       <c r="C20" s="45"/>
@@ -9327,7 +8524,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="45" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -9355,7 +8552,7 @@
         <v>350660</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I22" s="20"/>
     </row>
@@ -9373,7 +8570,7 @@
         <v>113275</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="I23" s="20"/>
     </row>
@@ -9391,7 +8588,7 @@
         <v>420783</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="I24" s="20"/>
     </row>
@@ -9425,7 +8622,7 @@
         <v>1170735.9</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I26" s="20"/>
     </row>
@@ -9443,7 +8640,7 @@
         <v>3135818.085</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -9461,13 +8658,13 @@
         <v>-271.984999999404</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="47" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B29" s="47"/>
       <c r="C29" s="47"/>
@@ -9479,13 +8676,13 @@
         <v>27721000</v>
       </c>
       <c r="H29" s="38" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="I29" s="38"/>
     </row>
     <row r="31" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B31" s="49"/>
       <c r="C31" s="49"/>
@@ -9498,7 +8695,7 @@
     </row>
     <row r="32" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B32" s="49"/>
       <c r="C32" s="49"/>
@@ -9573,7 +8770,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -9597,7 +8794,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -9610,7 +8807,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -9661,7 +8858,7 @@
         <v>111</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>9991</v>
@@ -9795,7 +8992,7 @@
         <v>121</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>6</v>
@@ -9823,7 +9020,7 @@
         <v>122</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>3</v>
@@ -9851,7 +9048,7 @@
         <v>123</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>3</v>
@@ -9879,7 +9076,7 @@
         <v>124</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>3</v>
@@ -9900,7 +9097,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>125</v>
@@ -9909,7 +9106,7 @@
         <v>126</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>2</v>
@@ -9935,7 +9132,7 @@
         <v>127</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>1</v>
@@ -9961,7 +9158,7 @@
         <v>95</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>3</v>
@@ -10012,7 +9209,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="45" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -10028,7 +9225,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="45" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B22" s="45"/>
       <c r="C22" s="45"/>
@@ -10044,7 +9241,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="45" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -10072,7 +9269,7 @@
         <v>176220</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I24" s="20"/>
     </row>
@@ -10090,7 +9287,7 @@
         <v>56925</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="I25" s="20"/>
     </row>
@@ -10108,7 +9305,7 @@
         <v>425563.07</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="I26" s="20"/>
     </row>
@@ -10142,7 +9339,7 @@
         <v>859620.4035</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I28" s="20"/>
     </row>
@@ -10160,7 +9357,7 @@
         <v>1397749.271025</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -10178,13 +9375,13 @@
         <v>-777.744524996728</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="I30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="47" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B31" s="47"/>
       <c r="C31" s="47"/>
@@ -10196,13 +9393,13 @@
         <v>19449000</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="I31" s="38"/>
     </row>
     <row r="33" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B33" s="49"/>
       <c r="C33" s="49"/>
@@ -10215,7 +9412,7 @@
     </row>
     <row r="34" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B34" s="49"/>
       <c r="C34" s="49"/>
@@ -10290,7 +9487,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -10314,7 +9511,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -10327,7 +9524,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -10375,10 +9572,10 @@
         <v>38</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>21</v>
@@ -10391,7 +9588,7 @@
         <v>6300000</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>158</v>
@@ -10406,7 +9603,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>4</v>
@@ -10419,7 +9616,7 @@
         <v>1040000</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>158</v>
@@ -10431,10 +9628,10 @@
         <v>44</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>3</v>
@@ -10455,16 +9652,16 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -10477,7 +9674,7 @@
         <v>2400000</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>71</v>
@@ -10489,10 +9686,10 @@
         <v>47</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -10505,7 +9702,7 @@
         <v>1700000</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>71</v>
@@ -10517,10 +9714,10 @@
         <v>47</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>1</v>
@@ -10533,7 +9730,7 @@
         <v>3500000</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>71</v>
@@ -10542,10 +9739,10 @@
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>75</v>
@@ -10561,7 +9758,7 @@
         <v>1200000</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>71</v>
@@ -10570,10 +9767,10 @@
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>75</v>
@@ -10589,7 +9786,7 @@
         <v>800000</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>71</v>
@@ -10604,7 +9801,7 @@
         <v>52</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>2</v>
@@ -10617,7 +9814,7 @@
         <v>1280000</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>71</v>
@@ -10632,7 +9829,7 @@
         <v>58</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>1</v>
@@ -10654,10 +9851,10 @@
         <v>157</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>75</v>
@@ -10673,7 +9870,7 @@
         <v>900000</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>157</v>
@@ -10685,7 +9882,7 @@
         <v>59</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>75</v>
@@ -10707,7 +9904,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>61</v>
@@ -10716,7 +9913,7 @@
         <v>62</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>242</v>
@@ -10729,7 +9926,7 @@
         <v>1210000</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>71</v>
@@ -10744,7 +9941,7 @@
         <v>65</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>2</v>
@@ -10770,7 +9967,7 @@
         <v>68</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>2</v>
@@ -10841,7 +10038,7 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -10857,7 +10054,7 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="45" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B26" s="45"/>
       <c r="C26" s="45"/>
@@ -10873,7 +10070,7 @@
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="45" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B27" s="45"/>
       <c r="C27" s="45"/>
@@ -10901,7 +10098,7 @@
         <v>313280</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I28" s="20"/>
     </row>
@@ -10919,7 +10116,7 @@
         <v>101200</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -10937,7 +10134,7 @@
         <v>344588</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -10971,7 +10168,7 @@
         <v>1402453.4</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I32" s="20"/>
     </row>
@@ -10989,7 +10186,7 @@
         <v>4075728.21</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I33" s="20"/>
     </row>
@@ -11007,13 +10204,13 @@
         <v>-249.609999999404</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="I34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="47" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="47"/>
@@ -11025,13 +10222,13 @@
         <v>33527000</v>
       </c>
       <c r="H35" s="38" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="I35" s="38"/>
     </row>
     <row r="37" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B37" s="49"/>
       <c r="C37" s="49"/>
@@ -11044,7 +10241,7 @@
     </row>
     <row r="38" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B38" s="49"/>
       <c r="C38" s="49"/>
@@ -11120,7 +10317,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -11144,7 +10341,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -11157,7 +10354,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -11208,7 +10405,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>9</v>
@@ -11236,7 +10433,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>6</v>
@@ -11264,7 +10461,7 @@
         <v>87</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>4</v>
@@ -11292,7 +10489,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>4</v>
@@ -11320,7 +10517,7 @@
         <v>92</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>5</v>
@@ -11341,7 +10538,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>94</v>
@@ -11350,7 +10547,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>9</v>
@@ -11378,7 +10575,7 @@
         <v>98</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -11425,7 +10622,7 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>101</v>
@@ -11458,7 +10655,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>22</v>
@@ -11509,7 +10706,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="45" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B19" s="45"/>
       <c r="C19" s="45"/>
@@ -11525,7 +10722,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B20" s="45"/>
       <c r="C20" s="45"/>
@@ -11541,7 +10738,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="45" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -11569,7 +10766,7 @@
         <v>350660</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I22" s="20"/>
     </row>
@@ -11587,7 +10784,7 @@
         <v>113275</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="I23" s="20"/>
     </row>
@@ -11605,7 +10802,7 @@
         <v>420783</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="I24" s="20"/>
     </row>
@@ -11639,7 +10836,7 @@
         <v>1170735.9</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I26" s="20"/>
     </row>
@@ -11657,7 +10854,7 @@
         <v>3135818.085</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -11675,13 +10872,13 @@
         <v>-271.984999999404</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="47" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B29" s="47"/>
       <c r="C29" s="47"/>
@@ -11693,13 +10890,13 @@
         <v>27721000</v>
       </c>
       <c r="H29" s="38" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="I29" s="38"/>
     </row>
     <row r="31" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B31" s="49"/>
       <c r="C31" s="49"/>
@@ -11712,7 +10909,7 @@
     </row>
     <row r="32" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B32" s="49"/>
       <c r="C32" s="49"/>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -20,7 +20,6 @@
     <sheet name="B_조방" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="베이스자재" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="공정표" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="요율근거" sheetId="13" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Titles" vbProcedure="false">B_도비!$7:$7</definedName>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="366">
   <si>
     <t xml:space="preserve">N M   S O L U T I O N</t>
   </si>
@@ -548,7 +547,49 @@
     <t xml:space="preserve">총 공사금액</t>
   </si>
   <si>
-    <t xml:space="preserve">요율: 산재 3.56%·고용 1.15% (노무비 기준), 산업안전보건관리비 3.11% ((재료비 + 노무비) 기준), 일반관리비 5% (순공사원가 기준), 이윤 15%. 보험료율은 2026년 고용노동부 고시, 산업안전보건관리비는 고용노동부 계상기준 적용함.</t>
+    <t xml:space="preserve">요율: 산재 3.56%·고용 1.15% (노무비 기준), 산업안전보건관리비 3.11% ((재료비 + 노무비) 기준), 일반관리비 5% (순공사원가 기준), 이윤 15%. 근거는 아래 적용 요율 표.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적용 요율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적용 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">요율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근거</t>
+  </si>
+  <si>
+    <t xml:space="preserve">노무비 ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026년 고용노동부 보험료율 고시 (건설업)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026년 고용노동부 보험료율 고시 (150인 미만)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(재료비 + 노무비) ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고용노동부 산업안전보건관리비 계상기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순공사원가 ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6% 이내 적용 (국가계약법 시행규칙 제8조 기준)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(노무비 + 경비 + 일반관리비) ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15% 이내 적용 (국가계약법 시행규칙 제8조 기준)</t>
   </si>
   <si>
     <t xml:space="preserve">A안 · B안 금액 비교 (공급가액, 부가세 별도)</t>
@@ -603,9 +644,6 @@
   </si>
   <si>
     <t xml:space="preserve">금액(원)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">근거</t>
   </si>
   <si>
     <t xml:space="preserve">(6 + 6 + 3)명 × 300,000원</t>
@@ -1112,69 +1150,6 @@
   </si>
   <si>
     <t xml:space="preserve">가정 일정: 2026-10-21(수) 착공 ~ 11-02(월) 완료, 일요일 휴무 기준 작업일 11일. 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요율 입력값</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요율·단가 칸은 입력값임. 변경 시 모든 공종 시트와 견적서가 다시 계산됨.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">항목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적용 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출처·비고</t>
-  </si>
-  <si>
-    <t xml:space="preserve">노무비 ×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고용노동부 2026년 보험료율 고시 (대한전문건설협회 안내자료): 건설업 3.56% (출퇴근재해 0.06% 포함)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고용노동부 2026년 보험료율 고시 (대한전문건설협회 안내자료): 실업급여 사업주 0.9% + 고용안정·직업능력개발 0.25% (150인 미만)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(재료비 + 노무비) ×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고용노동부 건설업 산업안전보건관리비 계상 및 사용기준 (5억 미만 건축공사 3.11%). 총공사금액 2천만원 이상 의무 계상</t>
-  </si>
-  <si>
-    <t xml:space="preserve">순공사원가 ×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">국가계약법 시행규칙 제8조 (일반관리비 6%·이윤 15% 상한, 민간공사 참고). 6% 이내에서 5% 적용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이윤 (도비)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(노무비 + 경비 + 일반관리비) ×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">국가계약법 시행규칙 제8조 (일반관리비 6%·이윤 15% 상한, 민간공사 참고). 15% 이내</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이윤 (용접)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이윤 (베이스)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이윤 (B_도비)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이윤 (B_용접)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이윤 (B_조방)</t>
   </si>
 </sst>
 </file>
@@ -1185,11 +1160,11 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="General"/>
-    <numFmt numFmtId="168" formatCode="#,##0"/>
-    <numFmt numFmtId="169" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="169" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1311,6 +1286,20 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Pretendard"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1D2430"/>
+      <name val="Pretendard SemiBold"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1D2430"/>
       <name val="Pretendard"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1459,7 +1448,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1608,7 +1597,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1616,7 +1617,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1648,11 +1649,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1664,11 +1665,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1680,28 +1681,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3834,7 +3827,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -3858,7 +3851,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -3870,21 +3863,21 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>308</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
+      <c r="A5" s="47" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -3916,10 +3909,10 @@
         <v>157</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>75</v>
@@ -3935,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>157</v>
@@ -3970,10 +3963,10 @@
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11"/>
       <c r="B10" s="11" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>75</v>
@@ -3989,7 +3982,7 @@
         <v>380000</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>157</v>
@@ -4003,10 +3996,10 @@
         <v>120</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>2</v>
@@ -4019,7 +4012,7 @@
         <v>700000</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>158</v>
@@ -4031,10 +4024,10 @@
         <v>80</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>2</v>
@@ -4047,7 +4040,7 @@
         <v>1000000</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>158</v>
@@ -4059,10 +4052,10 @@
         <v>89</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>2</v>
@@ -4075,7 +4068,7 @@
         <v>400000</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>158</v>
@@ -4087,10 +4080,10 @@
         <v>91</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -4103,7 +4096,7 @@
         <v>250000</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>158</v>
@@ -4115,10 +4108,10 @@
         <v>120</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>4</v>
@@ -4131,7 +4124,7 @@
         <v>1400000</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>158</v>
@@ -4161,22 +4154,22 @@
         <v>550000</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46" t="n">
+      <c r="A17" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$16,"재료비",$G$8:$G$16)</f>
         <v>800000</v>
       </c>
@@ -4184,15 +4177,15 @@
       <c r="I17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="46" t="n">
+      <c r="A18" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$16,"노무비",$G$8:$G$16)</f>
         <v>3750000</v>
       </c>
@@ -4200,15 +4193,15 @@
       <c r="I18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46" t="n">
+      <c r="A19" s="48" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$16,"경비",$G$8:$G$16)</f>
         <v>550000</v>
       </c>
@@ -4216,56 +4209,56 @@
       <c r="I19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46" t="n">
-        <f aca="false">G18*요율근거!$C$5</f>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49" t="n">
+        <f aca="false">G18*원가계산서!$D$24</f>
         <v>133500</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="I20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46" t="n">
-        <f aca="false">G18*요율근거!$C$6</f>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49" t="n">
+        <f aca="false">G18*원가계산서!$D$25</f>
         <v>43125</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46" t="n">
-        <f aca="false">(G17+G18)*요율근거!$C$7</f>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49" t="n">
+        <f aca="false">(G17+G18)*원가계산서!$D$26</f>
         <v>141505</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I22" s="20"/>
     </row>
@@ -4286,102 +4279,102 @@
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46" t="n">
-        <f aca="false">G23*요율근거!$C$8</f>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49" t="n">
+        <f aca="false">G23*원가계산서!$D$27</f>
         <v>270906.5</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="I24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46" t="n">
-        <f aca="false">(G18+G19+G20+G21+G22+G24)*요율근거!$C$14</f>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="49" t="n">
+        <f aca="false">(G18+G19+G20+G21+G22+G24)*원가계산서!$D$28</f>
         <v>733355.475</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46" t="n">
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49" t="n">
         <f aca="false">-MOD(G23+G24+G25,1000)</f>
         <v>-391.974999999627</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="48" t="n">
+      <c r="A27" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="51" t="n">
         <f aca="false">G23+G24+G25+G26</f>
         <v>6422000</v>
       </c>
-      <c r="H27" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="I27" s="38"/>
+      <c r="H27" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="I27" s="41"/>
     </row>
     <row r="29" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
+      <c r="A29" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
     </row>
     <row r="30" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
+      <c r="A30" s="52" t="s">
+        <v>305</v>
+      </c>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -4439,111 +4432,111 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>315</v>
+      <c r="A1" s="42" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="50" t="n">
+      <c r="A4" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="B4" s="50" t="n">
+      <c r="B4" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="51" t="n">
+      <c r="C4" s="54" t="n">
         <f aca="false">A4*B4</f>
         <v>40</v>
       </c>
-      <c r="D4" s="50" t="n">
+      <c r="D4" s="53" t="n">
         <v>72.4</v>
       </c>
-      <c r="E4" s="52" t="n">
+      <c r="E4" s="55" t="n">
         <f aca="false">C4*D4</f>
         <v>2896</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="n">
+      <c r="A5" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="50" t="n">
+      <c r="B5" s="53" t="n">
         <v>16</v>
       </c>
-      <c r="C5" s="51" t="n">
+      <c r="C5" s="54" t="n">
         <f aca="false">A5*B5</f>
         <v>80</v>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="53" t="n">
         <v>72.4</v>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="55" t="n">
         <f aca="false">C5*D5</f>
         <v>5792</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="50" t="n">
+      <c r="A6" s="53" t="n">
         <v>0.6</v>
       </c>
-      <c r="B6" s="50" t="n">
+      <c r="B6" s="53" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="51" t="n">
+      <c r="C6" s="54" t="n">
         <f aca="false">A6*B6</f>
         <v>18</v>
       </c>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="53" t="n">
         <v>72.4</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="55" t="n">
         <f aca="false">C6*D6</f>
         <v>1303.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54" t="s">
+      <c r="A7" s="56"/>
+      <c r="B7" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="C7" s="53" t="n">
+      <c r="C7" s="56" t="n">
         <f aca="false">SUM(C4:C6)</f>
         <v>138</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="55" t="n">
+      <c r="D7" s="56"/>
+      <c r="E7" s="58" t="n">
         <f aca="false">SUM(E4:E6)</f>
         <v>9991.2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>36</v>
@@ -4551,9 +4544,9 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="B10" s="56" t="n">
+        <v>335</v>
+      </c>
+      <c r="B10" s="59" t="n">
         <f aca="false">E7</f>
         <v>9991.2</v>
       </c>
@@ -4565,12 +4558,12 @@
         <v>6993840</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="s">
-        <v>324</v>
+      <c r="A12" s="43" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4598,377 +4591,187 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>325</v>
+      <c r="A1" s="42" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>328</v>
-      </c>
-      <c r="D3" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>330</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>331</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>332</v>
-      </c>
-      <c r="H3" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>334</v>
-      </c>
-      <c r="J3" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K3" s="57" t="s">
-        <v>336</v>
-      </c>
-      <c r="L3" s="57" t="s">
-        <v>337</v>
-      </c>
-      <c r="M3" s="57" t="s">
-        <v>338</v>
+        <v>340</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>342</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>343</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>345</v>
+      </c>
+      <c r="H3" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I3" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="J3" s="60" t="s">
+        <v>348</v>
+      </c>
+      <c r="K3" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="L3" s="60" t="s">
+        <v>350</v>
+      </c>
+      <c r="M3" s="60" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="50" t="s">
-        <v>339</v>
-      </c>
-      <c r="B4" s="50" t="s">
-        <v>340</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
+      <c r="A4" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>342</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
+      <c r="A5" s="53" t="s">
+        <v>354</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="50" t="s">
-        <v>343</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>344</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
+      <c r="A6" s="53" t="s">
+        <v>356</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="50" t="s">
-        <v>345</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>346</v>
-      </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
+      <c r="A7" s="53" t="s">
+        <v>358</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>359</v>
+      </c>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="50" t="s">
-        <v>347</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>348</v>
-      </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
+      <c r="A8" s="53" t="s">
+        <v>360</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>361</v>
+      </c>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50" t="s">
-        <v>349</v>
-      </c>
-      <c r="B9" s="50" t="s">
-        <v>350</v>
-      </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
+      <c r="A9" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>363</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>340</v>
-      </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="58"/>
+      <c r="A10" s="53" t="s">
+        <v>364</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>353</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="61"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="s">
-        <v>352</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.629861111111111" right="0.629861111111111" top="0.709722222222222" bottom="0.709722222222222" header="0.511811023622047" footer="0.35"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;"Pretendard,Regular"&amp;8 엔엠솔루션  |  경기도 평택시 고덕동 도시지원로 121 지식공장아이타워 906호  |  대표전화 1800-5901  |  직통 010-2369-3691  |  nm-solution.co.kr&amp;R&amp;"Pretendard,Regular"&amp;8 &amp;P / &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="40" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="C5" s="59" t="n">
-        <v>0.0356</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="C6" s="59" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="C7" s="59" t="n">
-        <v>0.0311</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="C8" s="59" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D8" s="13" t="s">
+      <c r="A12" s="43" t="s">
         <v>365</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="60" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C10" s="60" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C11" s="60" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C12" s="60" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C13" s="60" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C14" s="60" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -4987,7 +4790,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -5355,11 +5158,124 @@
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="37" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="38" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="F24" s="39"/>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="38" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="E25" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="38" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="F26" s="39"/>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="F27" s="39"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="F28" s="39"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="15">
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E28:F28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.629861111111111" right="0.629861111111111" top="0.709722222222222" bottom="0.709722222222222" header="0.511811023622047" footer="0.35"/>
@@ -5386,26 +5302,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
+      <c r="A1" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>36</v>
@@ -5428,7 +5344,7 @@
         <v>9005000</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5448,12 +5364,12 @@
         <v>0</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">베이스!$G$31</f>
@@ -5468,12 +5384,12 @@
         <v>-13027000</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
-        <v>178</v>
+      <c r="A7" s="41" t="s">
+        <v>192</v>
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">SUM(B4:B6)</f>
@@ -5487,11 +5403,11 @@
         <f aca="false">SUM(D4:D6)</f>
         <v>-4022000</v>
       </c>
-      <c r="E7" s="38"/>
+      <c r="E7" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
@@ -5500,7 +5416,7 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B10" s="36"/>
       <c r="C10" s="36"/>
@@ -5509,7 +5425,7 @@
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
@@ -5550,18 +5466,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>182</v>
+      <c r="A1" s="42" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="40" t="s">
-        <v>183</v>
+      <c r="A2" s="43" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>30</v>
@@ -5570,13 +5486,13 @@
         <v>31</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5590,14 +5506,14 @@
         <v>39</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="41" t="n">
+        <v>201</v>
+      </c>
+      <c r="E5" s="44" t="n">
         <f aca="false">도비!G8</f>
         <v>4500000</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5611,14 +5527,14 @@
         <v>42</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="41" t="n">
+        <v>203</v>
+      </c>
+      <c r="E6" s="44" t="n">
         <f aca="false">도비!G9</f>
         <v>520000</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5632,14 +5548,14 @@
         <v>45</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" s="41" t="n">
+        <v>205</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <f aca="false">도비!G10</f>
         <v>960000</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5653,14 +5569,14 @@
         <v>48</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="41" t="n">
+        <v>206</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <f aca="false">도비!G11</f>
         <v>2400000</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5674,14 +5590,14 @@
         <v>50</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="41" t="n">
+        <v>208</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <f aca="false">도비!G12</f>
         <v>1700000</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5695,14 +5611,14 @@
         <v>52</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="41" t="n">
+        <v>209</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <f aca="false">도비!G13</f>
         <v>640000</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5716,14 +5632,14 @@
         <v>55</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" s="41" t="n">
+        <v>211</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <f aca="false">도비!G14</f>
         <v>2000000</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5737,14 +5653,14 @@
         <v>58</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E12" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <f aca="false">도비!G15</f>
         <v>3000000</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5758,14 +5674,14 @@
         <v>60</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E13" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <f aca="false">도비!G16</f>
         <v>1000000</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5779,14 +5695,14 @@
         <v>62</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" s="41" t="n">
+        <v>215</v>
+      </c>
+      <c r="E14" s="44" t="n">
         <f aca="false">도비!G17</f>
         <v>1210000</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5800,14 +5716,14 @@
         <v>65</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="E15" s="41" t="n">
+        <v>217</v>
+      </c>
+      <c r="E15" s="44" t="n">
         <f aca="false">도비!G18</f>
         <v>500000</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5821,14 +5737,14 @@
         <v>68</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="E16" s="41" t="n">
+        <v>219</v>
+      </c>
+      <c r="E16" s="44" t="n">
         <f aca="false">도비!G19</f>
         <v>520000</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5840,14 +5756,14 @@
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E17" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E17" s="44" t="n">
         <f aca="false">도비!G20</f>
         <v>380000</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5861,44 +5777,44 @@
         <v>72</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E18" s="41" t="n">
+        <v>222</v>
+      </c>
+      <c r="E18" s="44" t="n">
         <f aca="false">도비!G21</f>
         <v>600000</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20"/>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="45" t="s">
         <v>73</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="43" t="n">
+      <c r="E19" s="46" t="n">
         <f aca="false">도비!$G$32-SUM(도비!$G$22:$G$24)</f>
         <v>4592000</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20"/>
-      <c r="B20" s="42" t="s">
-        <v>212</v>
+      <c r="B20" s="45" t="s">
+        <v>225</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
-      <c r="E20" s="43" t="n">
+      <c r="E20" s="46" t="n">
         <f aca="false">도비!$G$32</f>
         <v>24522000</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5912,14 +5828,14 @@
         <v>81</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="E22" s="41" t="n">
+        <v>227</v>
+      </c>
+      <c r="E22" s="44" t="n">
         <f aca="false">용접!G8</f>
         <v>4500000</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5933,14 +5849,14 @@
         <v>84</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E23" s="41" t="n">
+        <v>228</v>
+      </c>
+      <c r="E23" s="44" t="n">
         <f aca="false">용접!G9</f>
         <v>2100000</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5954,14 +5870,14 @@
         <v>87</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="E24" s="41" t="n">
+        <v>229</v>
+      </c>
+      <c r="E24" s="44" t="n">
         <f aca="false">용접!G10</f>
         <v>1200000</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5975,14 +5891,14 @@
         <v>90</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="E25" s="41" t="n">
+        <v>230</v>
+      </c>
+      <c r="E25" s="44" t="n">
         <f aca="false">용접!G11</f>
         <v>800000</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5996,14 +5912,14 @@
         <v>92</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="E26" s="41" t="n">
+        <v>231</v>
+      </c>
+      <c r="E26" s="44" t="n">
         <f aca="false">용접!G12</f>
         <v>1250000</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6017,14 +5933,14 @@
         <v>95</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E27" s="41" t="n">
+        <v>233</v>
+      </c>
+      <c r="E27" s="44" t="n">
         <f aca="false">용접!G13</f>
         <v>3600000</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6038,14 +5954,14 @@
         <v>98</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E28" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E28" s="44" t="n">
         <f aca="false">용접!G14</f>
         <v>800000</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6059,14 +5975,14 @@
         <v>100</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="E29" s="41" t="n">
+        <v>234</v>
+      </c>
+      <c r="E29" s="44" t="n">
         <f aca="false">용접!G15</f>
         <v>3680000</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6078,14 +5994,14 @@
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E30" s="44" t="n">
         <f aca="false">용접!G16</f>
         <v>1000000</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6099,14 +6015,14 @@
         <v>103</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="E31" s="41" t="n">
+        <v>235</v>
+      </c>
+      <c r="E31" s="44" t="n">
         <f aca="false">용접!G17</f>
         <v>2200000</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6120,44 +6036,44 @@
         <v>105</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E32" s="41" t="n">
+        <v>236</v>
+      </c>
+      <c r="E32" s="44" t="n">
         <f aca="false">용접!G18</f>
         <v>1400000</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20"/>
-      <c r="B33" s="42" t="s">
+      <c r="B33" s="45" t="s">
         <v>73</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="20"/>
-      <c r="E33" s="43" t="n">
+      <c r="E33" s="46" t="n">
         <f aca="false">용접!$G$29-SUM(용접!$G$19:$G$21)</f>
         <v>5191000</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20"/>
-      <c r="B34" s="42" t="s">
-        <v>212</v>
+      <c r="B34" s="45" t="s">
+        <v>225</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
-      <c r="E34" s="43" t="n">
+      <c r="E34" s="46" t="n">
         <f aca="false">용접!$G$29</f>
         <v>27721000</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6171,14 +6087,14 @@
         <v>111</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="E36" s="41" t="n">
+        <v>238</v>
+      </c>
+      <c r="E36" s="44" t="n">
         <f aca="false">베이스!G8</f>
         <v>6993700</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6190,14 +6106,14 @@
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E37" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E37" s="44" t="n">
         <f aca="false">베이스!G9</f>
         <v>160000</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6209,14 +6125,14 @@
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E38" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E38" s="44" t="n">
         <f aca="false">베이스!G10</f>
         <v>160000</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6230,14 +6146,14 @@
         <v>116</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E39" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E39" s="44" t="n">
         <f aca="false">베이스!G11</f>
         <v>1000000</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6251,14 +6167,14 @@
         <v>118</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E40" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E40" s="44" t="n">
         <f aca="false">베이스!G12</f>
         <v>420000</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6272,14 +6188,14 @@
         <v>121</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E41" s="41" t="n">
+        <v>228</v>
+      </c>
+      <c r="E41" s="44" t="n">
         <f aca="false">베이스!G13</f>
         <v>2100000</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6293,14 +6209,14 @@
         <v>122</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="E42" s="41" t="n">
+        <v>240</v>
+      </c>
+      <c r="E42" s="44" t="n">
         <f aca="false">베이스!G14</f>
         <v>1500000</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6314,14 +6230,14 @@
         <v>123</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E43" s="41" t="n">
+        <v>241</v>
+      </c>
+      <c r="E43" s="44" t="n">
         <f aca="false">베이스!G15</f>
         <v>600000</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6335,14 +6251,14 @@
         <v>124</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="E44" s="41" t="n">
+        <v>242</v>
+      </c>
+      <c r="E44" s="44" t="n">
         <f aca="false">베이스!G16</f>
         <v>750000</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6356,14 +6272,14 @@
         <v>126</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="E45" s="41" t="n">
+        <v>243</v>
+      </c>
+      <c r="E45" s="44" t="n">
         <f aca="false">베이스!G17</f>
         <v>600000</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6377,14 +6293,14 @@
         <v>127</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="E46" s="41" t="n">
+        <v>244</v>
+      </c>
+      <c r="E46" s="44" t="n">
         <f aca="false">베이스!G18</f>
         <v>300000</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6398,14 +6314,14 @@
         <v>95</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="E47" s="41" t="n">
+        <v>245</v>
+      </c>
+      <c r="E47" s="44" t="n">
         <f aca="false">베이스!G19</f>
         <v>1200000</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6419,70 +6335,70 @@
         <v>105</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E48" s="41" t="n">
+        <v>246</v>
+      </c>
+      <c r="E48" s="44" t="n">
         <f aca="false">베이스!G20</f>
         <v>750000</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="20"/>
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="45" t="s">
         <v>73</v>
       </c>
       <c r="C49" s="20"/>
       <c r="D49" s="20"/>
-      <c r="E49" s="43" t="n">
+      <c r="E49" s="46" t="n">
         <f aca="false">베이스!$G$31-SUM(베이스!$G$21:$G$23)</f>
         <v>2915300</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="20"/>
-      <c r="B50" s="42" t="s">
-        <v>212</v>
+      <c r="B50" s="45" t="s">
+        <v>225</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
-      <c r="E50" s="43" t="n">
+      <c r="E50" s="46" t="n">
         <f aca="false">베이스!$G$31</f>
         <v>19449000</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>38</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="E52" s="41" t="n">
+        <v>249</v>
+      </c>
+      <c r="E52" s="44" t="n">
         <f aca="false">B_도비!G8</f>
         <v>6300000</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B53" s="13" t="s">
         <v>41</v>
@@ -6491,145 +6407,145 @@
         <v>42</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="E53" s="41" t="n">
+        <v>250</v>
+      </c>
+      <c r="E53" s="44" t="n">
         <f aca="false">B_도비!G9</f>
         <v>1040000</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>44</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E54" s="41" t="n">
+        <v>205</v>
+      </c>
+      <c r="E54" s="44" t="n">
         <f aca="false">B_도비!G10</f>
         <v>960000</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E55" s="41" t="n">
+        <v>206</v>
+      </c>
+      <c r="E55" s="44" t="n">
         <f aca="false">B_도비!G11</f>
         <v>2400000</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E56" s="41" t="n">
+        <v>208</v>
+      </c>
+      <c r="E56" s="44" t="n">
         <f aca="false">B_도비!G12</f>
         <v>1700000</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B57" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="E57" s="41" t="n">
+        <v>255</v>
+      </c>
+      <c r="E57" s="44" t="n">
         <f aca="false">B_도비!G13</f>
         <v>3500000</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E58" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E58" s="44" t="n">
         <f aca="false">B_도비!G14</f>
         <v>1200000</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E59" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E59" s="44" t="n">
         <f aca="false">B_도비!G15</f>
         <v>800000</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>51</v>
@@ -6638,19 +6554,19 @@
         <v>52</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="E60" s="41" t="n">
+        <v>260</v>
+      </c>
+      <c r="E60" s="44" t="n">
         <f aca="false">B_도비!G16</f>
         <v>1280000</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>57</v>
@@ -6659,61 +6575,61 @@
         <v>58</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E61" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E61" s="44" t="n">
         <f aca="false">B_도비!G17</f>
         <v>3000000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E62" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E62" s="44" t="n">
         <f aca="false">B_도비!G18</f>
         <v>900000</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B63" s="13" t="s">
         <v>59</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E63" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E63" s="44" t="n">
         <f aca="false">B_도비!G19</f>
         <v>1000000</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B64" s="13" t="s">
         <v>61</v>
@@ -6722,19 +6638,19 @@
         <v>62</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="E64" s="41" t="n">
+        <v>264</v>
+      </c>
+      <c r="E64" s="44" t="n">
         <f aca="false">B_도비!G20</f>
         <v>1210000</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>64</v>
@@ -6743,19 +6659,19 @@
         <v>65</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="E65" s="41" t="n">
+        <v>217</v>
+      </c>
+      <c r="E65" s="44" t="n">
         <f aca="false">B_도비!G21</f>
         <v>500000</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>67</v>
@@ -6764,38 +6680,38 @@
         <v>68</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="E66" s="41" t="n">
+        <v>219</v>
+      </c>
+      <c r="E66" s="44" t="n">
         <f aca="false">B_도비!G22</f>
         <v>520000</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C67" s="13"/>
       <c r="D67" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E67" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E67" s="44" t="n">
         <f aca="false">B_도비!G23</f>
         <v>380000</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>71</v>
@@ -6804,49 +6720,49 @@
         <v>72</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E68" s="41" t="n">
+        <v>222</v>
+      </c>
+      <c r="E68" s="44" t="n">
         <f aca="false">B_도비!G24</f>
         <v>600000</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="20"/>
-      <c r="B69" s="42" t="s">
+      <c r="B69" s="45" t="s">
         <v>73</v>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
-      <c r="E69" s="43" t="n">
+      <c r="E69" s="46" t="n">
         <f aca="false">B_도비!$G$35-SUM(B_도비!$G$25:$G$27)</f>
         <v>6237000</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="20"/>
-      <c r="B70" s="42" t="s">
-        <v>212</v>
+      <c r="B70" s="45" t="s">
+        <v>225</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
-      <c r="E70" s="43" t="n">
+      <c r="E70" s="46" t="n">
         <f aca="false">B_도비!$G$35</f>
         <v>33527000</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B72" s="13" t="s">
         <v>80</v>
@@ -6855,19 +6771,19 @@
         <v>81</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="E72" s="41" t="n">
+        <v>227</v>
+      </c>
+      <c r="E72" s="44" t="n">
         <f aca="false">B_용접!G8</f>
         <v>4500000</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B73" s="13" t="s">
         <v>83</v>
@@ -6876,19 +6792,19 @@
         <v>84</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E73" s="41" t="n">
+        <v>228</v>
+      </c>
+      <c r="E73" s="44" t="n">
         <f aca="false">B_용접!G9</f>
         <v>2100000</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B74" s="13" t="s">
         <v>86</v>
@@ -6897,19 +6813,19 @@
         <v>87</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="E74" s="41" t="n">
+        <v>229</v>
+      </c>
+      <c r="E74" s="44" t="n">
         <f aca="false">B_용접!G10</f>
         <v>1200000</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B75" s="13" t="s">
         <v>89</v>
@@ -6918,19 +6834,19 @@
         <v>90</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="E75" s="41" t="n">
+        <v>230</v>
+      </c>
+      <c r="E75" s="44" t="n">
         <f aca="false">B_용접!G11</f>
         <v>800000</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B76" s="13" t="s">
         <v>91</v>
@@ -6939,19 +6855,19 @@
         <v>92</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="E76" s="41" t="n">
+        <v>231</v>
+      </c>
+      <c r="E76" s="44" t="n">
         <f aca="false">B_용접!G12</f>
         <v>1250000</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B77" s="13" t="s">
         <v>94</v>
@@ -6960,19 +6876,19 @@
         <v>95</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E77" s="41" t="n">
+        <v>233</v>
+      </c>
+      <c r="E77" s="44" t="n">
         <f aca="false">B_용접!G13</f>
         <v>3600000</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B78" s="13" t="s">
         <v>97</v>
@@ -6981,19 +6897,19 @@
         <v>98</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E78" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E78" s="44" t="n">
         <f aca="false">B_용접!G14</f>
         <v>800000</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B79" s="13" t="s">
         <v>99</v>
@@ -7002,38 +6918,38 @@
         <v>100</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="E79" s="41" t="n">
+        <v>234</v>
+      </c>
+      <c r="E79" s="44" t="n">
         <f aca="false">B_용접!G15</f>
         <v>3680000</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>101</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E80" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E80" s="44" t="n">
         <f aca="false">B_용접!G16</f>
         <v>1000000</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B81" s="13" t="s">
         <v>102</v>
@@ -7042,19 +6958,19 @@
         <v>103</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="E81" s="41" t="n">
+        <v>235</v>
+      </c>
+      <c r="E81" s="44" t="n">
         <f aca="false">B_용접!G17</f>
         <v>2200000</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="13" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>71</v>
@@ -7063,70 +6979,70 @@
         <v>105</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E82" s="41" t="n">
+        <v>236</v>
+      </c>
+      <c r="E82" s="44" t="n">
         <f aca="false">B_용접!G18</f>
         <v>1400000</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="20"/>
-      <c r="B83" s="42" t="s">
+      <c r="B83" s="45" t="s">
         <v>73</v>
       </c>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
-      <c r="E83" s="43" t="n">
+      <c r="E83" s="46" t="n">
         <f aca="false">B_용접!$G$29-SUM(B_용접!$G$19:$G$21)</f>
         <v>5191000</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="20"/>
-      <c r="B84" s="42" t="s">
-        <v>212</v>
+      <c r="B84" s="45" t="s">
+        <v>225</v>
       </c>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
-      <c r="E84" s="43" t="n">
+      <c r="E84" s="46" t="n">
         <f aca="false">B_용접!$G$29</f>
         <v>27721000</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E86" s="41" t="n">
+        <v>270</v>
+      </c>
+      <c r="E86" s="44" t="n">
         <f aca="false">B_조방!G8</f>
         <v>0</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B87" s="13" t="s">
         <v>99</v>
@@ -7135,145 +7051,145 @@
         <v>116</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E87" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E87" s="44" t="n">
         <f aca="false">B_조방!G9</f>
         <v>420000</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E88" s="41" t="n">
+        <v>212</v>
+      </c>
+      <c r="E88" s="44" t="n">
         <f aca="false">B_조방!G10</f>
         <v>380000</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B89" s="13" t="s">
         <v>120</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="E89" s="41" t="n">
+        <v>275</v>
+      </c>
+      <c r="E89" s="44" t="n">
         <f aca="false">B_조방!G11</f>
         <v>700000</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B90" s="13" t="s">
         <v>80</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="E90" s="41" t="n">
+        <v>277</v>
+      </c>
+      <c r="E90" s="44" t="n">
         <f aca="false">B_조방!G12</f>
         <v>1000000</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B91" s="13" t="s">
         <v>89</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="E91" s="41" t="n">
+        <v>279</v>
+      </c>
+      <c r="E91" s="44" t="n">
         <f aca="false">B_조방!G13</f>
         <v>400000</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B92" s="13" t="s">
         <v>91</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="E92" s="41" t="n">
+        <v>281</v>
+      </c>
+      <c r="E92" s="44" t="n">
         <f aca="false">B_조방!G14</f>
         <v>250000</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B93" s="13" t="s">
         <v>120</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="E93" s="41" t="n">
+        <v>283</v>
+      </c>
+      <c r="E93" s="44" t="n">
         <f aca="false">B_조방!G15</f>
         <v>1400000</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="13" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B94" s="13" t="s">
         <v>71</v>
@@ -7282,44 +7198,44 @@
         <v>105</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="E94" s="41" t="n">
+        <v>284</v>
+      </c>
+      <c r="E94" s="44" t="n">
         <f aca="false">B_조방!G16</f>
         <v>550000</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="20"/>
-      <c r="B95" s="42" t="s">
+      <c r="B95" s="45" t="s">
         <v>73</v>
       </c>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
-      <c r="E95" s="43" t="n">
+      <c r="E95" s="46" t="n">
         <f aca="false">B_조방!$G$27-SUM(B_조방!$G$17:$G$19)</f>
         <v>1322000</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="20"/>
-      <c r="B96" s="42" t="s">
-        <v>212</v>
+      <c r="B96" s="45" t="s">
+        <v>225</v>
       </c>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
-      <c r="E96" s="43" t="n">
+      <c r="E96" s="46" t="n">
         <f aca="false">B_조방!$G$27</f>
         <v>6422000</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -7354,7 +7270,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -7378,7 +7294,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -7390,21 +7306,21 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>274</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
+      <c r="A5" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -7442,7 +7358,7 @@
         <v>39</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>15</v>
@@ -7470,7 +7386,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>2</v>
@@ -7498,7 +7414,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>3</v>
@@ -7519,7 +7435,7 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>47</v>
@@ -7528,7 +7444,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -7556,7 +7472,7 @@
         <v>50</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -7612,7 +7528,7 @@
         <v>55</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -7640,7 +7556,7 @@
         <v>58</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>1</v>
@@ -7687,7 +7603,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>61</v>
@@ -7696,7 +7612,7 @@
         <v>62</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>242</v>
@@ -7724,7 +7640,7 @@
         <v>65</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>2</v>
@@ -7752,7 +7668,7 @@
         <v>68</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>2</v>
@@ -7824,15 +7740,15 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46" t="n">
+      <c r="A22" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$21,"재료비",$G$8:$G$21)</f>
         <v>1380000</v>
       </c>
@@ -7840,15 +7756,15 @@
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46" t="n">
+      <c r="A23" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$21,"노무비",$G$8:$G$21)</f>
         <v>6480000</v>
       </c>
@@ -7856,15 +7772,15 @@
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46" t="n">
+      <c r="A24" s="48" t="s">
+        <v>297</v>
+      </c>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$21,"경비",$G$8:$G$21)</f>
         <v>12070000</v>
       </c>
@@ -7872,56 +7788,56 @@
       <c r="I24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46" t="n">
-        <f aca="false">G23*요율근거!$C$5</f>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="49" t="n">
+        <f aca="false">G23*원가계산서!$D$24</f>
         <v>230688</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46" t="n">
-        <f aca="false">G23*요율근거!$C$6</f>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49" t="n">
+        <f aca="false">G23*원가계산서!$D$25</f>
         <v>74520</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46" t="n">
-        <f aca="false">(G22+G23)*요율근거!$C$7</f>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49" t="n">
+        <f aca="false">(G22+G23)*원가계산서!$D$26</f>
         <v>244446</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -7942,102 +7858,102 @@
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46" t="n">
-        <f aca="false">G28*요율근거!$C$8</f>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="49" t="n">
+        <f aca="false">G28*원가계산서!$D$27</f>
         <v>1023982.7</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46" t="n">
-        <f aca="false">(G23+G24+G25+G26+G27+G29)*요율근거!$C$9</f>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="49" t="n">
+        <f aca="false">(G23+G24+G25+G26+G27+G29)*원가계산서!$D$28</f>
         <v>3018545.505</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="I30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="46" t="n">
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="49" t="n">
         <f aca="false">-MOD(G28+G29+G30,1000)</f>
         <v>-182.204999998212</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="48" t="n">
+      <c r="A32" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="51" t="n">
         <f aca="false">G28+G29+G30+G31</f>
         <v>24522000</v>
       </c>
-      <c r="H32" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="I32" s="38"/>
+      <c r="H32" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="I32" s="41"/>
     </row>
     <row r="34" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
+      <c r="A34" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
     </row>
     <row r="35" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
+      <c r="A35" s="52" t="s">
+        <v>305</v>
+      </c>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -8103,7 +8019,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -8127,7 +8043,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -8139,21 +8055,21 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
+      <c r="A5" s="47" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -8191,7 +8107,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>9</v>
@@ -8219,7 +8135,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>6</v>
@@ -8247,7 +8163,7 @@
         <v>87</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>4</v>
@@ -8275,7 +8191,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>4</v>
@@ -8303,7 +8219,7 @@
         <v>92</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>5</v>
@@ -8324,7 +8240,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>94</v>
@@ -8333,7 +8249,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>9</v>
@@ -8361,7 +8277,7 @@
         <v>98</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -8408,7 +8324,7 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>101</v>
@@ -8441,7 +8357,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>22</v>
@@ -8491,15 +8407,15 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46" t="n">
+      <c r="A19" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"재료비",$G$8:$G$18)</f>
         <v>3680000</v>
       </c>
@@ -8507,15 +8423,15 @@
       <c r="I19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46" t="n">
+      <c r="A20" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"노무비",$G$8:$G$18)</f>
         <v>9850000</v>
       </c>
@@ -8523,15 +8439,15 @@
       <c r="I20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46" t="n">
+      <c r="A21" s="48" t="s">
+        <v>297</v>
+      </c>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"경비",$G$8:$G$18)</f>
         <v>9000000</v>
       </c>
@@ -8539,56 +8455,56 @@
       <c r="I21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46" t="n">
-        <f aca="false">G20*요율근거!$C$5</f>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49" t="n">
+        <f aca="false">G20*원가계산서!$D$24</f>
         <v>350660</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46" t="n">
-        <f aca="false">G20*요율근거!$C$6</f>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49" t="n">
+        <f aca="false">G20*원가계산서!$D$25</f>
         <v>113275</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46" t="n">
-        <f aca="false">(G19+G20)*요율근거!$C$7</f>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49" t="n">
+        <f aca="false">(G19+G20)*원가계산서!$D$26</f>
         <v>420783</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I24" s="20"/>
     </row>
@@ -8609,102 +8525,102 @@
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46" t="n">
-        <f aca="false">G25*요율근거!$C$8</f>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49" t="n">
+        <f aca="false">G25*원가계산서!$D$27</f>
         <v>1170735.9</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46" t="n">
-        <f aca="false">(G20+G21+G22+G23+G24+G26)*요율근거!$C$10</f>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49" t="n">
+        <f aca="false">(G20+G21+G22+G23+G24+G26)*원가계산서!$D$28</f>
         <v>3135818.085</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46" t="n">
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49" t="n">
         <f aca="false">-MOD(G25+G26+G27,1000)</f>
         <v>-271.984999999404</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="48" t="n">
+      <c r="A29" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="51" t="n">
         <f aca="false">G25+G26+G27+G28</f>
         <v>27721000</v>
       </c>
-      <c r="H29" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="I29" s="38"/>
+      <c r="H29" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="I29" s="41"/>
     </row>
     <row r="31" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
+      <c r="A31" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
     </row>
     <row r="32" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
+      <c r="A32" s="52" t="s">
+        <v>305</v>
+      </c>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -8770,7 +8686,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -8794,7 +8710,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -8806,21 +8722,21 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>294</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
+      <c r="A5" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -8858,7 +8774,7 @@
         <v>111</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>9991</v>
@@ -8992,7 +8908,7 @@
         <v>121</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>6</v>
@@ -9020,7 +8936,7 @@
         <v>122</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>3</v>
@@ -9048,7 +8964,7 @@
         <v>123</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>3</v>
@@ -9076,7 +8992,7 @@
         <v>124</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>3</v>
@@ -9097,7 +9013,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>125</v>
@@ -9106,7 +9022,7 @@
         <v>126</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>2</v>
@@ -9132,7 +9048,7 @@
         <v>127</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>1</v>
@@ -9158,7 +9074,7 @@
         <v>95</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>3</v>
@@ -9208,15 +9124,15 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46" t="n">
+      <c r="A21" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$20,"재료비",$G$8:$G$20)</f>
         <v>8733700</v>
       </c>
@@ -9224,15 +9140,15 @@
       <c r="I21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46" t="n">
+      <c r="A22" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$20,"노무비",$G$8:$G$20)</f>
         <v>4950000</v>
       </c>
@@ -9240,15 +9156,15 @@
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46" t="n">
+      <c r="A23" s="48" t="s">
+        <v>297</v>
+      </c>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$20,"경비",$G$8:$G$20)</f>
         <v>2850000</v>
       </c>
@@ -9256,56 +9172,56 @@
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46" t="n">
-        <f aca="false">G22*요율근거!$C$5</f>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49" t="n">
+        <f aca="false">G22*원가계산서!$D$24</f>
         <v>176220</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="I24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46" t="n">
-        <f aca="false">G22*요율근거!$C$6</f>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="49" t="n">
+        <f aca="false">G22*원가계산서!$D$25</f>
         <v>56925</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46" t="n">
-        <f aca="false">(G21+G22)*요율근거!$C$7</f>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49" t="n">
+        <f aca="false">(G21+G22)*원가계산서!$D$26</f>
         <v>425563.07</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I26" s="20"/>
     </row>
@@ -9326,102 +9242,102 @@
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46" t="n">
-        <f aca="false">G27*요율근거!$C$8</f>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49" t="n">
+        <f aca="false">G27*원가계산서!$D$27</f>
         <v>859620.4035</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46" t="n">
-        <f aca="false">(G22+G23+G24+G25+G26+G28)*요율근거!$C$11</f>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="49" t="n">
+        <f aca="false">(G22+G23+G24+G25+G26+G28)*원가계산서!$D$28</f>
         <v>1397749.271025</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46" t="n">
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="49" t="n">
         <f aca="false">-MOD(G27+G28+G29,1000)</f>
         <v>-777.744524996728</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="48" t="n">
+      <c r="A31" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="51" t="n">
         <f aca="false">G27+G28+G29+G30</f>
         <v>19449000</v>
       </c>
-      <c r="H31" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="I31" s="38"/>
+      <c r="H31" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="I31" s="41"/>
     </row>
     <row r="33" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="B33" s="49"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
+      <c r="A33" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
     </row>
     <row r="34" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
+      <c r="A34" s="52" t="s">
+        <v>305</v>
+      </c>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9487,7 +9403,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -9511,7 +9427,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -9523,21 +9439,21 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>297</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
+      <c r="A5" s="47" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -9572,10 +9488,10 @@
         <v>38</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>21</v>
@@ -9588,7 +9504,7 @@
         <v>6300000</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>158</v>
@@ -9603,7 +9519,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>4</v>
@@ -9616,7 +9532,7 @@
         <v>1040000</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>158</v>
@@ -9628,10 +9544,10 @@
         <v>44</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>3</v>
@@ -9652,16 +9568,16 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -9674,7 +9590,7 @@
         <v>2400000</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>71</v>
@@ -9686,10 +9602,10 @@
         <v>47</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -9702,7 +9618,7 @@
         <v>1700000</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>71</v>
@@ -9714,10 +9630,10 @@
         <v>47</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>1</v>
@@ -9730,7 +9646,7 @@
         <v>3500000</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>71</v>
@@ -9739,10 +9655,10 @@
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>75</v>
@@ -9758,7 +9674,7 @@
         <v>1200000</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>71</v>
@@ -9767,10 +9683,10 @@
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>75</v>
@@ -9786,7 +9702,7 @@
         <v>800000</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>71</v>
@@ -9801,7 +9717,7 @@
         <v>52</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>2</v>
@@ -9814,7 +9730,7 @@
         <v>1280000</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>71</v>
@@ -9829,7 +9745,7 @@
         <v>58</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>1</v>
@@ -9851,10 +9767,10 @@
         <v>157</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>75</v>
@@ -9870,7 +9786,7 @@
         <v>900000</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>157</v>
@@ -9882,7 +9798,7 @@
         <v>59</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>75</v>
@@ -9904,7 +9820,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>61</v>
@@ -9913,7 +9829,7 @@
         <v>62</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>242</v>
@@ -9926,7 +9842,7 @@
         <v>1210000</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>71</v>
@@ -9941,7 +9857,7 @@
         <v>65</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>2</v>
@@ -9967,7 +9883,7 @@
         <v>68</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>2</v>
@@ -10037,15 +9953,15 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46" t="n">
+      <c r="A25" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$24,"재료비",$G$8:$G$24)</f>
         <v>2280000</v>
       </c>
@@ -10053,15 +9969,15 @@
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46" t="n">
+      <c r="A26" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$24,"노무비",$G$8:$G$24)</f>
         <v>8800000</v>
       </c>
@@ -10069,15 +9985,15 @@
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46" t="n">
+      <c r="A27" s="48" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$24,"경비",$G$8:$G$24)</f>
         <v>16210000</v>
       </c>
@@ -10085,56 +10001,56 @@
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46" t="n">
-        <f aca="false">G26*요율근거!$C$5</f>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49" t="n">
+        <f aca="false">G26*원가계산서!$D$24</f>
         <v>313280</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46" t="n">
-        <f aca="false">G26*요율근거!$C$6</f>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="49" t="n">
+        <f aca="false">G26*원가계산서!$D$25</f>
         <v>101200</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46" t="n">
-        <f aca="false">(G25+G26)*요율근거!$C$7</f>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="49" t="n">
+        <f aca="false">(G25+G26)*원가계산서!$D$26</f>
         <v>344588</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -10155,102 +10071,102 @@
       <c r="I31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="46" t="n">
-        <f aca="false">G31*요율근거!$C$8</f>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="49" t="n">
+        <f aca="false">G31*원가계산서!$D$27</f>
         <v>1402453.4</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="I32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="46" t="n">
-        <f aca="false">(G26+G27+G28+G29+G30+G32)*요율근거!$C$12</f>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="49" t="n">
+        <f aca="false">(G26+G27+G28+G29+G30+G32)*원가계산서!$D$28</f>
         <v>4075728.21</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="I33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="46" t="n">
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="49" t="n">
         <f aca="false">-MOD(G31+G32+G33,1000)</f>
         <v>-249.609999999404</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="48" t="n">
+      <c r="A35" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="51" t="n">
         <f aca="false">G31+G32+G33+G34</f>
         <v>33527000</v>
       </c>
-      <c r="H35" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="I35" s="38"/>
+      <c r="H35" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="I35" s="41"/>
     </row>
     <row r="37" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="B37" s="49"/>
-      <c r="C37" s="49"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
+      <c r="A37" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
     </row>
     <row r="38" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="49"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
+      <c r="A38" s="52" t="s">
+        <v>305</v>
+      </c>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -10317,7 +10233,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -10341,7 +10257,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -10353,21 +10269,21 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
+      <c r="A5" s="47" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -10405,7 +10321,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>9</v>
@@ -10433,7 +10349,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>6</v>
@@ -10461,7 +10377,7 @@
         <v>87</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>4</v>
@@ -10489,7 +10405,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>4</v>
@@ -10517,7 +10433,7 @@
         <v>92</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>5</v>
@@ -10538,7 +10454,7 @@
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>94</v>
@@ -10547,7 +10463,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>9</v>
@@ -10575,7 +10491,7 @@
         <v>98</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -10622,7 +10538,7 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>101</v>
@@ -10655,7 +10571,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>22</v>
@@ -10705,15 +10621,15 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46" t="n">
+      <c r="A19" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"재료비",$G$8:$G$18)</f>
         <v>3680000</v>
       </c>
@@ -10721,15 +10637,15 @@
       <c r="I19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46" t="n">
+      <c r="A20" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"노무비",$G$8:$G$18)</f>
         <v>9850000</v>
       </c>
@@ -10737,15 +10653,15 @@
       <c r="I20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46" t="n">
+      <c r="A21" s="48" t="s">
+        <v>297</v>
+      </c>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"경비",$G$8:$G$18)</f>
         <v>9000000</v>
       </c>
@@ -10753,56 +10669,56 @@
       <c r="I21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46" t="n">
-        <f aca="false">G20*요율근거!$C$5</f>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49" t="n">
+        <f aca="false">G20*원가계산서!$D$24</f>
         <v>350660</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46" t="n">
-        <f aca="false">G20*요율근거!$C$6</f>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49" t="n">
+        <f aca="false">G20*원가계산서!$D$25</f>
         <v>113275</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46" t="n">
-        <f aca="false">(G19+G20)*요율근거!$C$7</f>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49" t="n">
+        <f aca="false">(G19+G20)*원가계산서!$D$26</f>
         <v>420783</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I24" s="20"/>
     </row>
@@ -10823,102 +10739,102 @@
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46" t="n">
-        <f aca="false">G25*요율근거!$C$8</f>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49" t="n">
+        <f aca="false">G25*원가계산서!$D$27</f>
         <v>1170735.9</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46" t="n">
-        <f aca="false">(G20+G21+G22+G23+G24+G26)*요율근거!$C$13</f>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49" t="n">
+        <f aca="false">(G20+G21+G22+G23+G24+G26)*원가계산서!$D$28</f>
         <v>3135818.085</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46" t="n">
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49" t="n">
         <f aca="false">-MOD(G25+G26+G27,1000)</f>
         <v>-271.984999999404</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="48" t="n">
+      <c r="A29" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="51" t="n">
         <f aca="false">G25+G26+G27+G28</f>
         <v>27721000</v>
       </c>
-      <c r="H29" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="I29" s="38"/>
+      <c r="H29" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="I29" s="41"/>
     </row>
     <row r="31" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
+      <c r="A31" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
     </row>
     <row r="32" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
+      <c r="A32" s="52" t="s">
+        <v>305</v>
+      </c>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="30">

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="348">
   <si>
     <t xml:space="preserve">N M   S O L U T I O N</t>
   </si>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">사업자등록번호</t>
   </si>
   <si>
-    <t xml:space="preserve">견적금액  일금 칠천일백육십구만이천원정  (₩ 71,692,000, VAT 별도)</t>
+    <t xml:space="preserve">견적금액  일금 오천오백이십오만삼천원정  (₩ 55,253,000, VAT 별도)</t>
   </si>
   <si>
     <t xml:space="preserve">견적 내역</t>
@@ -382,489 +382,444 @@
     <t xml:space="preserve">공사 후 회수 조건</t>
   </si>
   <si>
-    <t xml:space="preserve">H빔 반입 운임</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회수 반출 운임</t>
-  </si>
-  <si>
-    <t xml:space="preserve">반입 운임과 같게 적용</t>
+    <t xml:space="preserve">H빔 운반</t>
+  </si>
+  <si>
+    <t xml:space="preserve">반입·회수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시공자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">베이스 제작·설치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3명 × 1일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">베이스 소계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">베이스 시트 참조</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공급가액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가세 (10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">합계 (VAT 포함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특기사항</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 공사 기간: 2026.10.21 ~ 2026.11.02 (가정 일정, 작업일 11일, 공정표 시트 참조). 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. 결제 조건: 선수금 30% (계약 시), 중도금 30% (회전·안착 완료 시), 잔금 40% (용접 완료 후). A안 VAT 포함 기준 18,233,490원 / 18,233,490원 / 24,311,320원.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. 견적 유효기간: 발행일로부터 30일.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. 포함: 임시 베이스 제작·설치·회수, 이동식 크레인(100t·60t)·도비, 접합면 사상, CO2 용접, 화재감시, 안전펜스·출입통제.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. 제외: 전기 수전, 배관·닥트 해체·복구, 보온, 도장, 비파괴검사(PT/UT), 시운전. 비파괴검사는 발주처 요구 시 별도 정산함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. 크레인 사양·배치는 크레인 업체와 협의해 확정하며, 크레인 변경에 따른 추가비용은 없음.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. 연장·야간·휴일 작업은 공정에 따라 당사가 수행하며 추가 정산하지 않음. 기상(우천 시 용접 불가)·발주처 사유에 따른 대기는 별도 협의함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. 작업구역(약 10×15m)은 이동식 안전펜스로 통제하며, 발주처 안전관리 규정과 출입 절차를 따름.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. 대안(B안: 기존 조방 개조 + 전체 90° 회전)의 금액은 AB비교 시트에 정리함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위와 같이 견적합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026년 10월 13일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엔엠솔루션   대표 김성배   (인)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엔엠솔루션  |  경기도 평택시 고덕동 도시지원로 121 지식공장아이타워 906호  |  대표전화 1800-5901  |  직통 010-2369-3691  |  nm-solution.co.kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공 사 원 가 계 산 서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공사명 : 진공건조로 회전·안착 및 접합부 용접 공사   |   NM-2610-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">용접</t>
+  </si>
+  <si>
+    <t xml:space="preserve">베이스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">합계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구성비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">재료비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">노무비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산재보험료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고용보험료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산업안전보건관리비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순공사원가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일반관리비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이윤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단수정리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가가치세 (10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">총 공사금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">요율: 산재 3.56%·고용 1.15% (노무비 기준), 산업안전보건관리비 3.11% ((재료비 + 노무비) 기준), 일반관리비 5% (순공사원가 기준), 이윤 15%. 근거는 아래 적용 요율 표. 베이스 공종은 회수조건 임시 구조물로 재료비·운반비·노무비만 계상함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적용 요율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적용 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">요율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근거</t>
+  </si>
+  <si>
+    <t xml:space="preserve">노무비 ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026년 고용노동부 보험료율 고시 (건설업)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026년 고용노동부 보험료율 고시 (150인 미만)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(재료비 + 노무비) ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고용노동부 산업안전보건관리비 계상기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순공사원가 ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6% 이내 적용 (국가계약법 시행규칙 제8조 기준)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(노무비 + 경비 + 일반관리비) ×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15% 이내 적용 (국가계약법 시행규칙 제8조 기준)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A안 · B안 금액 비교 (공급가액, 부가세 별도)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A안 (임시 베이스 + 밀착 이동)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B안 (조방 개조 + 90° 회전)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">차액 (B − A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B안: 200t급 크레인 1대 1일 추가(단독 90° 회전), 도비 6명 1일 추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">같은 인원·장비로 상부·측면 용접 후 회전해서 하부 용접</t>
+  </si>
+  <si>
+    <t xml:space="preserve">베이스 / 조방</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B안: 신규 베이스 대신 조방 개조(현장 보강보), 기구물·배관 제거·복원 2명 × 2일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공급가액 계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ B안 200t급 크레인은 1일 임대 단가 적용, 회송·웨이트 운반은 별도 항목으로 계상함. B안 용접은 3면 용접 → 전체 90° 회전 → 나머지 1면 용접 순서로, 용접 1일이 회전 후로 이동함(금액 동일).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ B안 회전은 일체 약 86t(38t + 48t)을 모서리 기준으로 세우는 작업으로, 실제 크레인 사양은 인양계획서·구조검토로 확정 필요함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 회전 후 원래 자세로 되돌리는 회전이나 영구 받침이 필요하면 별도임.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">견적 산출근거</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금액은 공종 시트에서 연동됨. 인원·일수는 작업 범위와 공정표 기준, 단가는 동종 플랜트 현장 시장 단가 기준으로 산정함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산출식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금액(원)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6 + 6 + 3)명 × 300,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인원·일수: 작업 범위·공정표 기준 / 단가: 중량물 도비 전문기공 시장 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2명 × 1일 × 260,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">크레인 인양 작업 안전관리 인력, 단가: 시장 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1명 × 3일 × 320,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1대 × 1일 × 2,400,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이동식 크레인 1일 임대 시장 단가 (운전원 포함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1대 × 1일 × 1,700,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8매 × 80,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장비 임대 시장 단가, 투입 수량·일수는 공정표 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1식 (2일)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">중량물 작업 전문장비 사용 손료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자재 시장 단가, 작업 범위 기준 1식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업구역 10×15m, 둘레 50m ÷ 2.4m = 21매 + 출입문 1매 → 22매 × 11일 × 5,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업구역 둘레 기준 수량 × 임대 시장 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2명 × 1일 × 250,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인원·일수: 작업 범위·공정표 기준 / 단가: 플랜트 숙련 기능인력 시장 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2회 × 260,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화물 운반 시장 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업구역 출입통제 자재, 1식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1식 600,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공종 현장 부대비 1식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">법정 요율·일반관리비·이윤 (원가계산서 하단 참조)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공종 합계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가세 별도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3명 × 3일 × 500,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2명 × 3일 × 350,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2명 × 2일 × 300,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2명 × 2일 × 200,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1명 × 5일 × 250,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산업안전보건기준에 관한 규칙 제241조의2 (화기작업 화재감시자 배치), 단가는 숙련 기능인력 시장 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3대 × 3일 × 400,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1식 (용접재 3,000,000 + 전원 케이블·잡자재 680,000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2대 × 11일 × 100,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28인·일 기준 1식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">투입 인·일 기준 현장 부대비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1식 (9,991kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H빔 9,991kg (베이스자재 시트), 공사 후 회수 조건 1식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화물 운반 시장 단가 (반입·회수)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3명 × 1일 × 350,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B_도비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안착·밀착·90° 회전·회전 후 정리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6 + 6 + 3 + 6)명 × 300,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2명 × 2일 × 260,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인양구역 통제</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100TON (안착)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60TON (안착)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200TON급 (90° 회전 주 크레인)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1대 × 1일 × 3,500,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200TON 회송·웨이트 운반</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카운터웨이트 트레일러 왕복</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회전용 대형 줄걸이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100t급 샤클·슬링·스프레더 손료</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2회 × 640,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회전 착지 깔목·고무판</t>
+  </si>
+  <si>
+    <t xml:space="preserve">목재 받침 300×300, 고무판</t>
+  </si>
+  <si>
+    <t xml:space="preserve">와이어 보호대 등</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A안과 같음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B안 (대안), 부가세 별도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B_용접</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B_조방</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보강보</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-200급, 약 25m (현장 보유 강재 사용)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현장 보유 강재 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현장 보유 강재 사용, 자재비 미계상</t>
   </si>
   <si>
     <t xml:space="preserve">용접봉·가스·디스크</t>
   </si>
   <si>
-    <t xml:space="preserve">레벨 조정재</t>
-  </si>
-  <si>
-    <t xml:space="preserve">라이너·심 플레이트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">베이스 수평 ±2mm</t>
+    <t xml:space="preserve">배관 복구 자재</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가스켓·볼트·너트</t>
   </si>
   <si>
     <t xml:space="preserve">제관사</t>
   </si>
   <si>
-    <t xml:space="preserve">절단·취부</t>
-  </si>
-  <si>
-    <t xml:space="preserve">베이스 조립 용접</t>
-  </si>
-  <si>
-    <t xml:space="preserve">자재 정리·보조</t>
-  </si>
-  <si>
-    <t xml:space="preserve">용접·절단 화기작업 전담</t>
-  </si>
-  <si>
-    <t xml:space="preserve">지게차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">자재 하역·조립</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회수 시 해체·상차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1대 × 3일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제관 6 + 용접 3 + 조공 3 + 화재감시 3 (가스절단기는 용접 공종에 계상)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">베이스 소계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">베이스 시트 참조</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공급가액</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부가세 (10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">합계 (VAT 포함)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">특기사항</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 공사 기간: 2026.10.21 ~ 2026.11.02 (가정 일정, 작업일 11일, 공정표 시트 참조). 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. 결제 조건: 선수금 30% (계약 시), 중도금 30% (회전·안착 완료 시), 잔금 40% (용접 완료 후). A안 VAT 포함 기준 23,658,360원 / 23,658,360원 / 31,544,480원.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. 견적 유효기간: 발행일로부터 30일.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. 포함: 임시 베이스 제작·설치·회수, 이동식 크레인(100t·60t)·도비, 접합면 사상, CO2 용접, 화재감시, 안전펜스·출입통제.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. 제외: 전기 수전, 배관·닥트 해체·복구, 보온, 도장, 비파괴검사(PT/UT), 시운전. 비파괴검사는 발주처 요구 시 별도 정산함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. 크레인 사양·배치는 크레인 업체와 협의해 확정하며, 크레인 변경에 따른 추가비용은 없음.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. 연장·야간·휴일 작업은 공정에 따라 당사가 수행하며 추가 정산하지 않음. 기상(우천 시 용접 불가)·발주처 사유에 따른 대기는 별도 협의함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. 작업구역(약 10×15m)은 이동식 안전펜스로 통제하며, 발주처 안전관리 규정과 출입 절차를 따름.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. 대안(B안: 기존 조방 개조 + 전체 90° 회전)의 금액은 AB비교 시트에 정리함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">위와 같이 견적합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026년 10월 13일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엔엠솔루션   대표 김성배   (인)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엔엠솔루션  |  경기도 평택시 고덕동 도시지원로 121 지식공장아이타워 906호  |  대표전화 1800-5901  |  직통 010-2369-3691  |  nm-solution.co.kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공 사 원 가 계 산 서</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공사명 : 진공건조로 회전·안착 및 접합부 용접 공사   |   NM-2610-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">비목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">용접</t>
-  </si>
-  <si>
-    <t xml:space="preserve">베이스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">합계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구성비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">재료비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">노무비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산재보험료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고용보험료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산업안전보건관리비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">순공사원가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">일반관리비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이윤</t>
-  </si>
-  <si>
-    <t xml:space="preserve">단수정리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부가가치세 (10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">총 공사금액</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요율: 산재 3.56%·고용 1.15% (노무비 기준), 산업안전보건관리비 3.11% ((재료비 + 노무비) 기준), 일반관리비 5% (순공사원가 기준), 이윤 15%. 근거는 아래 적용 요율 표.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적용 요율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">항목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적용 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">근거</t>
-  </si>
-  <si>
-    <t xml:space="preserve">노무비 ×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026년 고용노동부 보험료율 고시 (건설업)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026년 고용노동부 보험료율 고시 (150인 미만)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(재료비 + 노무비) ×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고용노동부 산업안전보건관리비 계상기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">순공사원가 ×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6% 이내 적용 (국가계약법 시행규칙 제8조 기준)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(노무비 + 경비 + 일반관리비) ×</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15% 이내 적용 (국가계약법 시행규칙 제8조 기준)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A안 · B안 금액 비교 (공급가액, 부가세 별도)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구분</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A안 (임시 베이스 + 밀착 이동)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B안 (조방 개조 + 90° 회전)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">차액 (B − A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B안: 200t급 크레인 1대 1일 추가(단독 90° 회전), 도비 6명 1일 추가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">같은 인원·장비로 상부·측면 용접 후 회전해서 하부 용접</t>
-  </si>
-  <si>
-    <t xml:space="preserve">베이스 / 조방</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B안: 신규 베이스 대신 조방 개조(현장 보강보), 기구물·배관 제거·복원 2명 × 2일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공급가액 계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ B안 200t급 크레인은 1일 임대 단가 적용, 회송·웨이트 운반은 별도 항목으로 계상함. B안 용접은 3면 용접 → 전체 90° 회전 → 나머지 1면 용접 순서로, 용접 1일이 회전 후로 이동함(금액 동일).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ B안 회전은 일체 약 86t(38t + 48t)을 모서리 기준으로 세우는 작업으로, 실제 크레인 사양은 인양계획서·구조검토로 확정 필요함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 회전 후 원래 자세로 되돌리는 회전이나 영구 받침이 필요하면 별도임.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">견적 산출근거</t>
-  </si>
-  <si>
-    <t xml:space="preserve">금액은 공종 시트에서 연동됨. 인원·일수는 작업 범위와 공정표 기준, 단가는 동종 플랜트 현장 시장 단가 기준으로 산정함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공종</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산출식</t>
-  </si>
-  <si>
-    <t xml:space="preserve">금액(원)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6 + 6 + 3)명 × 300,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인원·일수: 작업 범위·공정표 기준 / 단가: 중량물 도비 전문기공 시장 단가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2명 × 1일 × 260,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">크레인 인양 작업 안전관리 인력, 단가: 시장 단가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1명 × 3일 × 320,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1대 × 1일 × 2,400,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이동식 크레인 1일 임대 시장 단가 (운전원 포함)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1대 × 1일 × 1,700,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8매 × 80,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">장비 임대 시장 단가, 투입 수량·일수는 공정표 기준</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1식 (2일)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1식</t>
-  </si>
-  <si>
-    <t xml:space="preserve">중량물 작업 전문장비 사용 손료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">자재 시장 단가, 작업 범위 기준 1식</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업구역 10×15m, 둘레 50m ÷ 2.4m = 21매 + 출입문 1매 → 22매 × 11일 × 5,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업구역 둘레 기준 수량 × 임대 시장 단가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2명 × 1일 × 250,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인원·일수: 작업 범위·공정표 기준 / 단가: 플랜트 숙련 기능인력 시장 단가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2회 × 260,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화물 운반 시장 단가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작업구역 출입통제 자재, 1식</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1식 600,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공종 현장 부대비 1식</t>
-  </si>
-  <si>
-    <t xml:space="preserve">법정 요율·일반관리비·이윤 (원가계산서 하단 참조)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공종 합계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부가세 별도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3명 × 3일 × 500,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2명 × 3일 × 350,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2명 × 2일 × 300,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2명 × 2일 × 200,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1명 × 5일 × 250,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산업안전보건기준에 관한 규칙 제241조의2 (화기작업 화재감시자 배치), 단가는 숙련 기능인력 시장 단가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3대 × 3일 × 400,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1식 (용접재 3,000,000 + 전원 케이블·잡자재 680,000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2대 × 11일 × 100,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28인·일 기준 1식</t>
-  </si>
-  <si>
-    <t xml:space="preserve">투입 인·일 기준 현장 부대비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,991kg × 700원 (회수조건 적용 단가, 베이스자재 시트)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H빔 공칭중량 × 회수조건 적용 단가 (베이스자재 시트)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1명 × 3일 × 500,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1명 × 3일 × 200,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1명 × 3일 × 250,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2일 × 300,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1일 × 300,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1대 × 3일 × 400,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15인·일 기준 1식</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B_도비</t>
-  </si>
-  <si>
-    <t xml:space="preserve">안착·밀착·90° 회전·회전 후 정리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6 + 6 + 3 + 6)명 × 300,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2명 × 2일 × 260,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">인양구역 통제</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100TON (안착)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60TON (안착)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200TON급 (90° 회전 주 크레인)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1대 × 1일 × 3,500,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200TON 회송·웨이트 운반</t>
-  </si>
-  <si>
-    <t xml:space="preserve">카운터웨이트 트레일러 왕복</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회전용 대형 줄걸이</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100t급 샤클·슬링·스프레더 손료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2회 × 640,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회전 착지 깔목·고무판</t>
-  </si>
-  <si>
-    <t xml:space="preserve">목재 받침 300×300, 고무판</t>
-  </si>
-  <si>
-    <t xml:space="preserve">와이어 보호대 등</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A안과 같음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B안 (대안), 부가세 별도</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B_용접</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B_조방</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보강보</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-200급, 약 25m (현장 보유 강재 사용)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현장 보유 강재 사용</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현장 보유 강재 사용, 자재비 미계상</t>
-  </si>
-  <si>
-    <t xml:space="preserve">배관 복구 자재</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가스켓·볼트·너트</t>
-  </si>
-  <si>
     <t xml:space="preserve">조방 보강보 취부</t>
   </si>
   <si>
@@ -967,10 +922,10 @@
     <t xml:space="preserve">공 종 : 사다리형 일체 임시 베이스 제작·설치 및 공사 후 회수, H-250×250</t>
   </si>
   <si>
-    <t xml:space="preserve">kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">일</t>
+    <t xml:space="preserve">운반비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미적용</t>
   </si>
   <si>
     <t xml:space="preserve">공 종 : B안: 조방 안착(100t·60t) + 전체 90° 회전(200t 단독), 안전펜스</t>
@@ -1043,12 +998,6 @@
   </si>
   <si>
     <t xml:space="preserve">중량(kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적용 단가(원/kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회수조건 적용</t>
   </si>
   <si>
     <t xml:space="preserve">공사 후 회수, 사용 기간 손료 개념</t>
@@ -1116,10 +1065,7 @@
     <t xml:space="preserve">조공 2명</t>
   </si>
   <si>
-    <t xml:space="preserve">베이스 제작·설치</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제관 2, 용접 1, 조공 1, 화재감시 1</t>
+    <t xml:space="preserve">시공자 3명</t>
   </si>
   <si>
     <t xml:space="preserve">회전·베이스 안착 (100t + 60t)</t>
@@ -1448,7 +1394,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1686,6 +1632,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1949,7 +1899,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -1990,12 +1940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
@@ -3061,19 +3006,19 @@
       </c>
       <c r="E49" s="14" t="n">
         <f aca="false">베이스!E8</f>
-        <v>9991</v>
+        <v>1</v>
       </c>
       <c r="F49" s="11" t="str">
         <f aca="false">베이스!D8</f>
-        <v>kg</v>
+        <v>식</v>
       </c>
       <c r="G49" s="14" t="n">
         <f aca="false">베이스!F8</f>
-        <v>700</v>
+        <v>1800000</v>
       </c>
       <c r="H49" s="14" t="n">
         <f aca="false">베이스!G8</f>
-        <v>6993700</v>
+        <v>1800000</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>112</v>
@@ -3087,7 +3032,9 @@
         <v>113</v>
       </c>
       <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
+      <c r="D50" s="13" t="s">
+        <v>114</v>
+      </c>
       <c r="E50" s="14" t="n">
         <f aca="false">베이스!E9</f>
         <v>1</v>
@@ -3111,607 +3058,276 @@
         <v>30</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
+      <c r="D51" s="13" t="s">
+        <v>116</v>
+      </c>
       <c r="E51" s="14" t="n">
         <f aca="false">베이스!E10</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" s="11" t="str">
         <f aca="false">베이스!D10</f>
-        <v>식</v>
+        <v>인·일</v>
       </c>
       <c r="G51" s="14" t="n">
         <f aca="false">베이스!F10</f>
-        <v>160000</v>
+        <v>350000</v>
       </c>
       <c r="H51" s="14" t="n">
         <f aca="false">베이스!G10</f>
-        <v>160000</v>
+        <v>1050000</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E52" s="14" t="n">
-        <f aca="false">베이스!E11</f>
-        <v>1</v>
-      </c>
-      <c r="F52" s="11" t="str">
-        <f aca="false">베이스!D11</f>
-        <v>식</v>
-      </c>
-      <c r="G52" s="14" t="n">
-        <f aca="false">베이스!F11</f>
-        <v>1000000</v>
-      </c>
-      <c r="H52" s="14" t="n">
-        <f aca="false">베이스!G11</f>
-        <v>1000000</v>
-      </c>
-      <c r="I52" s="13"/>
+      <c r="A52" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="16" t="n">
+        <f aca="false">베이스!$G$21</f>
+        <v>3010000</v>
+      </c>
+      <c r="I52" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <f aca="false">베이스!E12</f>
-        <v>1</v>
-      </c>
-      <c r="F53" s="11" t="str">
-        <f aca="false">베이스!D12</f>
-        <v>식</v>
-      </c>
-      <c r="G53" s="14" t="n">
-        <f aca="false">베이스!F12</f>
-        <v>420000</v>
-      </c>
-      <c r="H53" s="14" t="n">
-        <f aca="false">베이스!G12</f>
-        <v>420000</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>119</v>
-      </c>
+      <c r="A53" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="19" t="n">
+        <f aca="false">H33+H47+H52</f>
+        <v>55253000</v>
+      </c>
+      <c r="I53" s="20"/>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13" t="s">
+      <c r="A54" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E54" s="14" t="n">
-        <f aca="false">베이스!E13</f>
-        <v>6</v>
-      </c>
-      <c r="F54" s="11" t="str">
-        <f aca="false">베이스!D13</f>
-        <v>인·일</v>
-      </c>
-      <c r="G54" s="14" t="n">
-        <f aca="false">베이스!F13</f>
-        <v>350000</v>
-      </c>
-      <c r="H54" s="14" t="n">
-        <f aca="false">베이스!G13</f>
-        <v>2100000</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13" t="s">
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="19" t="n">
+        <f aca="false">H53*0.1</f>
+        <v>5525300</v>
+      </c>
+      <c r="I54" s="20"/>
+    </row>
+    <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E55" s="14" t="n">
-        <f aca="false">베이스!E14</f>
-        <v>3</v>
-      </c>
-      <c r="F55" s="11" t="str">
-        <f aca="false">베이스!D14</f>
-        <v>인·일</v>
-      </c>
-      <c r="G55" s="14" t="n">
-        <f aca="false">베이스!F14</f>
-        <v>500000</v>
-      </c>
-      <c r="H55" s="14" t="n">
-        <f aca="false">베이스!G14</f>
-        <v>1500000</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13" t="s">
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="22" t="n">
+        <f aca="false">H53+H54</f>
+        <v>60778300</v>
+      </c>
+      <c r="I55" s="23"/>
+    </row>
+    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E56" s="14" t="n">
-        <f aca="false">베이스!E15</f>
-        <v>3</v>
-      </c>
-      <c r="F56" s="11" t="str">
-        <f aca="false">베이스!D15</f>
-        <v>인·일</v>
-      </c>
-      <c r="G56" s="14" t="n">
-        <f aca="false">베이스!F15</f>
-        <v>200000</v>
-      </c>
-      <c r="H56" s="14" t="n">
-        <f aca="false">베이스!G15</f>
-        <v>600000</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E57" s="14" t="n">
-        <f aca="false">베이스!E16</f>
-        <v>3</v>
-      </c>
-      <c r="F57" s="11" t="str">
-        <f aca="false">베이스!D16</f>
-        <v>인·일</v>
-      </c>
-      <c r="G57" s="14" t="n">
-        <f aca="false">베이스!F16</f>
-        <v>250000</v>
-      </c>
-      <c r="H57" s="14" t="n">
-        <f aca="false">베이스!G16</f>
-        <v>750000</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+    </row>
+    <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13" t="s">
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="24"/>
+    </row>
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E58" s="14" t="n">
-        <f aca="false">베이스!E17</f>
-        <v>2</v>
-      </c>
-      <c r="F58" s="11" t="str">
-        <f aca="false">베이스!D17</f>
-        <v>일</v>
-      </c>
-      <c r="G58" s="14" t="n">
-        <f aca="false">베이스!F17</f>
-        <v>300000</v>
-      </c>
-      <c r="H58" s="14" t="n">
-        <f aca="false">베이스!G17</f>
-        <v>600000</v>
-      </c>
-      <c r="I58" s="13"/>
-    </row>
-    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13" t="s">
+      <c r="B60" s="24"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="24"/>
+    </row>
+    <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="E59" s="14" t="n">
-        <f aca="false">베이스!E18</f>
-        <v>1</v>
-      </c>
-      <c r="F59" s="11" t="str">
-        <f aca="false">베이스!D18</f>
-        <v>일</v>
-      </c>
-      <c r="G59" s="14" t="n">
-        <f aca="false">베이스!F18</f>
-        <v>300000</v>
-      </c>
-      <c r="H59" s="14" t="n">
-        <f aca="false">베이스!G18</f>
-        <v>300000</v>
-      </c>
-      <c r="I59" s="13"/>
-    </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <f aca="false">베이스!E19</f>
-        <v>3</v>
-      </c>
-      <c r="F60" s="11" t="str">
-        <f aca="false">베이스!D19</f>
-        <v>대·일</v>
-      </c>
-      <c r="G60" s="14" t="n">
-        <f aca="false">베이스!F19</f>
-        <v>400000</v>
-      </c>
-      <c r="H60" s="14" t="n">
-        <f aca="false">베이스!G19</f>
-        <v>1200000</v>
-      </c>
-      <c r="I60" s="13" t="s">
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+    </row>
+    <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="24" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E61" s="14" t="n">
-        <f aca="false">베이스!E20</f>
-        <v>1</v>
-      </c>
-      <c r="F61" s="11" t="str">
-        <f aca="false">베이스!D20</f>
-        <v>식</v>
-      </c>
-      <c r="G61" s="14" t="n">
-        <f aca="false">베이스!F20</f>
-        <v>750000</v>
-      </c>
-      <c r="H61" s="14" t="n">
-        <f aca="false">베이스!G20</f>
-        <v>750000</v>
-      </c>
-      <c r="I61" s="13" t="s">
+      <c r="B62" s="24"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+    </row>
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="24" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G62" s="14" t="n">
-        <f aca="false">H62</f>
-        <v>2915300</v>
-      </c>
-      <c r="H62" s="14" t="n">
-        <f aca="false">베이스!$G$31-베이스!$G$21-베이스!$G$22-베이스!$G$23</f>
-        <v>2915300</v>
-      </c>
-      <c r="I62" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="15" t="s">
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
+    </row>
+    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="16" t="n">
-        <f aca="false">베이스!$G$31</f>
-        <v>19449000</v>
-      </c>
-      <c r="I63" s="17" t="s">
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="24"/>
+    </row>
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="24" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="18" t="s">
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="24"/>
+    </row>
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="19" t="n">
-        <f aca="false">H33+H47+H63</f>
-        <v>71692000</v>
-      </c>
-      <c r="I64" s="20"/>
-    </row>
-    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="18" t="s">
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+    </row>
+    <row r="68" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="19" t="n">
-        <f aca="false">H64*0.1</f>
-        <v>7169200</v>
-      </c>
-      <c r="I65" s="20"/>
-    </row>
-    <row r="66" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="21" t="s">
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
+    </row>
+    <row r="69" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="21"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="22" t="n">
-        <f aca="false">H64+H65</f>
-        <v>78861200</v>
-      </c>
-      <c r="I66" s="23"/>
-    </row>
-    <row r="68" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+    </row>
+    <row r="70" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="26" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="24" t="s">
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+    </row>
+    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="24"/>
-    </row>
-    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
-      <c r="D70" s="24"/>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="24"/>
-      <c r="H70" s="24"/>
-      <c r="I70" s="24"/>
-    </row>
-    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
-      <c r="H71" s="24"/>
-      <c r="I71" s="24"/>
-    </row>
-    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="B72" s="24"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="24"/>
-      <c r="H72" s="24"/>
-      <c r="I72" s="24"/>
-    </row>
-    <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="B73" s="24"/>
-      <c r="C73" s="24"/>
-      <c r="D73" s="24"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="24"/>
-    </row>
-    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="24"/>
-    </row>
-    <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
-      <c r="H75" s="24"/>
-      <c r="I75" s="24"/>
-    </row>
-    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="24"/>
-    </row>
-    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="24"/>
-    </row>
-    <row r="79" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25"/>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25"/>
-      <c r="I79" s="25"/>
-    </row>
-    <row r="80" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-    </row>
-    <row r="81" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="26"/>
-      <c r="F81" s="26"/>
-      <c r="G81" s="26"/>
-      <c r="H81" s="26"/>
-      <c r="I81" s="26"/>
-    </row>
-    <row r="83" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
-      <c r="H83" s="27"/>
-      <c r="I83" s="27"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="85">
+  <mergeCells count="74">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
@@ -3767,34 +3383,23 @@
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A71:I71"/>
     <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A81:I81"/>
-    <mergeCell ref="A83:I83"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.629861111111111" right="0.629861111111111" top="0.709722222222222" bottom="0.709722222222222" header="0.511811023622047" footer="0.35"/>
@@ -3827,7 +3432,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -3851,7 +3456,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -3864,7 +3469,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="47" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -3877,7 +3482,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -3901,18 +3506,18 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>75</v>
@@ -3928,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3940,7 +3545,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>116</v>
+        <v>255</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>75</v>
@@ -3957,16 +3562,16 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11"/>
       <c r="B10" s="11" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>75</v>
@@ -3982,24 +3587,24 @@
         <v>380000</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>2</v>
@@ -4012,10 +3617,10 @@
         <v>700000</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4024,10 +3629,10 @@
         <v>80</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>2</v>
@@ -4040,10 +3645,10 @@
         <v>1000000</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4052,10 +3657,10 @@
         <v>89</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>2</v>
@@ -4068,10 +3673,10 @@
         <v>400000</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4080,10 +3685,10 @@
         <v>91</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -4096,22 +3701,22 @@
         <v>250000</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11" t="s">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>4</v>
@@ -4124,10 +3729,10 @@
         <v>1400000</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4154,7 +3759,7 @@
         <v>550000</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>71</v>
@@ -4162,7 +3767,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
@@ -4178,7 +3783,7 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="48" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
@@ -4194,7 +3799,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
@@ -4210,7 +3815,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
@@ -4222,13 +3827,13 @@
         <v>133500</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="I20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
@@ -4240,13 +3845,13 @@
         <v>43125</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="I21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
@@ -4258,13 +3863,13 @@
         <v>141505</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -4280,7 +3885,7 @@
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
@@ -4292,13 +3897,13 @@
         <v>270906.5</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="I24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="48" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
@@ -4310,13 +3915,13 @@
         <v>733355.475</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -4328,13 +3933,13 @@
         <v>-391.974999999627</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="50" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B27" s="50"/>
       <c r="C27" s="50"/>
@@ -4346,13 +3951,13 @@
         <v>6422000</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="I27" s="41"/>
     </row>
     <row r="29" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="52" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B29" s="52"/>
       <c r="C29" s="52"/>
@@ -4365,7 +3970,7 @@
     </row>
     <row r="30" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="52" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
@@ -4433,24 +4038,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4513,7 +4118,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="56"/>
       <c r="B7" s="57" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C7" s="56" t="n">
         <f aca="false">SUM(C4:C6)</f>
@@ -4527,16 +4132,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>334</v>
+        <v>32</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>36</v>
@@ -4544,26 +4149,26 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>335</v>
+        <v>110</v>
       </c>
       <c r="B10" s="59" t="n">
         <f aca="false">E7</f>
         <v>9991.2</v>
       </c>
-      <c r="C10" s="14" t="n">
-        <v>700</v>
+      <c r="C10" s="60" t="s">
+        <v>200</v>
       </c>
       <c r="D10" s="14" t="n">
-        <f aca="false">B10*C10</f>
-        <v>6993840</v>
+        <f aca="false">베이스!G8</f>
+        <v>1800000</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4592,58 +4197,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="C3" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>343</v>
-      </c>
-      <c r="F3" s="60" t="s">
-        <v>344</v>
-      </c>
-      <c r="G3" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="H3" s="60" t="s">
-        <v>346</v>
-      </c>
-      <c r="I3" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="J3" s="60" t="s">
-        <v>348</v>
-      </c>
-      <c r="K3" s="60" t="s">
-        <v>349</v>
-      </c>
-      <c r="L3" s="60" t="s">
-        <v>350</v>
-      </c>
-      <c r="M3" s="60" t="s">
-        <v>351</v>
+        <v>323</v>
+      </c>
+      <c r="C3" s="61" t="s">
+        <v>324</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>325</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>326</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>328</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>329</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>330</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>331</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>332</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="M3" s="61" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="53" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>353</v>
-      </c>
-      <c r="C4" s="61"/>
+        <v>336</v>
+      </c>
+      <c r="C4" s="62"/>
       <c r="D4" s="54"/>
       <c r="E4" s="54"/>
       <c r="F4" s="54"/>
@@ -4657,14 +4262,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="53" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>355</v>
-      </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
+        <v>337</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
       <c r="F5" s="54"/>
       <c r="G5" s="54"/>
       <c r="H5" s="54"/>
@@ -4676,15 +4281,15 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="53" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="C6" s="54"/>
       <c r="D6" s="54"/>
       <c r="E6" s="54"/>
-      <c r="F6" s="61"/>
+      <c r="F6" s="62"/>
       <c r="G6" s="54"/>
       <c r="H6" s="54"/>
       <c r="I6" s="54"/>
@@ -4695,17 +4300,17 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="53" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="C7" s="54"/>
       <c r="D7" s="54"/>
       <c r="E7" s="54"/>
       <c r="F7" s="54"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
       <c r="I7" s="54"/>
       <c r="J7" s="54"/>
       <c r="K7" s="54"/>
@@ -4714,10 +4319,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="53" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="C8" s="54"/>
       <c r="D8" s="54"/>
@@ -4725,18 +4330,18 @@
       <c r="F8" s="54"/>
       <c r="G8" s="54"/>
       <c r="H8" s="54"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
       <c r="K8" s="54"/>
       <c r="L8" s="54"/>
       <c r="M8" s="54"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="53" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="54"/>
@@ -4746,16 +4351,16 @@
       <c r="H9" s="54"/>
       <c r="I9" s="54"/>
       <c r="J9" s="54"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="61"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="53" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="C10" s="54"/>
       <c r="D10" s="54"/>
@@ -4767,11 +4372,11 @@
       <c r="J10" s="54"/>
       <c r="K10" s="54"/>
       <c r="L10" s="54"/>
-      <c r="M10" s="61"/>
+      <c r="M10" s="62"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -4801,7 +4406,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -4819,7 +4424,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -4829,27 +4434,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">도비!$G$22</f>
@@ -4860,21 +4465,21 @@
         <v>3680000</v>
       </c>
       <c r="D6" s="14" t="n">
-        <f aca="false">베이스!$G$21</f>
-        <v>8733700</v>
+        <f aca="false">베이스!$G$11</f>
+        <v>1800000</v>
       </c>
       <c r="E6" s="31" t="n">
         <f aca="false">SUM(B6:D6)</f>
-        <v>13793700</v>
+        <v>6860000</v>
       </c>
       <c r="F6" s="32" t="n">
         <f aca="false">E6/$E$16</f>
-        <v>0.192402220610389</v>
+        <v>0.124156154416955</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B7" s="14" t="n">
         <f aca="false">도비!$G$23</f>
@@ -4885,16 +4490,16 @@
         <v>9850000</v>
       </c>
       <c r="D7" s="14" t="n">
-        <f aca="false">베이스!$G$22</f>
-        <v>4950000</v>
+        <f aca="false">베이스!$G$12</f>
+        <v>1050000</v>
       </c>
       <c r="E7" s="31" t="n">
         <f aca="false">SUM(B7:D7)</f>
-        <v>21280000</v>
+        <v>17380000</v>
       </c>
       <c r="F7" s="32" t="n">
         <f aca="false">E7/$E$16</f>
-        <v>0.296825308263126</v>
+        <v>0.314553055942664</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4910,21 +4515,21 @@
         <v>9000000</v>
       </c>
       <c r="D8" s="14" t="n">
-        <f aca="false">베이스!$G$23</f>
-        <v>2850000</v>
+        <f aca="false">베이스!$G$13</f>
+        <v>160000</v>
       </c>
       <c r="E8" s="31" t="n">
         <f aca="false">SUM(B8:D8)</f>
-        <v>23920000</v>
+        <v>21230000</v>
       </c>
       <c r="F8" s="32" t="n">
         <f aca="false">E8/$E$16</f>
-        <v>0.333649500641634</v>
+        <v>0.384232530360342</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">도비!$G$25</f>
@@ -4935,21 +4540,21 @@
         <v>350660</v>
       </c>
       <c r="D9" s="14" t="n">
-        <f aca="false">베이스!$G$24</f>
-        <v>176220</v>
+        <f aca="false">베이스!$G$14</f>
+        <v>0</v>
       </c>
       <c r="E9" s="31" t="n">
         <f aca="false">SUM(B9:D9)</f>
-        <v>757568</v>
+        <v>581348</v>
       </c>
       <c r="F9" s="32" t="n">
         <f aca="false">E9/$E$16</f>
-        <v>0.0105669809741673</v>
+        <v>0.0105215644399399</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">도비!$G$26</f>
@@ -4960,21 +4565,21 @@
         <v>113275</v>
       </c>
       <c r="D10" s="14" t="n">
-        <f aca="false">베이스!$G$25</f>
-        <v>56925</v>
+        <f aca="false">베이스!$G$15</f>
+        <v>0</v>
       </c>
       <c r="E10" s="31" t="n">
         <f aca="false">SUM(B10:D10)</f>
-        <v>244720</v>
+        <v>187795</v>
       </c>
       <c r="F10" s="32" t="n">
         <f aca="false">E10/$E$16</f>
-        <v>0.00341349104502594</v>
+        <v>0.0033988199735761</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B11" s="14" t="n">
         <f aca="false">도비!$G$27</f>
@@ -4985,21 +4590,21 @@
         <v>420783</v>
       </c>
       <c r="D11" s="14" t="n">
-        <f aca="false">베이스!$G$26</f>
-        <v>425563.07</v>
+        <f aca="false">베이스!$G$16</f>
+        <v>0</v>
       </c>
       <c r="E11" s="31" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>1090792.07</v>
+        <v>665229</v>
       </c>
       <c r="F11" s="32" t="n">
         <f aca="false">E11/$E$16</f>
-        <v>0.0152149761479663</v>
+        <v>0.0120396901525709</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B12" s="19" t="n">
         <f aca="false">도비!$G$28</f>
@@ -5010,21 +4615,21 @@
         <v>23414718</v>
       </c>
       <c r="D12" s="19" t="n">
-        <f aca="false">베이스!$G$27</f>
-        <v>17192408.07</v>
+        <f aca="false">베이스!$G$17</f>
+        <v>3010000</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>61086780.07</v>
+        <v>46904372</v>
       </c>
       <c r="F12" s="33" t="n">
         <f aca="false">E12/$E$16</f>
-        <v>0.852072477682308</v>
+        <v>0.848901815286048</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">도비!$G$29</f>
@@ -5035,21 +4640,21 @@
         <v>1170735.9</v>
       </c>
       <c r="D13" s="14" t="n">
-        <f aca="false">베이스!$G$28</f>
-        <v>859620.4035</v>
+        <f aca="false">베이스!$G$18</f>
+        <v>0</v>
       </c>
       <c r="E13" s="31" t="n">
         <f aca="false">SUM(B13:D13)</f>
-        <v>3054339.0035</v>
+        <v>2194718.6</v>
       </c>
       <c r="F13" s="32" t="n">
         <f aca="false">E13/$E$16</f>
-        <v>0.0426036238841154</v>
+        <v>0.0397212567643386</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">도비!$G$30</f>
@@ -5060,21 +4665,21 @@
         <v>3135818.085</v>
       </c>
       <c r="D14" s="14" t="n">
-        <f aca="false">베이스!$G$29</f>
-        <v>1397749.271025</v>
+        <f aca="false">베이스!$G$19</f>
+        <v>0</v>
       </c>
       <c r="E14" s="31" t="n">
         <f aca="false">SUM(B14:D14)</f>
-        <v>7552112.861025</v>
+        <v>6154363.59</v>
       </c>
       <c r="F14" s="32" t="n">
         <f aca="false">E14/$E$16</f>
-        <v>0.105341082143405</v>
+        <v>0.111385148136753</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B15" s="14" t="n">
         <f aca="false">도비!$G$31</f>
@@ -5085,21 +4690,21 @@
         <v>-271.984999999404</v>
       </c>
       <c r="D15" s="14" t="n">
-        <f aca="false">베이스!$G$30</f>
-        <v>-777.744524996728</v>
+        <f aca="false">베이스!$G$20</f>
+        <v>-0</v>
       </c>
       <c r="E15" s="31" t="n">
         <f aca="false">SUM(B15:D15)</f>
-        <v>-1231.93452499434</v>
+        <v>-454.189999997616</v>
       </c>
       <c r="F15" s="32" t="n">
         <f aca="false">E15/$E$16</f>
-        <v>-1.71837098280749E-005</v>
+        <v>-8.22018713911671E-006</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">도비!$G$32</f>
@@ -5110,12 +4715,12 @@
         <v>27721000</v>
       </c>
       <c r="D16" s="19" t="n">
-        <f aca="false">베이스!$G$31</f>
-        <v>19449000</v>
+        <f aca="false">베이스!$G$21</f>
+        <v>3010000</v>
       </c>
       <c r="E16" s="19" t="n">
         <f aca="false">SUM(B16:D16)</f>
-        <v>71692000</v>
+        <v>55253000</v>
       </c>
       <c r="F16" s="33" t="n">
         <f aca="false">E16/$E$16</f>
@@ -5124,33 +4729,33 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14" t="n">
         <f aca="false">E16*0.1</f>
-        <v>7169200</v>
+        <v>5525300</v>
       </c>
       <c r="F17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="34" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B18" s="35"/>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
       <c r="E18" s="35" t="n">
         <f aca="false">E16+E17</f>
-        <v>78861200</v>
+        <v>60778300</v>
       </c>
       <c r="F18" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="36" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
@@ -5160,102 +4765,102 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="38" t="n">
         <v>0.0356</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F24" s="39"/>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="38" t="n">
         <v>0.0115</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="38" t="n">
         <v>0.0311</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="38" t="n">
         <v>0.05</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="F27" s="39"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="38" t="n">
         <v>0.15</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F28" s="39"/>
     </row>
@@ -5303,7 +4908,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -5312,16 +4917,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>36</v>
@@ -5329,7 +4934,7 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B4" s="14" t="n">
         <f aca="false">도비!$G$32</f>
@@ -5344,12 +4949,12 @@
         <v>9005000</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B5" s="14" t="n">
         <f aca="false">용접!$G$29</f>
@@ -5364,16 +4969,16 @@
         <v>0</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B6" s="14" t="n">
-        <f aca="false">베이스!$G$31</f>
-        <v>19449000</v>
+        <f aca="false">베이스!$G$21</f>
+        <v>3010000</v>
       </c>
       <c r="C6" s="14" t="n">
         <f aca="false">B_조방!$G$27</f>
@@ -5381,19 +4986,19 @@
       </c>
       <c r="D6" s="14" t="n">
         <f aca="false">C6-B6</f>
-        <v>-13027000</v>
+        <v>3412000</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="41" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">SUM(B4:B6)</f>
-        <v>71692000</v>
+        <v>55253000</v>
       </c>
       <c r="C7" s="35" t="n">
         <f aca="false">SUM(C4:C6)</f>
@@ -5401,13 +5006,13 @@
       </c>
       <c r="D7" s="35" t="n">
         <f aca="false">SUM(D4:D6)</f>
-        <v>-4022000</v>
+        <v>12417000</v>
       </c>
       <c r="E7" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
@@ -5416,7 +5021,7 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B10" s="36"/>
       <c r="C10" s="36"/>
@@ -5425,7 +5030,7 @@
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
@@ -5454,7 +5059,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -5467,17 +5072,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>30</v>
@@ -5486,18 +5091,18 @@
         <v>31</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>38</v>
@@ -5506,19 +5111,19 @@
         <v>39</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E5" s="44" t="n">
         <f aca="false">도비!G8</f>
         <v>4500000</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>41</v>
@@ -5527,19 +5132,19 @@
         <v>42</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E6" s="44" t="n">
         <f aca="false">도비!G9</f>
         <v>520000</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>44</v>
@@ -5548,19 +5153,19 @@
         <v>45</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="E7" s="44" t="n">
         <f aca="false">도비!G10</f>
         <v>960000</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>47</v>
@@ -5569,19 +5174,19 @@
         <v>48</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E8" s="44" t="n">
         <f aca="false">도비!G11</f>
         <v>2400000</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>47</v>
@@ -5590,19 +5195,19 @@
         <v>50</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E9" s="44" t="n">
         <f aca="false">도비!G12</f>
         <v>1700000</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>51</v>
@@ -5611,19 +5216,19 @@
         <v>52</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E10" s="44" t="n">
         <f aca="false">도비!G13</f>
         <v>640000</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>54</v>
@@ -5632,19 +5237,19 @@
         <v>55</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E11" s="44" t="n">
         <f aca="false">도비!G14</f>
         <v>2000000</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>57</v>
@@ -5653,19 +5258,19 @@
         <v>58</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E12" s="44" t="n">
         <f aca="false">도비!G15</f>
         <v>3000000</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>59</v>
@@ -5674,19 +5279,19 @@
         <v>60</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E13" s="44" t="n">
         <f aca="false">도비!G16</f>
         <v>1000000</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>61</v>
@@ -5695,19 +5300,19 @@
         <v>62</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E14" s="44" t="n">
         <f aca="false">도비!G17</f>
         <v>1210000</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>64</v>
@@ -5716,19 +5321,19 @@
         <v>65</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E15" s="44" t="n">
         <f aca="false">도비!G18</f>
         <v>500000</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>67</v>
@@ -5737,38 +5342,38 @@
         <v>68</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="E16" s="44" t="n">
         <f aca="false">도비!G19</f>
         <v>520000</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E17" s="44" t="n">
         <f aca="false">도비!G20</f>
         <v>380000</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>71</v>
@@ -5777,14 +5382,14 @@
         <v>72</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E18" s="44" t="n">
         <f aca="false">도비!G21</f>
         <v>600000</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5799,13 +5404,13 @@
         <v>4592000</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20"/>
       <c r="B20" s="45" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
@@ -5814,12 +5419,12 @@
         <v>24522000</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>80</v>
@@ -5828,19 +5433,19 @@
         <v>81</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E22" s="44" t="n">
         <f aca="false">용접!G8</f>
         <v>4500000</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>83</v>
@@ -5849,19 +5454,19 @@
         <v>84</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E23" s="44" t="n">
         <f aca="false">용접!G9</f>
         <v>2100000</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>86</v>
@@ -5870,19 +5475,19 @@
         <v>87</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E24" s="44" t="n">
         <f aca="false">용접!G10</f>
         <v>1200000</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>89</v>
@@ -5891,19 +5496,19 @@
         <v>90</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="E25" s="44" t="n">
         <f aca="false">용접!G11</f>
         <v>800000</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>91</v>
@@ -5912,19 +5517,19 @@
         <v>92</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="E26" s="44" t="n">
         <f aca="false">용접!G12</f>
         <v>1250000</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>94</v>
@@ -5933,19 +5538,19 @@
         <v>95</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="E27" s="44" t="n">
         <f aca="false">용접!G13</f>
         <v>3600000</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>97</v>
@@ -5954,19 +5559,19 @@
         <v>98</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E28" s="44" t="n">
         <f aca="false">용접!G14</f>
         <v>800000</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>99</v>
@@ -5975,38 +5580,38 @@
         <v>100</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E29" s="44" t="n">
         <f aca="false">용접!G15</f>
         <v>3680000</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>101</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E30" s="44" t="n">
         <f aca="false">용접!G16</f>
         <v>1000000</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>102</v>
@@ -6015,19 +5620,19 @@
         <v>103</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="E31" s="44" t="n">
         <f aca="false">용접!G17</f>
         <v>2200000</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>71</v>
@@ -6036,14 +5641,14 @@
         <v>105</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E32" s="44" t="n">
         <f aca="false">용접!G18</f>
         <v>1400000</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6058,13 +5663,13 @@
         <v>5191000</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20"/>
       <c r="B34" s="45" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
@@ -6073,12 +5678,12 @@
         <v>27721000</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>110</v>
@@ -6087,310 +5692,320 @@
         <v>111</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="E36" s="44" t="n">
         <f aca="false">베이스!G8</f>
-        <v>6993700</v>
+        <v>1800000</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="13"/>
+      <c r="C37" s="13" t="s">
+        <v>114</v>
+      </c>
       <c r="D37" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E37" s="44" t="n">
         <f aca="false">베이스!G9</f>
         <v>160000</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C38" s="13"/>
+        <v>115</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>116</v>
+      </c>
       <c r="D38" s="13" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="E38" s="44" t="n">
         <f aca="false">베이스!G10</f>
-        <v>160000</v>
+        <v>1050000</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E39" s="44" t="n">
-        <f aca="false">베이스!G11</f>
-        <v>1000000</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E40" s="44" t="n">
-        <f aca="false">베이스!G12</f>
-        <v>420000</v>
-      </c>
-      <c r="F40" s="13" t="s">
+      <c r="A39" s="20"/>
+      <c r="B39" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="46" t="n">
+        <f aca="false">베이스!$G$21</f>
+        <v>3010000</v>
+      </c>
+      <c r="F39" s="20" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E41" s="44" t="n">
-        <f aca="false">베이스!G13</f>
-        <v>2100000</v>
+        <f aca="false">B_도비!G8</f>
+        <v>6300000</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E42" s="44" t="n">
-        <f aca="false">베이스!G14</f>
-        <v>1500000</v>
+        <f aca="false">B_도비!G9</f>
+        <v>1040000</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>123</v>
+        <v>234</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>241</v>
+        <v>193</v>
       </c>
       <c r="E43" s="44" t="n">
-        <f aca="false">베이스!G15</f>
-        <v>600000</v>
+        <f aca="false">B_도비!G10</f>
+        <v>960000</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>124</v>
+        <v>235</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="E44" s="44" t="n">
-        <f aca="false">베이스!G16</f>
-        <v>750000</v>
+        <f aca="false">B_도비!G11</f>
+        <v>2400000</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="E45" s="44" t="n">
-        <f aca="false">베이스!G17</f>
-        <v>600000</v>
+        <f aca="false">B_도비!G12</f>
+        <v>1700000</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E46" s="44" t="n">
-        <f aca="false">베이스!G18</f>
-        <v>300000</v>
+        <f aca="false">B_도비!G13</f>
+        <v>3500000</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>94</v>
+        <v>239</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>95</v>
+        <v>240</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="E47" s="44" t="n">
-        <f aca="false">베이스!G19</f>
+        <f aca="false">B_도비!G14</f>
         <v>1200000</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>71</v>
+        <v>241</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="E48" s="44" t="n">
-        <f aca="false">베이스!G20</f>
-        <v>750000</v>
+        <f aca="false">B_도비!G15</f>
+        <v>800000</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="20"/>
-      <c r="B49" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="46" t="n">
-        <f aca="false">베이스!$G$31-SUM(베이스!$G$21:$G$23)</f>
-        <v>2915300</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>224</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="E49" s="44" t="n">
+        <f aca="false">B_도비!G16</f>
+        <v>1280000</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="20"/>
-      <c r="B50" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="46" t="n">
-        <f aca="false">베이스!$G$31</f>
-        <v>19449000</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>226</v>
+      <c r="A50" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E50" s="44" t="n">
+        <f aca="false">B_도비!G17</f>
+        <v>3000000</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E51" s="44" t="n">
+        <f aca="false">B_도비!G18</f>
+        <v>900000</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="E52" s="44" t="n">
-        <f aca="false">B_도비!G8</f>
-        <v>6300000</v>
+        <f aca="false">B_도비!G19</f>
+        <v>1000000</v>
       </c>
       <c r="F52" s="13" t="s">
         <v>202</v>
@@ -6398,20 +6013,20 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>250</v>
-      </c>
       <c r="E53" s="44" t="n">
-        <f aca="false">B_도비!G9</f>
-        <v>1040000</v>
+        <f aca="false">B_도비!G20</f>
+        <v>1210000</v>
       </c>
       <c r="F53" s="13" t="s">
         <v>204</v>
@@ -6419,823 +6034,592 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>251</v>
+        <v>65</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>205</v>
       </c>
       <c r="E54" s="44" t="n">
-        <f aca="false">B_도비!G10</f>
-        <v>960000</v>
+        <f aca="false">B_도비!G21</f>
+        <v>500000</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>252</v>
+        <v>68</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E55" s="44" t="n">
-        <f aca="false">B_도비!G11</f>
-        <v>2400000</v>
+        <f aca="false">B_도비!G22</f>
+        <v>520000</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>253</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C56" s="13"/>
       <c r="D56" s="13" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E56" s="44" t="n">
-        <f aca="false">B_도비!G12</f>
-        <v>1700000</v>
+        <f aca="false">B_도비!G23</f>
+        <v>380000</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>254</v>
+        <v>72</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="E57" s="44" t="n">
-        <f aca="false">B_도비!G13</f>
-        <v>3500000</v>
+        <f aca="false">B_도비!G24</f>
+        <v>600000</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="D58" s="13" t="s">
+      <c r="A58" s="20"/>
+      <c r="B58" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="46" t="n">
+        <f aca="false">B_도비!$G$35-SUM(B_도비!$G$25:$G$27)</f>
+        <v>6237000</v>
+      </c>
+      <c r="F58" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="E58" s="44" t="n">
-        <f aca="false">B_도비!G14</f>
-        <v>1200000</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>210</v>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E59" s="44" t="n">
-        <f aca="false">B_도비!G15</f>
-        <v>800000</v>
-      </c>
-      <c r="F59" s="13" t="s">
+      <c r="A59" s="20"/>
+      <c r="B59" s="45" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E60" s="44" t="n">
-        <f aca="false">B_도비!G16</f>
-        <v>1280000</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>210</v>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="46" t="n">
+        <f aca="false">B_도비!$G$35</f>
+        <v>33527000</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E61" s="44" t="n">
-        <f aca="false">B_도비!G17</f>
-        <v>3000000</v>
+        <f aca="false">B_용접!G8</f>
+        <v>4500000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E62" s="44" t="n">
-        <f aca="false">B_도비!G18</f>
-        <v>900000</v>
+        <f aca="false">B_용접!G9</f>
+        <v>2100000</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>263</v>
+        <v>87</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E63" s="44" t="n">
-        <f aca="false">B_도비!G19</f>
-        <v>1000000</v>
+        <f aca="false">B_용접!G10</f>
+        <v>1200000</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="E64" s="44" t="n">
-        <f aca="false">B_도비!G20</f>
-        <v>1210000</v>
+        <f aca="false">B_용접!G11</f>
+        <v>800000</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E65" s="44" t="n">
-        <f aca="false">B_도비!G21</f>
-        <v>500000</v>
+        <f aca="false">B_용접!G12</f>
+        <v>1250000</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E66" s="44" t="n">
-        <f aca="false">B_도비!G22</f>
-        <v>520000</v>
+        <f aca="false">B_용접!G13</f>
+        <v>3600000</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="13"/>
+        <v>97</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>98</v>
+      </c>
       <c r="D67" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E67" s="44" t="n">
-        <f aca="false">B_도비!G23</f>
-        <v>380000</v>
+        <f aca="false">B_용접!G14</f>
+        <v>800000</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>222</v>
       </c>
       <c r="E68" s="44" t="n">
-        <f aca="false">B_도비!G24</f>
-        <v>600000</v>
+        <f aca="false">B_용접!G15</f>
+        <v>3680000</v>
       </c>
       <c r="F68" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E69" s="44" t="n">
+        <f aca="false">B_용접!G16</f>
+        <v>1000000</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D70" s="13" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20"/>
-      <c r="B69" s="45" t="s">
+      <c r="E70" s="44" t="n">
+        <f aca="false">B_용접!G17</f>
+        <v>2200000</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="E71" s="44" t="n">
+        <f aca="false">B_용접!G18</f>
+        <v>1400000</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="20"/>
+      <c r="B72" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="46" t="n">
-        <f aca="false">B_도비!$G$35-SUM(B_도비!$G$25:$G$27)</f>
-        <v>6237000</v>
-      </c>
-      <c r="F69" s="20" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="20"/>
-      <c r="B70" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="46" t="n">
-        <f aca="false">B_도비!$G$35</f>
-        <v>33527000</v>
-      </c>
-      <c r="F70" s="20" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="E72" s="44" t="n">
-        <f aca="false">B_용접!G8</f>
-        <v>4500000</v>
-      </c>
-      <c r="F72" s="13" t="s">
-        <v>218</v>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="46" t="n">
+        <f aca="false">B_용접!$G$29-SUM(B_용접!$G$19:$G$21)</f>
+        <v>5191000</v>
+      </c>
+      <c r="F72" s="20" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E73" s="44" t="n">
-        <f aca="false">B_용접!G9</f>
-        <v>2100000</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="E74" s="44" t="n">
-        <f aca="false">B_용접!G10</f>
-        <v>1200000</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>218</v>
+      <c r="A73" s="20"/>
+      <c r="B73" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="46" t="n">
+        <f aca="false">B_용접!$G$29</f>
+        <v>27721000</v>
+      </c>
+      <c r="F73" s="20" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="13" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>89</v>
+        <v>251</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>90</v>
+        <v>252</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="E75" s="44" t="n">
-        <f aca="false">B_용접!G11</f>
-        <v>800000</v>
+        <f aca="false">B_조방!G8</f>
+        <v>0</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="13" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>92</v>
+        <v>255</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="E76" s="44" t="n">
-        <f aca="false">B_용접!G12</f>
-        <v>1250000</v>
+        <f aca="false">B_조방!G9</f>
+        <v>420000</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="13" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>95</v>
+        <v>257</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="E77" s="44" t="n">
-        <f aca="false">B_용접!G13</f>
-        <v>3600000</v>
+        <f aca="false">B_조방!G10</f>
+        <v>380000</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="13" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>98</v>
+        <v>259</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>212</v>
+        <v>260</v>
       </c>
       <c r="E78" s="44" t="n">
-        <f aca="false">B_용접!G14</f>
-        <v>800000</v>
+        <f aca="false">B_조방!G11</f>
+        <v>700000</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="13" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>100</v>
+        <v>261</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="E79" s="44" t="n">
-        <f aca="false">B_용접!G15</f>
-        <v>3680000</v>
+        <f aca="false">B_조방!G12</f>
+        <v>1000000</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E80" s="44" t="n">
+        <f aca="false">B_조방!G13</f>
+        <v>400000</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="D81" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="B80" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E80" s="44" t="n">
-        <f aca="false">B_용접!G16</f>
-        <v>1000000</v>
-      </c>
-      <c r="F80" s="13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="B81" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>235</v>
-      </c>
       <c r="E81" s="44" t="n">
-        <f aca="false">B_용접!G17</f>
-        <v>2200000</v>
+        <f aca="false">B_조방!G14</f>
+        <v>250000</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="13" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B82" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E82" s="44" t="n">
+        <f aca="false">B_조방!G15</f>
+        <v>1400000</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B83" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C83" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D82" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="E82" s="44" t="n">
-        <f aca="false">B_용접!G18</f>
-        <v>1400000</v>
-      </c>
-      <c r="F82" s="13" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="20"/>
-      <c r="B83" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="C83" s="20"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="46" t="n">
-        <f aca="false">B_용접!$G$29-SUM(B_용접!$G$19:$G$21)</f>
-        <v>5191000</v>
-      </c>
-      <c r="F83" s="20" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D83" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="E83" s="44" t="n">
+        <f aca="false">B_조방!G16</f>
+        <v>550000</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="20"/>
       <c r="B84" s="45" t="s">
-        <v>225</v>
+        <v>73</v>
       </c>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="46" t="n">
-        <f aca="false">B_용접!$G$29</f>
-        <v>27721000</v>
-      </c>
-      <c r="F84" s="20" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="E86" s="44" t="n">
-        <f aca="false">B_조방!G8</f>
-        <v>0</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D87" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E87" s="44" t="n">
-        <f aca="false">B_조방!G9</f>
-        <v>420000</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E88" s="44" t="n">
-        <f aca="false">B_조방!G10</f>
-        <v>380000</v>
-      </c>
-      <c r="F88" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="E89" s="44" t="n">
-        <f aca="false">B_조방!G11</f>
-        <v>700000</v>
-      </c>
-      <c r="F89" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B90" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E90" s="44" t="n">
-        <f aca="false">B_조방!G12</f>
-        <v>1000000</v>
-      </c>
-      <c r="F90" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="E91" s="44" t="n">
-        <f aca="false">B_조방!G13</f>
-        <v>400000</v>
-      </c>
-      <c r="F91" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B92" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="E92" s="44" t="n">
-        <f aca="false">B_조방!G14</f>
-        <v>250000</v>
-      </c>
-      <c r="F92" s="13" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B93" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E93" s="44" t="n">
-        <f aca="false">B_조방!G15</f>
-        <v>1400000</v>
-      </c>
-      <c r="F93" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="E94" s="44" t="n">
-        <f aca="false">B_조방!G16</f>
-        <v>550000</v>
-      </c>
-      <c r="F94" s="13" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="20"/>
-      <c r="B95" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="C95" s="20"/>
-      <c r="D95" s="20"/>
-      <c r="E95" s="46" t="n">
         <f aca="false">B_조방!$G$27-SUM(B_조방!$G$17:$G$19)</f>
         <v>1322000</v>
       </c>
-      <c r="F95" s="20" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="20"/>
-      <c r="B96" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="C96" s="20"/>
-      <c r="D96" s="20"/>
-      <c r="E96" s="46" t="n">
+      <c r="F84" s="20" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="20"/>
+      <c r="B85" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="46" t="n">
         <f aca="false">B_조방!$G$27</f>
         <v>6422000</v>
       </c>
-      <c r="F96" s="20" t="s">
-        <v>265</v>
+      <c r="F85" s="20" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -7270,7 +6654,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -7294,7 +6678,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -7307,7 +6691,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="47" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -7320,7 +6704,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -7344,12 +6728,12 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>38</v>
@@ -7358,7 +6742,7 @@
         <v>39</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>15</v>
@@ -7374,7 +6758,7 @@
         <v>40</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7386,7 +6770,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>2</v>
@@ -7402,7 +6786,7 @@
         <v>43</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7414,7 +6798,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>3</v>
@@ -7430,12 +6814,12 @@
         <v>46</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>47</v>
@@ -7444,7 +6828,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -7472,7 +6856,7 @@
         <v>50</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -7528,7 +6912,7 @@
         <v>55</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -7556,7 +6940,7 @@
         <v>58</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>1</v>
@@ -7575,7 +6959,7 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>59</v>
@@ -7598,12 +6982,12 @@
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>61</v>
@@ -7612,7 +6996,7 @@
         <v>62</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>242</v>
@@ -7640,7 +7024,7 @@
         <v>65</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>2</v>
@@ -7656,7 +7040,7 @@
         <v>66</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7668,7 +7052,7 @@
         <v>68</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>2</v>
@@ -7708,7 +7092,7 @@
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7741,7 +7125,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
@@ -7757,7 +7141,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
@@ -7773,7 +7157,7 @@
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
@@ -7789,7 +7173,7 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="48" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
@@ -7801,13 +7185,13 @@
         <v>230688</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -7819,13 +7203,13 @@
         <v>74520</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B27" s="48"/>
       <c r="C27" s="48"/>
@@ -7837,13 +7221,13 @@
         <v>244446</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -7859,7 +7243,7 @@
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="48" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
@@ -7871,13 +7255,13 @@
         <v>1023982.7</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="48" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
@@ -7889,13 +7273,13 @@
         <v>3018545.505</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="I30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="48" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
@@ -7907,13 +7291,13 @@
         <v>-182.204999998212</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="I31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="50" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B32" s="50"/>
       <c r="C32" s="50"/>
@@ -7925,13 +7309,13 @@
         <v>24522000</v>
       </c>
       <c r="H32" s="41" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="I32" s="41"/>
     </row>
     <row r="34" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="52" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B34" s="52"/>
       <c r="C34" s="52"/>
@@ -7944,7 +7328,7 @@
     </row>
     <row r="35" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="52" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B35" s="52"/>
       <c r="C35" s="52"/>
@@ -8019,7 +7403,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -8043,7 +7427,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -8056,7 +7440,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="47" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -8069,7 +7453,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -8093,12 +7477,12 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>80</v>
@@ -8107,7 +7491,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>9</v>
@@ -8123,7 +7507,7 @@
         <v>82</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8135,7 +7519,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>6</v>
@@ -8151,7 +7535,7 @@
         <v>85</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8163,7 +7547,7 @@
         <v>87</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>4</v>
@@ -8179,7 +7563,7 @@
         <v>88</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8191,7 +7575,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>4</v>
@@ -8207,7 +7591,7 @@
         <v>88</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8219,7 +7603,7 @@
         <v>92</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>5</v>
@@ -8235,12 +7619,12 @@
         <v>93</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>94</v>
@@ -8249,7 +7633,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>9</v>
@@ -8277,7 +7661,7 @@
         <v>98</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -8296,7 +7680,7 @@
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>99</v>
@@ -8319,12 +7703,12 @@
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>101</v>
@@ -8357,7 +7741,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>22</v>
@@ -8408,7 +7792,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
@@ -8424,7 +7808,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
@@ -8440,7 +7824,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
@@ -8456,7 +7840,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
@@ -8468,13 +7852,13 @@
         <v>350660</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
@@ -8486,13 +7870,13 @@
         <v>113275</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
@@ -8504,13 +7888,13 @@
         <v>420783</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -8526,7 +7910,7 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -8538,13 +7922,13 @@
         <v>1170735.9</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B27" s="48"/>
       <c r="C27" s="48"/>
@@ -8556,13 +7940,13 @@
         <v>3135818.085</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="48" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B28" s="48"/>
       <c r="C28" s="48"/>
@@ -8574,13 +7958,13 @@
         <v>-271.984999999404</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="50" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B29" s="50"/>
       <c r="C29" s="50"/>
@@ -8592,13 +7976,13 @@
         <v>27721000</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="I29" s="41"/>
     </row>
     <row r="31" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="52" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B31" s="52"/>
       <c r="C31" s="52"/>
@@ -8611,7 +7995,7 @@
     </row>
     <row r="32" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="52" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B32" s="52"/>
       <c r="C32" s="52"/>
@@ -8670,7 +8054,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -8686,7 +8070,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -8710,7 +8094,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -8723,7 +8107,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="47" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -8736,7 +8120,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -8760,12 +8144,12 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>110</v>
@@ -8774,31 +8158,35 @@
         <v>111</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>9991</v>
+        <v>1</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>700</v>
+        <v>1800000</v>
       </c>
       <c r="G8" s="14" t="n">
         <f aca="false">E8*F8</f>
-        <v>6993700</v>
+        <v>1800000</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>112</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11"/>
+      <c r="A9" s="11" t="s">
+        <v>293</v>
+      </c>
       <c r="B9" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="13"/>
+      <c r="C9" s="13" t="s">
+        <v>114</v>
+      </c>
       <c r="D9" s="11" t="s">
         <v>75</v>
       </c>
@@ -8814,563 +8202,284 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="11" t="s">
-        <v>157</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11"/>
+      <c r="A10" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="B10" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="13"/>
+        <v>115</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>116</v>
+      </c>
       <c r="D10" s="11" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>160000</v>
+        <v>350000</v>
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">E10*F10</f>
+        <v>1050000</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="48" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="49" t="n">
+        <f aca="false">SUMIF($I$8:$I$10,"재료비",$G$8:$G$10)</f>
+        <v>1800000</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="49" t="n">
+        <f aca="false">SUMIF($I$8:$I$10,"노무비",$G$8:$G$10)</f>
+        <v>1050000</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="48" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="49" t="n">
+        <f aca="false">SUMIF($I$8:$I$10,"경비",$G$8:$G$10)</f>
         <v>160000</v>
       </c>
-      <c r="H10" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <f aca="false">E11*F11</f>
-        <v>1000000</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>420000</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <f aca="false">E12*F12</f>
-        <v>420000</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="11" t="s">
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="49" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="49" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="49" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="I16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19" t="n">
+        <f aca="false">SUM(G11:G16)</f>
+        <v>3010000</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="49" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="I18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="I19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49" t="n">
+        <f aca="false">-MOD(G17+G18+G19,1000)</f>
+        <v>-0</v>
+      </c>
+      <c r="H20" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>350000</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <f aca="false">E13*F13</f>
-        <v>2100000</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <f aca="false">E14*F14</f>
-        <v>1500000</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <f aca="false">E15*F15</f>
-        <v>600000</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <f aca="false">E16*F16</f>
-        <v>750000</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
+      <c r="I20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="51" t="n">
+        <f aca="false">G17+G18+G19+G20</f>
+        <v>3010000</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="I21" s="41"/>
+    </row>
+    <row r="23" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="52" t="s">
         <v>289</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <f aca="false">E17*F17</f>
-        <v>600000</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G18" s="14" t="n">
-        <f aca="false">E18*F18</f>
-        <v>300000</v>
-      </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="11" t="s">
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+    </row>
+    <row r="24" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="52" t="s">
         <v>290</v>
       </c>
-      <c r="E19" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <f aca="false">E19*F19</f>
-        <v>1200000</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>750000</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <f aca="false">E20*F20</f>
-        <v>750000</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="48" t="s">
-        <v>295</v>
-      </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49" t="n">
-        <f aca="false">SUMIF($I$8:$I$20,"재료비",$G$8:$G$20)</f>
-        <v>8733700</v>
-      </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="48" t="s">
-        <v>296</v>
-      </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49" t="n">
-        <f aca="false">SUMIF($I$8:$I$20,"노무비",$G$8:$G$20)</f>
-        <v>4950000</v>
-      </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="48" t="s">
-        <v>297</v>
-      </c>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49" t="n">
-        <f aca="false">SUMIF($I$8:$I$20,"경비",$G$8:$G$20)</f>
-        <v>2850000</v>
-      </c>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="49" t="n">
-        <f aca="false">G22*원가계산서!$D$24</f>
-        <v>176220</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="I24" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="49" t="n">
-        <f aca="false">G22*원가계산서!$D$25</f>
-        <v>56925</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="I25" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="49" t="n">
-        <f aca="false">(G21+G22)*원가계산서!$D$26</f>
-        <v>425563.07</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="19" t="n">
-        <f aca="false">SUM(G21:G26)</f>
-        <v>17192408.07</v>
-      </c>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="48" t="s">
-        <v>163</v>
-      </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="49" t="n">
-        <f aca="false">G27*원가계산서!$D$27</f>
-        <v>859620.4035</v>
-      </c>
-      <c r="H28" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="48" t="s">
-        <v>164</v>
-      </c>
-      <c r="B29" s="48"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="49" t="n">
-        <f aca="false">(G22+G23+G24+G25+G26+G28)*원가계산서!$D$28</f>
-        <v>1397749.271025</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="48" t="s">
-        <v>165</v>
-      </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="49" t="n">
-        <f aca="false">-MOD(G27+G28+G29,1000)</f>
-        <v>-777.744524996728</v>
-      </c>
-      <c r="H30" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="I30" s="20"/>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="51" t="n">
-        <f aca="false">G27+G28+G29+G30</f>
-        <v>19449000</v>
-      </c>
-      <c r="H31" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="I31" s="41"/>
-    </row>
-    <row r="33" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="52" t="s">
-        <v>304</v>
-      </c>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-    </row>
-    <row r="34" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="52" t="s">
-        <v>305</v>
-      </c>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="27">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="H20:I20"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.629861111111111" right="0.629861111111111" top="0.709722222222222" bottom="0.709722222222222" header="0.511811023622047" footer="0.35"/>
@@ -9403,7 +8512,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -9427,7 +8536,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -9440,7 +8549,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="47" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -9453,7 +8562,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -9477,21 +8586,21 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>21</v>
@@ -9504,10 +8613,10 @@
         <v>6300000</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9519,7 +8628,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>4</v>
@@ -9532,10 +8641,10 @@
         <v>1040000</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9544,10 +8653,10 @@
         <v>44</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>3</v>
@@ -9563,21 +8672,21 @@
         <v>46</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -9590,7 +8699,7 @@
         <v>2400000</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>71</v>
@@ -9602,10 +8711,10 @@
         <v>47</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -9618,7 +8727,7 @@
         <v>1700000</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>71</v>
@@ -9630,10 +8739,10 @@
         <v>47</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>1</v>
@@ -9646,7 +8755,7 @@
         <v>3500000</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>71</v>
@@ -9655,10 +8764,10 @@
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>75</v>
@@ -9674,7 +8783,7 @@
         <v>1200000</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>71</v>
@@ -9683,10 +8792,10 @@
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>75</v>
@@ -9702,7 +8811,7 @@
         <v>800000</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>71</v>
@@ -9717,7 +8826,7 @@
         <v>52</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>2</v>
@@ -9730,7 +8839,7 @@
         <v>1280000</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>71</v>
@@ -9745,7 +8854,7 @@
         <v>58</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>1</v>
@@ -9764,13 +8873,13 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>75</v>
@@ -9786,10 +8895,10 @@
         <v>900000</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9798,7 +8907,7 @@
         <v>59</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>75</v>
@@ -9815,12 +8924,12 @@
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>61</v>
@@ -9829,7 +8938,7 @@
         <v>62</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>242</v>
@@ -9842,7 +8951,7 @@
         <v>1210000</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>71</v>
@@ -9857,7 +8966,7 @@
         <v>65</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>2</v>
@@ -9871,7 +8980,7 @@
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9883,7 +8992,7 @@
         <v>68</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>2</v>
@@ -9921,7 +9030,7 @@
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9954,7 +9063,7 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="48" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
@@ -9970,7 +9079,7 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -9986,7 +9095,7 @@
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B27" s="48"/>
       <c r="C27" s="48"/>
@@ -10002,7 +9111,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="48" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B28" s="48"/>
       <c r="C28" s="48"/>
@@ -10014,13 +9123,13 @@
         <v>313280</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="48" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B29" s="48"/>
       <c r="C29" s="48"/>
@@ -10032,13 +9141,13 @@
         <v>101200</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="48" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B30" s="48"/>
       <c r="C30" s="48"/>
@@ -10050,13 +9159,13 @@
         <v>344588</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -10072,7 +9181,7 @@
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="48" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
@@ -10084,13 +9193,13 @@
         <v>1402453.4</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="I32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="48" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B33" s="48"/>
       <c r="C33" s="48"/>
@@ -10102,13 +9211,13 @@
         <v>4075728.21</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="I33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="48" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B34" s="48"/>
       <c r="C34" s="48"/>
@@ -10120,13 +9229,13 @@
         <v>-249.609999999404</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="I34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="50" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B35" s="50"/>
       <c r="C35" s="50"/>
@@ -10138,13 +9247,13 @@
         <v>33527000</v>
       </c>
       <c r="H35" s="41" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="I35" s="41"/>
     </row>
     <row r="37" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="52" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B37" s="52"/>
       <c r="C37" s="52"/>
@@ -10157,7 +9266,7 @@
     </row>
     <row r="38" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="52" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B38" s="52"/>
       <c r="C38" s="52"/>
@@ -10233,7 +9342,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -10257,7 +9366,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -10270,7 +9379,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="47" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -10283,7 +9392,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>30</v>
@@ -10307,12 +9416,12 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>80</v>
@@ -10321,7 +9430,7 @@
         <v>81</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>9</v>
@@ -10337,7 +9446,7 @@
         <v>82</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10349,7 +9458,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>6</v>
@@ -10365,7 +9474,7 @@
         <v>85</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10377,7 +9486,7 @@
         <v>87</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>4</v>
@@ -10393,7 +9502,7 @@
         <v>88</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10405,7 +9514,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>4</v>
@@ -10421,7 +9530,7 @@
         <v>88</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10433,7 +9542,7 @@
         <v>92</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>5</v>
@@ -10449,12 +9558,12 @@
         <v>93</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>94</v>
@@ -10463,7 +9572,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>9</v>
@@ -10491,7 +9600,7 @@
         <v>98</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -10510,7 +9619,7 @@
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>99</v>
@@ -10533,12 +9642,12 @@
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>101</v>
@@ -10571,7 +9680,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>22</v>
@@ -10622,7 +9731,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
@@ -10638,7 +9747,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
@@ -10654,7 +9763,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
@@ -10670,7 +9779,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
@@ -10682,13 +9791,13 @@
         <v>350660</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
@@ -10700,13 +9809,13 @@
         <v>113275</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
@@ -10718,13 +9827,13 @@
         <v>420783</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -10740,7 +9849,7 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -10752,13 +9861,13 @@
         <v>1170735.9</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B27" s="48"/>
       <c r="C27" s="48"/>
@@ -10770,13 +9879,13 @@
         <v>3135818.085</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="48" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B28" s="48"/>
       <c r="C28" s="48"/>
@@ -10788,13 +9897,13 @@
         <v>-271.984999999404</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="50" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B29" s="50"/>
       <c r="C29" s="50"/>
@@ -10806,13 +9915,13 @@
         <v>27721000</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="I29" s="41"/>
     </row>
     <row r="31" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="52" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B31" s="52"/>
       <c r="C31" s="52"/>
@@ -10825,7 +9934,7 @@
     </row>
     <row r="32" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="52" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B32" s="52"/>
       <c r="C32" s="52"/>

--- a/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
+++ b/experiments/2026-10-12-kkt-drying-furnace-base/estimate/견적서_금강변압기_진공건조로_회전안착_용접_v3.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="280">
   <si>
     <t xml:space="preserve">N M   S O L U T I O N</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">견적일자</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-13</t>
+    <t xml:space="preserve">2026-10-19</t>
   </si>
   <si>
     <t xml:space="preserve">견  적  서</t>
@@ -117,7 +117,7 @@
     <t xml:space="preserve">사업자등록번호</t>
   </si>
   <si>
-    <t xml:space="preserve">견적금액  일금 오천오백이십오만삼천원정  (₩ 55,253,000, VAT 별도)</t>
+    <t xml:space="preserve">견적금액  일금 육천삼백육십삼만육천삼백육십사원정  (₩ 63,636,364, VAT 별도)</t>
   </si>
   <si>
     <t xml:space="preserve">견적 내역</t>
@@ -147,16 +147,16 @@
     <t xml:space="preserve">비고</t>
   </si>
   <si>
-    <t xml:space="preserve">도비 작업: 회전·베이스 안착(100t·60t), 밀착 이동, 안전펜스</t>
+    <t xml:space="preserve">도비 작업: 회전·베이스 안착, 밀착, 완성품 이동 (250t 1대), 안전펜스</t>
   </si>
   <si>
     <t xml:space="preserve">도비 전문기공</t>
   </si>
   <si>
-    <t xml:space="preserve">회전·안착·밀착 이동</t>
-  </si>
-  <si>
-    <t xml:space="preserve">안착일 6명 + 밀착 이동 6명·3명 (6, 6, 3)</t>
+    <t xml:space="preserve">회전·안착·밀착·완성품 이동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안착일 6명 + 밀착 6명·3명 + 이동일 6명 (6, 6, 3, 6)</t>
   </si>
   <si>
     <t xml:space="preserve">신호수</t>
@@ -165,7 +165,7 @@
     <t xml:space="preserve">크레인 인양 신호</t>
   </si>
   <si>
-    <t xml:space="preserve">2명 × 1일 (안착일)</t>
+    <t xml:space="preserve">2명 × 2일 (안착일 + 이동일)</t>
   </si>
   <si>
     <t xml:space="preserve">안전담당 (관리감독자)</t>
@@ -174,19 +174,16 @@
     <t xml:space="preserve">작업 전 TBM·인양구역 통제</t>
   </si>
   <si>
-    <t xml:space="preserve">1명 × 3일</t>
+    <t xml:space="preserve">1명 × 4일</t>
   </si>
   <si>
     <t xml:space="preserve">크레인</t>
   </si>
   <si>
-    <t xml:space="preserve">100TON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">안착일 1일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60TON</t>
+    <t xml:space="preserve">250TON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안착일 1일 + 이동일 1일</t>
   </si>
   <si>
     <t xml:space="preserve">아웃리거 받침 철판</t>
@@ -198,13 +195,13 @@
     <t xml:space="preserve">아스팔트 지반 보호</t>
   </si>
   <si>
-    <t xml:space="preserve">밀착 이동 장비</t>
+    <t xml:space="preserve">밀착 장비</t>
   </si>
   <si>
     <t xml:space="preserve">유압잭·윈치·스키드</t>
   </si>
   <si>
-    <t xml:space="preserve">밀착 이동 2일</t>
+    <t xml:space="preserve">밀착 2일</t>
   </si>
   <si>
     <t xml:space="preserve">공구사용손료</t>
@@ -225,7 +222,7 @@
     <t xml:space="preserve">이동식 메쉬펜스 H1.8×W2.4m</t>
   </si>
   <si>
-    <t xml:space="preserve">22매(둘레 50m + 출입문) × 11일</t>
+    <t xml:space="preserve">22매(둘레 50m + 출입문) × 12일</t>
   </si>
   <si>
     <t xml:space="preserve">펜스 설치·해체</t>
@@ -348,7 +345,7 @@
     <t xml:space="preserve">산소·LPG, 2대 공정기간 상시</t>
   </si>
   <si>
-    <t xml:space="preserve">2대 × 11일</t>
+    <t xml:space="preserve">2대 × 12일</t>
   </si>
   <si>
     <t xml:space="preserve">식대·교통비·부대 잡비</t>
@@ -363,13 +360,13 @@
     <t xml:space="preserve">용접 시트 참조</t>
   </si>
   <si>
-    <t xml:space="preserve">베이스 작업: 임시 사다리형 베이스 제작·설치·회수</t>
+    <t xml:space="preserve">베이스 작업: 기존 철판 조방 위 H빔 베이스 설치·회수</t>
   </si>
   <si>
     <t xml:space="preserve">H빔 (회수조건)</t>
   </si>
   <si>
-    <t xml:space="preserve">H-250×250×9×14, 10m 4·5m 16·0.6m 30EA</t>
+    <t xml:space="preserve">H-250×250×9×14, 10m 2EA·3m 2EA</t>
   </si>
   <si>
     <t xml:space="preserve">공사 후 회수 조건</t>
@@ -384,7 +381,7 @@
     <t xml:space="preserve">시공자</t>
   </si>
   <si>
-    <t xml:space="preserve">베이스 제작·설치</t>
+    <t xml:space="preserve">베이스 배치·용접·회수</t>
   </si>
   <si>
     <t xml:space="preserve">3명 × 1일</t>
@@ -396,6 +393,15 @@
     <t xml:space="preserve">베이스 시트 참조</t>
   </si>
   <si>
+    <t xml:space="preserve">공종 합계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">협의 조정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">발주처 협의 금액 반영</t>
+  </si>
+  <si>
     <t xml:space="preserve">공급가액</t>
   </si>
   <si>
@@ -408,16 +414,16 @@
     <t xml:space="preserve">특기사항</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 공사 기간: 2026.10.21 ~ 2026.11.02 (가정 일정, 작업일 11일, 공정표 시트 참조). 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. 결제 조건: 선수금 30% (계약 시), 중도금 30% (회전·안착 완료 시), 잔금 40% (용접 완료 후). VAT 포함 기준 18,233,490원 / 18,233,490원 / 24,311,320원.</t>
+    <t xml:space="preserve">1. 공사 기간: 2026.10.21 ~ 2026.11.03 (가정 일정, 작업일 12일, 공정표 시트 참조). 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. 결제 조건: 선수금 30% (계약 시), 중도금 30% (회전·안착 완료 시), 잔금 40% (완성품 이동 완료 후). VAT 포함 기준 21,000,000원 / 21,000,000원 / 28,000,000원.</t>
   </si>
   <si>
     <t xml:space="preserve">3. 견적 유효기간: 발행일로부터 30일.</t>
   </si>
   <si>
-    <t xml:space="preserve">4. 포함: 임시 베이스 제작·설치·회수, 이동식 크레인(100t·60t)·도비, 접합면 사상, CO2 용접, 화재감시, 안전펜스·출입통제.</t>
+    <t xml:space="preserve">4. 포함: 임시 베이스 설치·회수, 이동식 크레인(250t 1대)·도비, 접합면 사상, CO2 용접, 화재감시, 완성품 지정 장소 이동, 안전펜스·출입통제.</t>
   </si>
   <si>
     <t xml:space="preserve">5. 제외: 전기 수전, 배관·닥트 해체·복구, 보온, 도장, 비파괴검사(PT/UT), 시운전. 비파괴검사는 발주처 요구 시 별도 정산함.</t>
@@ -435,7 +441,7 @@
     <t xml:space="preserve">위와 같이 견적합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026년 10월 13일</t>
+    <t xml:space="preserve">2026년 10월 19일</t>
   </si>
   <si>
     <t xml:space="preserve">엔엠솔루션   대표 김성배   (인)</t>
@@ -561,30 +567,27 @@
     <t xml:space="preserve">금액(원)</t>
   </si>
   <si>
-    <t xml:space="preserve">(6 + 6 + 3)명 × 300,000원</t>
+    <t xml:space="preserve">(6 + 6 + 3 + 6)명 × 300,000원</t>
   </si>
   <si>
     <t xml:space="preserve">인원·일수: 작업 범위·공정표 기준 / 단가: 중량물 도비 전문기공 시장 단가</t>
   </si>
   <si>
-    <t xml:space="preserve">2명 × 1일 × 260,000원</t>
+    <t xml:space="preserve">2명 × 2일 × 260,000원</t>
   </si>
   <si>
     <t xml:space="preserve">크레인 인양 작업 안전관리 인력, 단가: 시장 단가</t>
   </si>
   <si>
-    <t xml:space="preserve">1명 × 3일 × 320,000원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1대 × 1일 × 2,400,000원</t>
+    <t xml:space="preserve">1명 × 4일 × 320,000원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1대 × 2일 × 5,000,000원</t>
   </si>
   <si>
     <t xml:space="preserve">이동식 크레인 1일 임대 시장 단가 (운전원 포함)</t>
   </si>
   <si>
-    <t xml:space="preserve">1대 × 1일 × 1,700,000원</t>
-  </si>
-  <si>
     <t xml:space="preserve">8매 × 80,000원</t>
   </si>
   <si>
@@ -603,7 +606,7 @@
     <t xml:space="preserve">자재 시장 단가, 작업 범위 기준 1식</t>
   </si>
   <si>
-    <t xml:space="preserve">작업구역 10×15m, 둘레 50m ÷ 2.4m = 21매 + 출입문 1매 → 22매 × 11일 × 5,000원</t>
+    <t xml:space="preserve">작업구역 10×15m, 둘레 50m ÷ 2.4m = 21매 + 출입문 1매 → 22매 × 12일 × 5,000원</t>
   </si>
   <si>
     <t xml:space="preserve">작업구역 둘레 기준 수량 × 임대 시장 단가</t>
@@ -633,9 +636,6 @@
     <t xml:space="preserve">법정 요율·일반관리비·이윤 (원가계산서 하단 참조)</t>
   </si>
   <si>
-    <t xml:space="preserve">공종 합계</t>
-  </si>
-  <si>
     <t xml:space="preserve">부가세 별도</t>
   </si>
   <si>
@@ -663,7 +663,7 @@
     <t xml:space="preserve">1식 (용접재 3,000,000 + 전원 케이블·잡자재 680,000)</t>
   </si>
   <si>
-    <t xml:space="preserve">2대 × 11일 × 100,000원</t>
+    <t xml:space="preserve">2대 × 12일 × 100,000원</t>
   </si>
   <si>
     <t xml:space="preserve">28인·일 기준 1식</t>
@@ -672,10 +672,10 @@
     <t xml:space="preserve">투입 인·일 기준 현장 부대비</t>
   </si>
   <si>
-    <t xml:space="preserve">1식 (9,991kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H빔 9,991kg (베이스자재 시트), 공사 후 회수 조건 1식</t>
+    <t xml:space="preserve">1식 (1,882kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H빔 1,882kg (베이스자재 시트), 공사 후 회수 조건 1식</t>
   </si>
   <si>
     <t xml:space="preserve">화물 운반 시장 단가 (반입·회수)</t>
@@ -687,10 +687,10 @@
     <t xml:space="preserve">공 종 별   내 역 서</t>
   </si>
   <si>
-    <t xml:space="preserve">견적번호 NM-2610-01   |   견적일 2026-10-13   |   주식회사 금강변압기 귀중</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공 종 : 진공건조로 2기 회전·베이스 안착(1일), 용접면 밀착 이동(2일), 작업구역 안전펜스</t>
+    <t xml:space="preserve">견적번호 NM-2610-01   |   견적일 2026-10-19   |   주식회사 금강변압기 귀중</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공 종 : 진공건조로 2기 회전·베이스 안착(1일), 용접면 밀착(2일), 완성품 이동(1일), 작업구역 안전펜스</t>
   </si>
   <si>
     <t xml:space="preserve">구분</t>
@@ -753,7 +753,7 @@
     <t xml:space="preserve">공 종 : 접합면 사상(2일) 및 접합부 CO2 용접(3일)</t>
   </si>
   <si>
-    <t xml:space="preserve">공 종 : 사다리형 일체 임시 베이스 제작·설치 및 공사 후 회수, H-250×250</t>
+    <t xml:space="preserve">공 종 : 기존 철판 조방 위 H빔 임시 베이스 설치 및 공사 후 회수, H-250×250</t>
   </si>
   <si>
     <t xml:space="preserve">운반비</t>
@@ -783,10 +783,10 @@
     <t xml:space="preserve">공사 후 회수, 사용 기간 손료 개념</t>
   </si>
   <si>
-    <t xml:space="preserve">단위중량 72.4 kg/m는 KS H-250×250×9×14 공칭값임. 베이스는 임시 구조물로 방청·도장 미적용.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공정표 (가정 일정 2026.10.21 ~ 11.02, 작업일 11일)</t>
+    <t xml:space="preserve">기존 철판 조방 위에 10m H빔 2본을 길이 방향으로 놓고, 양 끝에 3m H빔을 직각으로 용접함. 단위중량 72.4 kg/m는 KS H-250×250×9×14 공칭값. 임시 구조물로 방청·도장 미적용.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공정표 (가정 일정 2026.10.21 ~ 11.03, 작업일 12일)</t>
   </si>
   <si>
     <t xml:space="preserve">공정</t>
@@ -839,16 +839,23 @@
 월</t>
   </si>
   <si>
+    <t xml:space="preserve">11/3
+화</t>
+  </si>
+  <si>
     <t xml:space="preserve">안전펜스 설치·작업구역 통제</t>
   </si>
   <si>
     <t xml:space="preserve">조공 2명</t>
   </si>
   <si>
-    <t xml:space="preserve">시공자 3명</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회전·베이스 안착 (100t + 60t)</t>
+    <t xml:space="preserve">베이스 설치 (H빔 배치·용접)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시공자 4명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회전·베이스 안착 (250t)</t>
   </si>
   <si>
     <t xml:space="preserve">도비 6명, 신호수 2, 안전담당</t>
@@ -860,7 +867,7 @@
     <t xml:space="preserve">사상 2, 조공 2, 화재감시 1</t>
   </si>
   <si>
-    <t xml:space="preserve">용접면 밀착 이동</t>
+    <t xml:space="preserve">용접면 밀착</t>
   </si>
   <si>
     <t xml:space="preserve">도비 6명·3명, 안전담당</t>
@@ -872,10 +879,13 @@
     <t xml:space="preserve">용접사 3, 고급기술자 2, 화재감시 1</t>
   </si>
   <si>
+    <t xml:space="preserve">완성품 이동 (250t)·베이스 회수</t>
+  </si>
+  <si>
     <t xml:space="preserve">펜스 해체·정리</t>
   </si>
   <si>
-    <t xml:space="preserve">가정 일정: 2026-10-21(수) 착공 ~ 11-02(월) 완료, 일요일 휴무 기준 작업일 11일. 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
+    <t xml:space="preserve">가정 일정: 2026-10-21(수) 착공 ~ 11-03(화) 완료, 일요일 휴무 기준 작업일 12일. 날짜는 가정이며 착공일은 발주처 협의로 확정함.</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1184,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1309,6 +1319,10 @@
     </xf>
     <xf numFmtId="166" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1675,7 +1689,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -1905,7 +1919,7 @@
       </c>
       <c r="E18" s="14" t="n">
         <f aca="false">도비!E8</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F18" s="11" t="str">
         <f aca="false">도비!D8</f>
@@ -1917,7 +1931,7 @@
       </c>
       <c r="H18" s="14" t="n">
         <f aca="false">도비!G8</f>
-        <v>4500000</v>
+        <v>6300000</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>40</v>
@@ -1936,7 +1950,7 @@
       </c>
       <c r="E19" s="14" t="n">
         <f aca="false">도비!E9</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" s="11" t="str">
         <f aca="false">도비!D9</f>
@@ -1948,7 +1962,7 @@
       </c>
       <c r="H19" s="14" t="n">
         <f aca="false">도비!G9</f>
-        <v>520000</v>
+        <v>1040000</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>43</v>
@@ -1967,7 +1981,7 @@
       </c>
       <c r="E20" s="14" t="n">
         <f aca="false">도비!E10</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="11" t="str">
         <f aca="false">도비!D10</f>
@@ -1979,7 +1993,7 @@
       </c>
       <c r="H20" s="14" t="n">
         <f aca="false">도비!G10</f>
-        <v>960000</v>
+        <v>1280000</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>46</v>
@@ -1998,7 +2012,7 @@
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">도비!E11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="11" t="str">
         <f aca="false">도비!D11</f>
@@ -2006,11 +2020,11 @@
       </c>
       <c r="G21" s="14" t="n">
         <f aca="false">도비!F11</f>
-        <v>2400000</v>
+        <v>5000000</v>
       </c>
       <c r="H21" s="14" t="n">
         <f aca="false">도비!G11</f>
-        <v>2400000</v>
+        <v>10000000</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>49</v>
@@ -2021,11 +2035,11 @@
         <v>5</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">도비!E12</f>
@@ -2033,18 +2047,18 @@
       </c>
       <c r="F22" s="11" t="str">
         <f aca="false">도비!D12</f>
-        <v>대·일</v>
+        <v>식</v>
       </c>
       <c r="G22" s="14" t="n">
         <f aca="false">도비!F12</f>
-        <v>1700000</v>
+        <v>640000</v>
       </c>
       <c r="H22" s="14" t="n">
         <f aca="false">도비!G12</f>
-        <v>1700000</v>
+        <v>640000</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2052,11 +2066,11 @@
         <v>6</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E23" s="14" t="n">
         <f aca="false">도비!E13</f>
@@ -2064,18 +2078,18 @@
       </c>
       <c r="F23" s="11" t="str">
         <f aca="false">도비!D13</f>
-        <v>식</v>
+        <v>SET</v>
       </c>
       <c r="G23" s="14" t="n">
         <f aca="false">도비!F13</f>
-        <v>640000</v>
+        <v>2000000</v>
       </c>
       <c r="H23" s="14" t="n">
         <f aca="false">도비!G13</f>
-        <v>640000</v>
+        <v>2000000</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2083,11 +2097,11 @@
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">도비!E14</f>
@@ -2099,26 +2113,24 @@
       </c>
       <c r="G24" s="14" t="n">
         <f aca="false">도비!F14</f>
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="H24" s="14" t="n">
         <f aca="false">도비!G14</f>
-        <v>2000000</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>56</v>
-      </c>
+        <v>3000000</v>
+      </c>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">도비!E15</f>
@@ -2126,15 +2138,15 @@
       </c>
       <c r="F25" s="11" t="str">
         <f aca="false">도비!D15</f>
-        <v>SET</v>
+        <v>식</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">도비!F15</f>
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="H25" s="14" t="n">
         <f aca="false">도비!G15</f>
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="I25" s="13"/>
     </row>
@@ -2143,59 +2155,61 @@
         <v>9</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26" s="14" t="n">
         <f aca="false">도비!E16</f>
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="F26" s="11" t="str">
         <f aca="false">도비!D16</f>
-        <v>식</v>
+        <v>매·일</v>
       </c>
       <c r="G26" s="14" t="n">
         <f aca="false">도비!F16</f>
-        <v>1000000</v>
+        <v>5000</v>
       </c>
       <c r="H26" s="14" t="n">
         <f aca="false">도비!G16</f>
-        <v>1000000</v>
-      </c>
-      <c r="I26" s="13"/>
+        <v>1320000</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E27" s="14" t="n">
         <f aca="false">도비!E17</f>
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="F27" s="11" t="str">
         <f aca="false">도비!D17</f>
-        <v>매·일</v>
+        <v>인·일</v>
       </c>
       <c r="G27" s="14" t="n">
         <f aca="false">도비!F17</f>
-        <v>5000</v>
+        <v>250000</v>
       </c>
       <c r="H27" s="14" t="n">
         <f aca="false">도비!G17</f>
-        <v>1210000</v>
+        <v>500000</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2203,11 +2217,11 @@
         <v>11</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E28" s="14" t="n">
         <f aca="false">도비!E18</f>
@@ -2215,18 +2229,18 @@
       </c>
       <c r="F28" s="11" t="str">
         <f aca="false">도비!D18</f>
-        <v>인·일</v>
+        <v>회</v>
       </c>
       <c r="G28" s="14" t="n">
         <f aca="false">도비!F18</f>
-        <v>250000</v>
+        <v>260000</v>
       </c>
       <c r="H28" s="14" t="n">
         <f aca="false">도비!G18</f>
-        <v>500000</v>
+        <v>520000</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2234,31 +2248,27 @@
         <v>12</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C29" s="13"/>
-      <c r="D29" s="13" t="s">
-        <v>68</v>
-      </c>
+      <c r="D29" s="13"/>
       <c r="E29" s="14" t="n">
         <f aca="false">도비!E19</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="11" t="str">
         <f aca="false">도비!D19</f>
-        <v>회</v>
+        <v>식</v>
       </c>
       <c r="G29" s="14" t="n">
         <f aca="false">도비!F19</f>
-        <v>260000</v>
+        <v>380000</v>
       </c>
       <c r="H29" s="14" t="n">
         <f aca="false">도비!G19</f>
-        <v>520000</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>69</v>
-      </c>
+        <v>380000</v>
+      </c>
+      <c r="I29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="n">
@@ -2268,7 +2278,9 @@
         <v>70</v>
       </c>
       <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
+      <c r="D30" s="13" t="s">
+        <v>71</v>
+      </c>
       <c r="E30" s="14" t="n">
         <f aca="false">도비!E20</f>
         <v>1</v>
@@ -2279,11 +2291,11 @@
       </c>
       <c r="G30" s="14" t="n">
         <f aca="false">도비!F20</f>
-        <v>380000</v>
+        <v>600000</v>
       </c>
       <c r="H30" s="14" t="n">
         <f aca="false">도비!G20</f>
-        <v>380000</v>
+        <v>600000</v>
       </c>
       <c r="I30" s="13"/>
     </row>
@@ -2292,119 +2304,121 @@
         <v>14</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E31" s="14" t="n">
-        <f aca="false">도비!E21</f>
         <v>1</v>
       </c>
-      <c r="F31" s="11" t="str">
-        <f aca="false">도비!D21</f>
-        <v>식</v>
+      <c r="F31" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="G31" s="14" t="n">
-        <f aca="false">도비!F21</f>
-        <v>600000</v>
+        <f aca="false">H31</f>
+        <v>6636000</v>
       </c>
       <c r="H31" s="14" t="n">
-        <f aca="false">도비!G21</f>
-        <v>600000</v>
-      </c>
-      <c r="I31" s="13"/>
+        <f aca="false">도비!$G$31-도비!$G$21-도비!$G$22-도비!$G$23</f>
+        <v>6636000</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="16" t="n">
+        <f aca="false">도비!$G$31</f>
+        <v>35216000</v>
+      </c>
+      <c r="I32" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <f aca="false">H32</f>
-        <v>4592000</v>
-      </c>
-      <c r="H32" s="14" t="n">
-        <f aca="false">도비!$G$32-도비!$G$22-도비!$G$23-도비!$G$24</f>
-        <v>4592000</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="16" t="n">
-        <f aca="false">도비!$G$32</f>
-        <v>24522000</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <f aca="false">용접!E8</f>
+        <v>9</v>
+      </c>
+      <c r="F34" s="11" t="str">
+        <f aca="false">용접!D8</f>
+        <v>인·일</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <f aca="false">용접!F8</f>
+        <v>500000</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <f aca="false">용접!G8</f>
+        <v>4500000</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="n">
         <v>16</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E35" s="14" t="n">
-        <f aca="false">용접!E8</f>
-        <v>9</v>
+        <f aca="false">용접!E9</f>
+        <v>6</v>
       </c>
       <c r="F35" s="11" t="str">
-        <f aca="false">용접!D8</f>
+        <f aca="false">용접!D9</f>
         <v>인·일</v>
       </c>
       <c r="G35" s="14" t="n">
-        <f aca="false">용접!F8</f>
-        <v>500000</v>
+        <f aca="false">용접!F9</f>
+        <v>350000</v>
       </c>
       <c r="H35" s="14" t="n">
-        <f aca="false">용접!G8</f>
-        <v>4500000</v>
+        <f aca="false">용접!G9</f>
+        <v>2100000</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2412,30 +2426,30 @@
         <v>17</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E36" s="14" t="n">
-        <f aca="false">용접!E9</f>
-        <v>6</v>
+        <f aca="false">용접!E10</f>
+        <v>4</v>
       </c>
       <c r="F36" s="11" t="str">
-        <f aca="false">용접!D9</f>
+        <f aca="false">용접!D10</f>
         <v>인·일</v>
       </c>
       <c r="G36" s="14" t="n">
-        <f aca="false">용접!F9</f>
-        <v>350000</v>
+        <f aca="false">용접!F10</f>
+        <v>300000</v>
       </c>
       <c r="H36" s="14" t="n">
-        <f aca="false">용접!G9</f>
-        <v>2100000</v>
+        <f aca="false">용접!G10</f>
+        <v>1200000</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2443,30 +2457,30 @@
         <v>18</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <f aca="false">용접!E11</f>
+        <v>4</v>
+      </c>
+      <c r="F37" s="11" t="str">
+        <f aca="false">용접!D11</f>
+        <v>인·일</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <f aca="false">용접!F11</f>
+        <v>200000</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <f aca="false">용접!G11</f>
+        <v>800000</v>
+      </c>
+      <c r="I37" s="13" t="s">
         <v>87</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <f aca="false">용접!E10</f>
-        <v>4</v>
-      </c>
-      <c r="F37" s="11" t="str">
-        <f aca="false">용접!D10</f>
-        <v>인·일</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <f aca="false">용접!F10</f>
-        <v>300000</v>
-      </c>
-      <c r="H37" s="14" t="n">
-        <f aca="false">용접!G10</f>
-        <v>1200000</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2474,30 +2488,30 @@
         <v>19</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E38" s="14" t="n">
-        <f aca="false">용접!E11</f>
-        <v>4</v>
+        <f aca="false">용접!E12</f>
+        <v>5</v>
       </c>
       <c r="F38" s="11" t="str">
-        <f aca="false">용접!D11</f>
+        <f aca="false">용접!D12</f>
         <v>인·일</v>
       </c>
       <c r="G38" s="14" t="n">
-        <f aca="false">용접!F11</f>
-        <v>200000</v>
+        <f aca="false">용접!F12</f>
+        <v>250000</v>
       </c>
       <c r="H38" s="14" t="n">
-        <f aca="false">용접!G11</f>
-        <v>800000</v>
+        <f aca="false">용접!G12</f>
+        <v>1250000</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2505,30 +2519,30 @@
         <v>20</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E39" s="14" t="n">
-        <f aca="false">용접!E12</f>
-        <v>5</v>
+        <f aca="false">용접!E13</f>
+        <v>9</v>
       </c>
       <c r="F39" s="11" t="str">
-        <f aca="false">용접!D12</f>
-        <v>인·일</v>
+        <f aca="false">용접!D13</f>
+        <v>대·일</v>
       </c>
       <c r="G39" s="14" t="n">
-        <f aca="false">용접!F12</f>
-        <v>250000</v>
+        <f aca="false">용접!F13</f>
+        <v>400000</v>
       </c>
       <c r="H39" s="14" t="n">
-        <f aca="false">용접!G12</f>
-        <v>1250000</v>
+        <f aca="false">용접!G13</f>
+        <v>3600000</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2536,58 +2550,56 @@
         <v>21</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E40" s="14" t="n">
-        <f aca="false">용접!E13</f>
-        <v>9</v>
+        <f aca="false">용접!E14</f>
+        <v>1</v>
       </c>
       <c r="F40" s="11" t="str">
-        <f aca="false">용접!D13</f>
-        <v>대·일</v>
+        <f aca="false">용접!D14</f>
+        <v>SET</v>
       </c>
       <c r="G40" s="14" t="n">
-        <f aca="false">용접!F13</f>
-        <v>400000</v>
+        <f aca="false">용접!F14</f>
+        <v>800000</v>
       </c>
       <c r="H40" s="14" t="n">
-        <f aca="false">용접!G13</f>
-        <v>3600000</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>96</v>
-      </c>
+        <f aca="false">용접!G14</f>
+        <v>800000</v>
+      </c>
+      <c r="I40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="n">
         <v>22</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E41" s="14" t="n">
-        <f aca="false">용접!E14</f>
+        <f aca="false">용접!E15</f>
         <v>1</v>
       </c>
       <c r="F41" s="11" t="str">
-        <f aca="false">용접!D14</f>
-        <v>SET</v>
+        <f aca="false">용접!D15</f>
+        <v>식</v>
       </c>
       <c r="G41" s="14" t="n">
-        <f aca="false">용접!F14</f>
-        <v>800000</v>
+        <f aca="false">용접!F15</f>
+        <v>3680000</v>
       </c>
       <c r="H41" s="14" t="n">
-        <f aca="false">용접!G14</f>
-        <v>800000</v>
+        <f aca="false">용접!G15</f>
+        <v>3680000</v>
       </c>
       <c r="I41" s="13"/>
     </row>
@@ -2596,27 +2608,25 @@
         <v>23</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" s="13"/>
-      <c r="D42" s="13" t="s">
-        <v>100</v>
-      </c>
+      <c r="D42" s="13"/>
       <c r="E42" s="14" t="n">
-        <f aca="false">용접!E15</f>
+        <f aca="false">용접!E16</f>
         <v>1</v>
       </c>
       <c r="F42" s="11" t="str">
-        <f aca="false">용접!D15</f>
+        <f aca="false">용접!D16</f>
         <v>식</v>
       </c>
       <c r="G42" s="14" t="n">
-        <f aca="false">용접!F15</f>
-        <v>3680000</v>
+        <f aca="false">용접!F16</f>
+        <v>1000000</v>
       </c>
       <c r="H42" s="14" t="n">
-        <f aca="false">용접!G15</f>
-        <v>3680000</v>
+        <f aca="false">용접!G16</f>
+        <v>1000000</v>
       </c>
       <c r="I42" s="13"/>
     </row>
@@ -2628,54 +2638,58 @@
         <v>101</v>
       </c>
       <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
+      <c r="D43" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="E43" s="14" t="n">
-        <f aca="false">용접!E16</f>
-        <v>1</v>
+        <f aca="false">용접!E17</f>
+        <v>24</v>
       </c>
       <c r="F43" s="11" t="str">
-        <f aca="false">용접!D16</f>
-        <v>식</v>
+        <f aca="false">용접!D17</f>
+        <v>대·일</v>
       </c>
       <c r="G43" s="14" t="n">
-        <f aca="false">용접!F16</f>
-        <v>1000000</v>
+        <f aca="false">용접!F17</f>
+        <v>100000</v>
       </c>
       <c r="H43" s="14" t="n">
-        <f aca="false">용접!G16</f>
-        <v>1000000</v>
-      </c>
-      <c r="I43" s="13"/>
+        <f aca="false">용접!G17</f>
+        <v>2400000</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="n">
         <v>25</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E44" s="14" t="n">
-        <f aca="false">용접!E17</f>
-        <v>22</v>
+        <f aca="false">용접!E18</f>
+        <v>1</v>
       </c>
       <c r="F44" s="11" t="str">
-        <f aca="false">용접!D17</f>
-        <v>대·일</v>
+        <f aca="false">용접!D18</f>
+        <v>식</v>
       </c>
       <c r="G44" s="14" t="n">
-        <f aca="false">용접!F17</f>
-        <v>100000</v>
+        <f aca="false">용접!F18</f>
+        <v>1400000</v>
       </c>
       <c r="H44" s="14" t="n">
-        <f aca="false">용접!G17</f>
-        <v>2200000</v>
+        <f aca="false">용접!G18</f>
+        <v>1400000</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2683,200 +2697,185 @@
         <v>26</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="13" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="E45" s="14" t="n">
-        <f aca="false">용접!E18</f>
         <v>1</v>
       </c>
-      <c r="F45" s="11" t="str">
-        <f aca="false">용접!D18</f>
+      <c r="F45" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <f aca="false">H45</f>
+        <v>5232000</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <f aca="false">용접!$G$29-용접!$G$19-용접!$G$20-용접!$G$21</f>
+        <v>5232000</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="16" t="n">
+        <f aca="false">용접!$G$29</f>
+        <v>27962000</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="11"/>
+      <c r="B47" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <f aca="false">베이스!E8</f>
+        <v>1</v>
+      </c>
+      <c r="F48" s="11" t="str">
+        <f aca="false">베이스!D8</f>
         <v>식</v>
       </c>
-      <c r="G45" s="14" t="n">
-        <f aca="false">용접!F18</f>
-        <v>1400000</v>
-      </c>
-      <c r="H45" s="14" t="n">
-        <f aca="false">용접!G18</f>
-        <v>1400000</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G46" s="14" t="n">
-        <f aca="false">H46</f>
-        <v>5191000</v>
-      </c>
-      <c r="H46" s="14" t="n">
-        <f aca="false">용접!$G$29-용접!$G$19-용접!$G$20-용접!$G$21</f>
-        <v>5191000</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="16" t="n">
-        <f aca="false">용접!$G$29</f>
-        <v>27721000</v>
-      </c>
-      <c r="I47" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
+      <c r="G48" s="14" t="n">
+        <f aca="false">베이스!F8</f>
+        <v>1800000</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <f aca="false">베이스!G8</f>
+        <v>1800000</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="n">
         <v>28</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E49" s="14" t="n">
-        <f aca="false">베이스!E8</f>
+        <f aca="false">베이스!E9</f>
         <v>1</v>
       </c>
       <c r="F49" s="11" t="str">
-        <f aca="false">베이스!D8</f>
+        <f aca="false">베이스!D9</f>
         <v>식</v>
       </c>
       <c r="G49" s="14" t="n">
-        <f aca="false">베이스!F8</f>
-        <v>1800000</v>
+        <f aca="false">베이스!F9</f>
+        <v>160000</v>
       </c>
       <c r="H49" s="14" t="n">
-        <f aca="false">베이스!G8</f>
-        <v>1800000</v>
-      </c>
-      <c r="I49" s="13" t="s">
-        <v>112</v>
-      </c>
+        <f aca="false">베이스!G9</f>
+        <v>160000</v>
+      </c>
+      <c r="I49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="n">
         <v>29</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E50" s="14" t="n">
-        <f aca="false">베이스!E9</f>
-        <v>1</v>
-      </c>
-      <c r="F50" s="11" t="str">
-        <f aca="false">베이스!D9</f>
-        <v>식</v>
-      </c>
-      <c r="G50" s="14" t="n">
-        <f aca="false">베이스!F9</f>
-        <v>160000</v>
-      </c>
-      <c r="H50" s="14" t="n">
-        <f aca="false">베이스!G9</f>
-        <v>160000</v>
-      </c>
-      <c r="I50" s="13"/>
-    </row>
-    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E51" s="14" t="n">
         <f aca="false">베이스!E10</f>
         <v>3</v>
       </c>
-      <c r="F51" s="11" t="str">
+      <c r="F50" s="11" t="str">
         <f aca="false">베이스!D10</f>
         <v>인·일</v>
       </c>
-      <c r="G51" s="14" t="n">
+      <c r="G50" s="14" t="n">
         <f aca="false">베이스!F10</f>
         <v>350000</v>
       </c>
-      <c r="H51" s="14" t="n">
+      <c r="H50" s="14" t="n">
         <f aca="false">베이스!G10</f>
         <v>1050000</v>
       </c>
-      <c r="I51" s="13" t="s">
+      <c r="I50" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="16" t="n">
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="16" t="n">
         <f aca="false">베이스!$G$21</f>
         <v>3010000</v>
       </c>
-      <c r="I52" s="17" t="s">
+      <c r="I51" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="18" t="s">
         <v>119</v>
       </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="19" t="n">
+        <f aca="false">H32+H46+H51</f>
+        <v>66188000</v>
+      </c>
+      <c r="I52" s="20"/>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="s">
@@ -2889,14 +2888,15 @@
       <c r="F53" s="18"/>
       <c r="G53" s="18"/>
       <c r="H53" s="19" t="n">
-        <f aca="false">H33+H47+H52</f>
-        <v>55253000</v>
-      </c>
-      <c r="I53" s="20"/>
+        <v>-2551636</v>
+      </c>
+      <c r="I53" s="20" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
@@ -2905,48 +2905,51 @@
       <c r="F54" s="18"/>
       <c r="G54" s="18"/>
       <c r="H54" s="19" t="n">
-        <f aca="false">H53*0.1</f>
-        <v>5525300</v>
+        <f aca="false">H52+H53</f>
+        <v>63636364</v>
       </c>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="22" t="n">
-        <f aca="false">H53+H54</f>
-        <v>60778300</v>
-      </c>
-      <c r="I55" s="23"/>
-    </row>
-    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="18" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="24" t="s">
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="19" t="n">
+        <f aca="false">ROUND(H54*0.1,0)</f>
+        <v>6363636</v>
+      </c>
+      <c r="I55" s="20"/>
+    </row>
+    <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-      <c r="I58" s="24"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="22" t="n">
+        <f aca="false">H54+H55</f>
+        <v>70000000</v>
+      </c>
+      <c r="I56" s="23"/>
+    </row>
+    <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B59" s="24"/>
       <c r="C59" s="24"/>
@@ -2957,9 +2960,9 @@
       <c r="H59" s="24"/>
       <c r="I59" s="24"/>
     </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B60" s="24"/>
       <c r="C60" s="24"/>
@@ -2970,9 +2973,9 @@
       <c r="H60" s="24"/>
       <c r="I60" s="24"/>
     </row>
-    <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B61" s="24"/>
       <c r="C61" s="24"/>
@@ -2985,7 +2988,7 @@
     </row>
     <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B62" s="24"/>
       <c r="C62" s="24"/>
@@ -2996,9 +2999,9 @@
       <c r="H62" s="24"/>
       <c r="I62" s="24"/>
     </row>
-    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B63" s="24"/>
       <c r="C63" s="24"/>
@@ -3009,9 +3012,9 @@
       <c r="H63" s="24"/>
       <c r="I63" s="24"/>
     </row>
-    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B64" s="24"/>
       <c r="C64" s="24"/>
@@ -3022,9 +3025,9 @@
       <c r="H64" s="24"/>
       <c r="I64" s="24"/>
     </row>
-    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B65" s="24"/>
       <c r="C65" s="24"/>
@@ -3035,22 +3038,22 @@
       <c r="H65" s="24"/>
       <c r="I65" s="24"/>
     </row>
-    <row r="67" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25"/>
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
     </row>
     <row r="68" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B68" s="25"/>
       <c r="C68" s="25"/>
@@ -3061,34 +3064,47 @@
       <c r="H68" s="25"/>
       <c r="I68" s="25"/>
     </row>
-    <row r="69" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="26"/>
-    </row>
-    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="27" t="s">
+    <row r="69" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="27"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+    </row>
+    <row r="70" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+    </row>
+    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="27"/>
+      <c r="C72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="74">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B6:D6"/>
@@ -3126,9 +3142,9 @@
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
@@ -3140,17 +3156,17 @@
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B48:C48"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A52:G52"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A61:I61"/>
@@ -3158,10 +3174,11 @@
     <mergeCell ref="A63:I63"/>
     <mergeCell ref="A64:I64"/>
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A72:I72"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.629861111111111" right="0.629861111111111" top="0.709722222222222" bottom="0.709722222222222" header="0.511811023622047" footer="0.35"/>
@@ -3178,7 +3195,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -3189,7 +3206,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -3207,7 +3224,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -3217,30 +3234,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B6" s="14" t="n">
-        <f aca="false">도비!$G$22</f>
+        <f aca="false">도비!$G$21</f>
         <v>1380000</v>
       </c>
       <c r="C6" s="14" t="n">
@@ -3257,16 +3274,16 @@
       </c>
       <c r="F6" s="32" t="n">
         <f aca="false">E6/$E$16</f>
-        <v>0.124156154416955</v>
+        <v>0.103644165105457</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B7" s="14" t="n">
-        <f aca="false">도비!$G$23</f>
-        <v>6480000</v>
+        <f aca="false">도비!$G$22</f>
+        <v>9120000</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">용접!$G$20</f>
@@ -3278,24 +3295,24 @@
       </c>
       <c r="E7" s="31" t="n">
         <f aca="false">SUM(B7:D7)</f>
-        <v>17380000</v>
+        <v>20020000</v>
       </c>
       <c r="F7" s="32" t="n">
         <f aca="false">E7/$E$16</f>
-        <v>0.314553055942664</v>
+        <v>0.302471747144498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="14" t="n">
-        <f aca="false">도비!$G$24</f>
-        <v>12070000</v>
+        <f aca="false">도비!$G$23</f>
+        <v>18080000</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">용접!$G$21</f>
-        <v>9000000</v>
+        <v>9200000</v>
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">베이스!$G$13</f>
@@ -3303,20 +3320,20 @@
       </c>
       <c r="E8" s="31" t="n">
         <f aca="false">SUM(B8:D8)</f>
-        <v>21230000</v>
+        <v>27440000</v>
       </c>
       <c r="F8" s="32" t="n">
         <f aca="false">E8/$E$16</f>
-        <v>0.384232530360342</v>
+        <v>0.414576660421829</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B9" s="14" t="n">
-        <f aca="false">도비!$G$25</f>
-        <v>230688</v>
+        <f aca="false">도비!$G$24</f>
+        <v>324672</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">용접!$G$22</f>
@@ -3328,20 +3345,20 @@
       </c>
       <c r="E9" s="31" t="n">
         <f aca="false">SUM(B9:D9)</f>
-        <v>581348</v>
+        <v>675332</v>
       </c>
       <c r="F9" s="32" t="n">
         <f aca="false">E9/$E$16</f>
-        <v>0.0105215644399399</v>
+        <v>0.0102032392578715</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B10" s="14" t="n">
-        <f aca="false">도비!$G$26</f>
-        <v>74520</v>
+        <f aca="false">도비!$G$25</f>
+        <v>104880</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">용접!$G$23</f>
@@ -3353,20 +3370,20 @@
       </c>
       <c r="E10" s="31" t="n">
         <f aca="false">SUM(B10:D10)</f>
-        <v>187795</v>
+        <v>218155</v>
       </c>
       <c r="F10" s="32" t="n">
         <f aca="false">E10/$E$16</f>
-        <v>0.0033988199735761</v>
+        <v>0.00329599020970569</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B11" s="14" t="n">
-        <f aca="false">도비!$G$27</f>
-        <v>244446</v>
+        <f aca="false">도비!$G$26</f>
+        <v>326550</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">용접!$G$24</f>
@@ -3378,24 +3395,24 @@
       </c>
       <c r="E11" s="31" t="n">
         <f aca="false">SUM(B11:D11)</f>
-        <v>665229</v>
+        <v>747333</v>
       </c>
       <c r="F11" s="32" t="n">
         <f aca="false">E11/$E$16</f>
-        <v>0.0120396901525709</v>
+        <v>0.0112910648455913</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B12" s="19" t="n">
-        <f aca="false">도비!$G$28</f>
-        <v>20479654</v>
+        <f aca="false">도비!$G$27</f>
+        <v>29336102</v>
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">용접!$G$25</f>
-        <v>23414718</v>
+        <v>23614718</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">베이스!$G$17</f>
@@ -3403,24 +3420,24 @@
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">SUM(B12:D12)</f>
-        <v>46904372</v>
+        <v>55960820</v>
       </c>
       <c r="F12" s="33" t="n">
         <f aca="false">E12/$E$16</f>
-        <v>0.848901815286048</v>
+        <v>0.845482866984952</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B13" s="14" t="n">
-        <f aca="false">도비!$G$29</f>
-        <v>1023982.7</v>
+        <f aca="false">도비!$G$28</f>
+        <v>1466805.1</v>
       </c>
       <c r="C13" s="14" t="n">
         <f aca="false">용접!$G$26</f>
-        <v>1170735.9</v>
+        <v>1180735.9</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">베이스!$G$18</f>
@@ -3428,24 +3445,24 @@
       </c>
       <c r="E13" s="31" t="n">
         <f aca="false">SUM(B13:D13)</f>
-        <v>2194718.6</v>
+        <v>2647541</v>
       </c>
       <c r="F13" s="32" t="n">
         <f aca="false">E13/$E$16</f>
-        <v>0.0397212567643386</v>
+        <v>0.0400003172780564</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B14" s="14" t="n">
-        <f aca="false">도비!$G$30</f>
-        <v>3018545.505</v>
+        <f aca="false">도비!$G$29</f>
+        <v>4413436.065</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">용접!$G$27</f>
-        <v>3135818.085</v>
+        <v>3167318.085</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">베이스!$G$19</f>
@@ -3453,24 +3470,24 @@
       </c>
       <c r="E14" s="31" t="n">
         <f aca="false">SUM(B14:D14)</f>
-        <v>6154363.59</v>
+        <v>7580754.15</v>
       </c>
       <c r="F14" s="32" t="n">
         <f aca="false">E14/$E$16</f>
-        <v>0.111385148136753</v>
+        <v>0.114533663957213</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B15" s="14" t="n">
-        <f aca="false">도비!$G$31</f>
-        <v>-182.204999998212</v>
+        <f aca="false">도비!$G$30</f>
+        <v>-343.164999999106</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">용접!$G$28</f>
-        <v>-271.984999999404</v>
+        <v>-771.984999999404</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">베이스!$G$20</f>
@@ -3478,24 +3495,24 @@
       </c>
       <c r="E15" s="31" t="n">
         <f aca="false">SUM(B15:D15)</f>
-        <v>-454.189999997616</v>
+        <v>-1115.14999999851</v>
       </c>
       <c r="F15" s="32" t="n">
         <f aca="false">E15/$E$16</f>
-        <v>-8.22018713911671E-006</v>
+        <v>-1.68482202211656E-005</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B16" s="19" t="n">
-        <f aca="false">도비!$G$32</f>
-        <v>24522000</v>
+        <f aca="false">도비!$G$31</f>
+        <v>35216000</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">용접!$G$29</f>
-        <v>27721000</v>
+        <v>27962000</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">베이스!$G$21</f>
@@ -3503,159 +3520,182 @@
       </c>
       <c r="E16" s="19" t="n">
         <f aca="false">SUM(B16:D16)</f>
-        <v>55253000</v>
+        <v>66188000</v>
       </c>
       <c r="F16" s="33" t="n">
         <f aca="false">E16/$E$16</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14" t="n">
-        <f aca="false">E16*0.1</f>
-        <v>5525300</v>
-      </c>
-      <c r="F17" s="14"/>
+        <v>-2551636</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35" t="n">
+      <c r="A18" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19" t="n">
         <f aca="false">E16+E17</f>
-        <v>60778300</v>
-      </c>
-      <c r="F18" s="35"/>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
+        <v>63636364</v>
+      </c>
+      <c r="F18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>155</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14" t="n">
+        <f aca="false">ROUND(E18*0.1,0)</f>
+        <v>6363636</v>
+      </c>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="35" t="s">
+        <v>156</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
       <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+      <c r="E20" s="36" t="n">
+        <f aca="false">E18+E19</f>
+        <v>70000000</v>
+      </c>
       <c r="F20" s="36"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="B25" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="B24" s="13" t="s">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="38" t="n">
-        <v>0.0356</v>
-      </c>
-      <c r="E24" s="39" t="s">
+      <c r="E25" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F24" s="39"/>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="38" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="F25" s="39"/>
+      <c r="F25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
         <v>148</v>
       </c>
       <c r="B26" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="39" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="E26" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="38" t="n">
-        <v>0.0311</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="F26" s="39"/>
+      <c r="F26" s="40"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C27" s="13"/>
-      <c r="D27" s="38" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="F27" s="39"/>
+      <c r="D27" s="39" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B28" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="39" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="F28" s="40"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="38" t="n">
+      <c r="C29" s="13"/>
+      <c r="D29" s="39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E29" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" s="40"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="39" t="n">
         <v>0.15</v>
       </c>
-      <c r="E28" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="F28" s="39"/>
+      <c r="E30" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="B26:C26"/>
@@ -3664,6 +3704,10 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="E30:F30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.629861111111111" right="0.629861111111111" top="0.709722222222222" bottom="0.709722222222222" header="0.511811023622047" footer="0.35"/>
@@ -3680,7 +3724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -3692,18 +3736,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
-        <v>170</v>
+      <c r="A1" s="41" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
-        <v>171</v>
+      <c r="A2" s="42" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>30</v>
@@ -3712,18 +3756,18 @@
         <v>31</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>38</v>
@@ -3732,19 +3776,19 @@
         <v>39</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E5" s="42" t="n">
+        <v>177</v>
+      </c>
+      <c r="E5" s="43" t="n">
         <f aca="false">도비!G8</f>
-        <v>4500000</v>
+        <v>6300000</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>41</v>
@@ -3753,19 +3797,19 @@
         <v>42</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E6" s="42" t="n">
+        <v>179</v>
+      </c>
+      <c r="E6" s="43" t="n">
         <f aca="false">도비!G9</f>
-        <v>520000</v>
+        <v>1040000</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>44</v>
@@ -3774,19 +3818,19 @@
         <v>45</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" s="42" t="n">
+        <v>181</v>
+      </c>
+      <c r="E7" s="43" t="n">
         <f aca="false">도비!G10</f>
-        <v>960000</v>
+        <v>1280000</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>47</v>
@@ -3795,588 +3839,567 @@
         <v>48</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="42" t="n">
+        <v>182</v>
+      </c>
+      <c r="E8" s="43" t="n">
         <f aca="false">도비!G11</f>
-        <v>2400000</v>
+        <v>10000000</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="42" t="n">
+        <v>184</v>
+      </c>
+      <c r="E9" s="43" t="n">
         <f aca="false">도비!G12</f>
-        <v>1700000</v>
+        <v>640000</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="E10" s="42" t="n">
+        <v>186</v>
+      </c>
+      <c r="E10" s="43" t="n">
         <f aca="false">도비!G13</f>
-        <v>640000</v>
+        <v>2000000</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="E11" s="42" t="n">
+        <v>187</v>
+      </c>
+      <c r="E11" s="43" t="n">
         <f aca="false">도비!G14</f>
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E12" s="42" t="n">
+        <v>187</v>
+      </c>
+      <c r="E12" s="43" t="n">
         <f aca="false">도비!G15</f>
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E13" s="42" t="n">
+        <v>190</v>
+      </c>
+      <c r="E13" s="43" t="n">
         <f aca="false">도비!G16</f>
-        <v>1000000</v>
+        <v>1320000</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" s="42" t="n">
+        <v>192</v>
+      </c>
+      <c r="E14" s="43" t="n">
         <f aca="false">도비!G17</f>
-        <v>1210000</v>
+        <v>500000</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E15" s="42" t="n">
+        <v>194</v>
+      </c>
+      <c r="E15" s="43" t="n">
         <f aca="false">도비!G18</f>
-        <v>500000</v>
+        <v>520000</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>68</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C16" s="13"/>
       <c r="D16" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E16" s="42" t="n">
+        <v>187</v>
+      </c>
+      <c r="E16" s="43" t="n">
         <f aca="false">도비!G19</f>
-        <v>520000</v>
+        <v>380000</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="13"/>
+      <c r="C17" s="13" t="s">
+        <v>71</v>
+      </c>
       <c r="D17" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E17" s="42" t="n">
+        <v>197</v>
+      </c>
+      <c r="E17" s="43" t="n">
         <f aca="false">도비!G20</f>
-        <v>380000</v>
+        <v>600000</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20"/>
+      <c r="B18" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="E18" s="42" t="n">
-        <f aca="false">도비!G21</f>
-        <v>600000</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="45" t="n">
+        <f aca="false">도비!$G$31-SUM(도비!$G$21:$G$23)</f>
+        <v>6636000</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20"/>
-      <c r="B19" s="43" t="s">
-        <v>73</v>
+      <c r="B19" s="44" t="s">
+        <v>119</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="44" t="n">
-        <f aca="false">도비!$G$32-SUM(도비!$G$22:$G$24)</f>
-        <v>4592000</v>
+      <c r="E19" s="45" t="n">
+        <f aca="false">도비!$G$31</f>
+        <v>35216000</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20"/>
-      <c r="B20" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="44" t="n">
-        <f aca="false">도비!$G$32</f>
-        <v>24522000</v>
-      </c>
-      <c r="F20" s="20" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E21" s="43" t="n">
+        <f aca="false">용접!G8</f>
+        <v>4500000</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E22" s="42" t="n">
-        <f aca="false">용접!G8</f>
-        <v>4500000</v>
+        <v>202</v>
+      </c>
+      <c r="E22" s="43" t="n">
+        <f aca="false">용접!G9</f>
+        <v>2100000</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E23" s="42" t="n">
-        <f aca="false">용접!G9</f>
-        <v>2100000</v>
+        <v>203</v>
+      </c>
+      <c r="E23" s="43" t="n">
+        <f aca="false">용접!G10</f>
+        <v>1200000</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="E24" s="42" t="n">
-        <f aca="false">용접!G10</f>
-        <v>1200000</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="E25" s="42" t="n">
+      <c r="E24" s="43" t="n">
         <f aca="false">용접!G11</f>
         <v>800000</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="13" t="s">
+      <c r="F24" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="D25" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="42" t="n">
+      <c r="E25" s="43" t="n">
         <f aca="false">용접!G12</f>
         <v>1250000</v>
       </c>
+      <c r="F25" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E26" s="43" t="n">
+        <f aca="false">용접!G13</f>
+        <v>3600000</v>
+      </c>
       <c r="F26" s="13" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="E27" s="42" t="n">
-        <f aca="false">용접!G13</f>
-        <v>3600000</v>
+        <v>187</v>
+      </c>
+      <c r="E27" s="43" t="n">
+        <f aca="false">용접!G14</f>
+        <v>800000</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E28" s="42" t="n">
-        <f aca="false">용접!G14</f>
-        <v>800000</v>
+        <v>208</v>
+      </c>
+      <c r="E28" s="43" t="n">
+        <f aca="false">용접!G15</f>
+        <v>3680000</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="13" t="s">
         <v>100</v>
       </c>
+      <c r="C29" s="13"/>
       <c r="D29" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="E29" s="42" t="n">
-        <f aca="false">용접!G15</f>
-        <v>3680000</v>
+        <v>187</v>
+      </c>
+      <c r="E29" s="43" t="n">
+        <f aca="false">용접!G16</f>
+        <v>1000000</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="13"/>
+      <c r="C30" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="D30" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E30" s="42" t="n">
-        <f aca="false">용접!G16</f>
-        <v>1000000</v>
+        <v>209</v>
+      </c>
+      <c r="E30" s="43" t="n">
+        <f aca="false">용접!G17</f>
+        <v>2400000</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E31" s="42" t="n">
-        <f aca="false">용접!G17</f>
-        <v>2200000</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="E32" s="42" t="n">
+      <c r="E31" s="43" t="n">
         <f aca="false">용접!G18</f>
         <v>1400000</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F31" s="13" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20"/>
+      <c r="B32" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="45" t="n">
+        <f aca="false">용접!$G$29-SUM(용접!$G$19:$G$21)</f>
+        <v>5232000</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20"/>
-      <c r="B33" s="43" t="s">
-        <v>73</v>
+      <c r="B33" s="44" t="s">
+        <v>119</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="20"/>
-      <c r="E33" s="44" t="n">
-        <f aca="false">용접!$G$29-SUM(용접!$G$19:$G$21)</f>
-        <v>5191000</v>
+      <c r="E33" s="45" t="n">
+        <f aca="false">용접!$G$29</f>
+        <v>27962000</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20"/>
-      <c r="B34" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="44" t="n">
-        <f aca="false">용접!$G$29</f>
-        <v>27721000</v>
-      </c>
-      <c r="F34" s="20" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B36" s="13" t="s">
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="13" t="s">
+      <c r="D35" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="E36" s="42" t="n">
+      <c r="E35" s="43" t="n">
         <f aca="false">베이스!G8</f>
         <v>1800000</v>
       </c>
+      <c r="F35" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E36" s="43" t="n">
+        <f aca="false">베이스!G9</f>
+        <v>160000</v>
+      </c>
       <c r="F36" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E37" s="42" t="n">
-        <f aca="false">베이스!G9</f>
-        <v>160000</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="E38" s="42" t="n">
+      <c r="E37" s="43" t="n">
         <f aca="false">베이스!G10</f>
         <v>1050000</v>
       </c>
-      <c r="F38" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20"/>
-      <c r="B39" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="44" t="n">
+      <c r="F37" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20"/>
+      <c r="B38" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="45" t="n">
         <f aca="false">베이스!$G$21</f>
         <v>3010000</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F38" s="20" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4396,7 +4419,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -4448,17 +4471,17 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="46" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
@@ -4486,12 +4509,12 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>38</v>
@@ -4503,20 +4526,20 @@
         <v>220</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>300000</v>
       </c>
       <c r="G8" s="14" t="n">
         <f aca="false">E8*F8</f>
-        <v>4500000</v>
+        <v>6300000</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>40</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4531,20 +4554,20 @@
         <v>220</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>260000</v>
       </c>
       <c r="G9" s="14" t="n">
         <f aca="false">E9*F9</f>
-        <v>520000</v>
+        <v>1040000</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>43</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4559,20 +4582,20 @@
         <v>220</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>320000</v>
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">E10*F10</f>
-        <v>960000</v>
+        <v>1280000</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4589,85 +4612,85 @@
         <v>222</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2400000</v>
+        <v>5000000</v>
       </c>
       <c r="G11" s="14" t="n">
         <f aca="false">E11*F11</f>
-        <v>2400000</v>
+        <v>10000000</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>49</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>222</v>
+        <v>74</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1700000</v>
+        <v>640000</v>
       </c>
       <c r="G12" s="14" t="n">
         <f aca="false">E12*F12</f>
-        <v>1700000</v>
+        <v>640000</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11"/>
       <c r="B13" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>640000</v>
+        <v>2000000</v>
       </c>
       <c r="G13" s="14" t="n">
         <f aca="false">E13*F13</f>
-        <v>640000</v>
+        <v>2000000</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>223</v>
@@ -4676,426 +4699,398 @@
         <v>1</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="G14" s="14" t="n">
         <f aca="false">E14*F14</f>
-        <v>2000000</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>56</v>
-      </c>
+        <v>3000000</v>
+      </c>
+      <c r="H14" s="13"/>
       <c r="I14" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
+      <c r="A15" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="B15" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>223</v>
+        <v>74</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="G15" s="14" t="n">
         <f aca="false">E15*F15</f>
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="11" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>1000000</v>
+        <v>5000</v>
       </c>
       <c r="G16" s="14" t="n">
         <f aca="false">E16*F16</f>
-        <v>1000000</v>
-      </c>
-      <c r="H16" s="13"/>
+        <v>1320000</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>62</v>
+      </c>
       <c r="I16" s="11" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>224</v>
-      </c>
+      <c r="A17" s="11"/>
       <c r="B17" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>5000</v>
+        <v>250000</v>
       </c>
       <c r="G17" s="14" t="n">
         <f aca="false">E17*F17</f>
-        <v>1210000</v>
+        <v>500000</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>71</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11"/>
       <c r="B18" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>2</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>250000</v>
+        <v>260000</v>
       </c>
       <c r="G18" s="14" t="n">
         <f aca="false">E18*F18</f>
-        <v>500000</v>
+        <v>520000</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11"/>
       <c r="B19" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>68</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C19" s="13"/>
       <c r="D19" s="11" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>260000</v>
+        <v>380000</v>
       </c>
       <c r="G19" s="14" t="n">
         <f aca="false">E19*F19</f>
-        <v>520000</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>69</v>
-      </c>
+        <v>380000</v>
+      </c>
+      <c r="H19" s="13"/>
       <c r="I19" s="11" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11"/>
+      <c r="A20" s="11" t="s">
+        <v>70</v>
+      </c>
       <c r="B20" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="13"/>
+      <c r="C20" s="13" t="s">
+        <v>71</v>
+      </c>
       <c r="D20" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>380000</v>
+        <v>600000</v>
       </c>
       <c r="G20" s="14" t="n">
         <f aca="false">E20*F20</f>
-        <v>380000</v>
+        <v>600000</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="11" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <f aca="false">E21*F21</f>
-        <v>600000</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="11" t="s">
-        <v>71</v>
-      </c>
+      <c r="A21" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="48" t="n">
+        <f aca="false">SUMIF($I$8:$I$20,"재료비",$G$8:$G$20)</f>
+        <v>1380000</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47" t="n">
-        <f aca="false">SUMIF($I$8:$I$21,"재료비",$G$8:$G$21)</f>
-        <v>1380000</v>
+      <c r="A22" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="48" t="n">
+        <f aca="false">SUMIF($I$8:$I$20,"노무비",$G$8:$G$20)</f>
+        <v>9120000</v>
       </c>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="47" t="n">
-        <f aca="false">SUMIF($I$8:$I$21,"노무비",$G$8:$G$21)</f>
-        <v>6480000</v>
+      <c r="A23" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="48" t="n">
+        <f aca="false">SUMIF($I$8:$I$20,"경비",$G$8:$G$20)</f>
+        <v>18080000</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="46" t="s">
-        <v>229</v>
-      </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47" t="n">
-        <f aca="false">SUMIF($I$8:$I$21,"경비",$G$8:$G$21)</f>
-        <v>12070000</v>
-      </c>
-      <c r="H24" s="20"/>
+      <c r="A24" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="48" t="n">
+        <f aca="false">G22*원가계산서!$D$26</f>
+        <v>324672</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>230</v>
+      </c>
       <c r="I24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="47" t="n">
-        <f aca="false">G23*원가계산서!$D$24</f>
-        <v>230688</v>
+      <c r="A25" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="48" t="n">
+        <f aca="false">G22*원가계산서!$D$27</f>
+        <v>104880</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47" t="n">
-        <f aca="false">G23*원가계산서!$D$25</f>
-        <v>74520</v>
+      <c r="A26" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48" t="n">
+        <f aca="false">(G21+G22)*원가계산서!$D$28</f>
+        <v>326550</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="47" t="n">
-        <f aca="false">(G22+G23)*원가계산서!$D$26</f>
-        <v>244446</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>232</v>
-      </c>
+      <c r="A27" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19" t="n">
+        <f aca="false">SUM(G21:G26)</f>
+        <v>29336102</v>
+      </c>
+      <c r="H27" s="20"/>
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="19" t="n">
-        <f aca="false">SUM(G22:G27)</f>
-        <v>20479654</v>
-      </c>
-      <c r="H28" s="20"/>
+      <c r="A28" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="48" t="n">
+        <f aca="false">G27*원가계산서!$D$29</f>
+        <v>1466805.1</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>233</v>
+      </c>
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="47" t="n">
-        <f aca="false">G28*원가계산서!$D$27</f>
-        <v>1023982.7</v>
+      <c r="A29" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="48" t="n">
+        <f aca="false">(G22+G23+G24+G25+G26+G28)*원가계산서!$D$30</f>
+        <v>4413436.065</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="47" t="n">
-        <f aca="false">(G23+G24+G25+G26+G27+G29)*원가계산서!$D$28</f>
-        <v>3018545.505</v>
+      <c r="A30" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="48" t="n">
+        <f aca="false">-MOD(G27+G28+G29,1000)</f>
+        <v>-343.164999999106</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="46" t="s">
-        <v>152</v>
-      </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="47" t="n">
-        <f aca="false">-MOD(G28+G29+G30,1000)</f>
-        <v>-182.204999998212</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="I31" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49" t="n">
-        <f aca="false">G28+G29+G30+G31</f>
-        <v>24522000</v>
-      </c>
-      <c r="H32" s="50" t="s">
+      <c r="A31" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="50" t="n">
+        <f aca="false">G27+G28+G29+G30</f>
+        <v>35216000</v>
+      </c>
+      <c r="H31" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="I32" s="50"/>
+      <c r="I31" s="51"/>
+    </row>
+    <row r="33" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
     </row>
     <row r="34" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-    </row>
-    <row r="35" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="51" t="s">
+      <c r="A34" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -5103,8 +5098,10 @@
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="H21:I21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="H22:I22"/>
     <mergeCell ref="A23:F23"/>
@@ -5125,10 +5122,8 @@
     <mergeCell ref="H30:I30"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="H31:I31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A35:I35"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.629861111111111" right="0.629861111111111" top="0.709722222222222" bottom="0.709722222222222" header="0.511811023622047" footer="0.35"/>
@@ -5197,17 +5192,17 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="46" t="s">
         <v>238</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
@@ -5235,18 +5230,18 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>220</v>
@@ -5262,19 +5257,19 @@
         <v>4500000</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11"/>
       <c r="B9" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>83</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>84</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>220</v>
@@ -5290,19 +5285,19 @@
         <v>2100000</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11"/>
       <c r="B10" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>87</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>220</v>
@@ -5318,19 +5313,19 @@
         <v>1200000</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>89</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>220</v>
@@ -5346,19 +5341,19 @@
         <v>800000</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>92</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>220</v>
@@ -5374,10 +5369,10 @@
         <v>1250000</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5385,10 +5380,10 @@
         <v>221</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>94</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>222</v>
@@ -5404,19 +5399,19 @@
         <v>3600000</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11"/>
       <c r="B14" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>98</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>223</v>
@@ -5433,21 +5428,21 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>100</v>
-      </c>
       <c r="D15" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>1</v>
@@ -5461,7 +5456,7 @@
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5469,11 +5464,11 @@
         <v>221</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>1</v>
@@ -5487,49 +5482,49 @@
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11"/>
       <c r="B17" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>102</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>103</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>222</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F17" s="14" t="n">
         <v>100000</v>
       </c>
       <c r="G17" s="14" t="n">
         <f aca="false">E17*F17</f>
-        <v>2200000</v>
+        <v>2400000</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>1</v>
@@ -5542,22 +5537,22 @@
         <v>1400000</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="47" t="n">
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="48" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"재료비",$G$8:$G$18)</f>
         <v>3680000</v>
       </c>
@@ -5565,15 +5560,15 @@
       <c r="I19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47" t="n">
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="48" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"노무비",$G$8:$G$18)</f>
         <v>9850000</v>
       </c>
@@ -5581,32 +5576,32 @@
       <c r="I20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="47" t="n">
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="48" t="n">
         <f aca="false">SUMIF($I$8:$I$18,"경비",$G$8:$G$18)</f>
-        <v>9000000</v>
+        <v>9200000</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47" t="n">
-        <f aca="false">G20*원가계산서!$D$24</f>
+      <c r="A22" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="48" t="n">
+        <f aca="false">G20*원가계산서!$D$26</f>
         <v>350660</v>
       </c>
       <c r="H22" s="20" t="s">
@@ -5615,16 +5610,16 @@
       <c r="I22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="47" t="n">
-        <f aca="false">G20*원가계산서!$D$25</f>
+      <c r="A23" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="48" t="n">
+        <f aca="false">G20*원가계산서!$D$27</f>
         <v>113275</v>
       </c>
       <c r="H23" s="20" t="s">
@@ -5633,16 +5628,16 @@
       <c r="I23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47" t="n">
-        <f aca="false">(G19+G20)*원가계산서!$D$26</f>
+      <c r="A24" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="48" t="n">
+        <f aca="false">(G19+G20)*원가계산서!$D$28</f>
         <v>420783</v>
       </c>
       <c r="H24" s="20" t="s">
@@ -5652,7 +5647,7 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -5661,23 +5656,23 @@
       <c r="F25" s="18"/>
       <c r="G25" s="19" t="n">
         <f aca="false">SUM(G19:G24)</f>
-        <v>23414718</v>
+        <v>23614718</v>
       </c>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47" t="n">
-        <f aca="false">G25*원가계산서!$D$27</f>
-        <v>1170735.9</v>
+      <c r="A26" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48" t="n">
+        <f aca="false">G25*원가계산서!$D$29</f>
+        <v>1180735.9</v>
       </c>
       <c r="H26" s="20" t="s">
         <v>233</v>
@@ -5685,17 +5680,17 @@
       <c r="I26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="47" t="n">
-        <f aca="false">(G20+G21+G22+G23+G24+G26)*원가계산서!$D$28</f>
-        <v>3135818.085</v>
+      <c r="A27" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="48" t="n">
+        <f aca="false">(G20+G21+G22+G23+G24+G26)*원가계산서!$D$30</f>
+        <v>3167318.085</v>
       </c>
       <c r="H27" s="20" t="s">
         <v>234</v>
@@ -5703,17 +5698,17 @@
       <c r="I27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="46" t="s">
-        <v>152</v>
-      </c>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="47" t="n">
+      <c r="A28" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="48" t="n">
         <f aca="false">-MOD(G25+G26+G27,1000)</f>
-        <v>-271.984999999404</v>
+        <v>-771.984999999404</v>
       </c>
       <c r="H28" s="20" t="s">
         <v>235</v>
@@ -5721,48 +5716,48 @@
       <c r="I28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="B29" s="48"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="49" t="n">
+      <c r="A29" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="50" t="n">
         <f aca="false">G25+G26+G27+G28</f>
-        <v>27721000</v>
-      </c>
-      <c r="H29" s="50" t="s">
+        <v>27962000</v>
+      </c>
+      <c r="H29" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="I29" s="50"/>
+      <c r="I29" s="51"/>
     </row>
     <row r="31" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
     </row>
     <row r="32" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="51"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -5864,17 +5859,17 @@
       <c r="I3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="46" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
@@ -5902,21 +5897,21 @@
         <v>36</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>111</v>
-      </c>
       <c r="D8" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>1</v>
@@ -5929,10 +5924,10 @@
         <v>1800000</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5940,13 +5935,13 @@
         <v>240</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>114</v>
-      </c>
       <c r="D9" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>1</v>
@@ -5960,18 +5955,18 @@
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>115</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>116</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>220</v>
@@ -5987,22 +5982,22 @@
         <v>1050000</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="47" t="n">
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48" t="n">
         <f aca="false">SUMIF($I$8:$I$10,"재료비",$G$8:$G$10)</f>
         <v>1800000</v>
       </c>
@@ -6010,15 +6005,15 @@
       <c r="I11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47" t="n">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48" t="n">
         <f aca="false">SUMIF($I$8:$I$10,"노무비",$G$8:$G$10)</f>
         <v>1050000</v>
       </c>
@@ -6026,15 +6021,15 @@
       <c r="I12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="47" t="n">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="48" t="n">
         <f aca="false">SUMIF($I$8:$I$10,"경비",$G$8:$G$10)</f>
         <v>160000</v>
       </c>
@@ -6042,15 +6037,15 @@
       <c r="I13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47" t="n">
+      <c r="A14" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
@@ -6060,15 +6055,15 @@
       <c r="I14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="47" t="n">
+      <c r="A15" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
@@ -6078,15 +6073,15 @@
       <c r="I15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="47" t="n">
+      <c r="A16" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="48" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
@@ -6097,7 +6092,7 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -6112,15 +6107,15 @@
       <c r="I17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="47" t="n">
+      <c r="A18" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="48" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
@@ -6130,15 +6125,15 @@
       <c r="I18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="47" t="n">
+      <c r="A19" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="48" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
@@ -6148,15 +6143,15 @@
       <c r="I19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="46" t="s">
-        <v>152</v>
-      </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47" t="n">
+      <c r="A20" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="48" t="n">
         <f aca="false">-MOD(G17+G18+G19,1000)</f>
         <v>-0</v>
       </c>
@@ -6166,48 +6161,48 @@
       <c r="I20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49" t="n">
+      <c r="A21" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="50" t="n">
         <f aca="false">G17+G18+G19+G20</f>
         <v>3010000</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="I21" s="50"/>
+      <c r="I21" s="51"/>
     </row>
     <row r="23" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
     </row>
     <row r="24" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -6263,7 +6258,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>242</v>
       </c>
     </row>
@@ -6285,75 +6280,56 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="52" t="n">
+      <c r="A4" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="B4" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="53" t="n">
+      <c r="B4" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="54" t="n">
         <f aca="false">A4*B4</f>
-        <v>40</v>
-      </c>
-      <c r="D4" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="53" t="n">
         <v>72.4</v>
       </c>
-      <c r="E4" s="54" t="n">
+      <c r="E4" s="55" t="n">
         <f aca="false">C4*D4</f>
-        <v>2896</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="52" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="52" t="n">
-        <v>16</v>
-      </c>
-      <c r="C5" s="53" t="n">
+      <c r="A5" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="54" t="n">
         <f aca="false">A5*B5</f>
-        <v>80</v>
-      </c>
-      <c r="D5" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="53" t="n">
         <v>72.4</v>
       </c>
-      <c r="E5" s="54" t="n">
+      <c r="E5" s="55" t="n">
         <f aca="false">C5*D5</f>
-        <v>5792</v>
+        <v>434.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B6" s="52" t="n">
-        <v>30</v>
-      </c>
-      <c r="C6" s="53" t="n">
-        <f aca="false">A6*B6</f>
-        <v>18</v>
-      </c>
-      <c r="D6" s="52" t="n">
-        <v>72.4</v>
-      </c>
-      <c r="E6" s="54" t="n">
-        <f aca="false">C6*D6</f>
-        <v>1303.2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="55"/>
-      <c r="B7" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="55" t="n">
-        <f aca="false">SUM(C4:C6)</f>
-        <v>138</v>
-      </c>
-      <c r="D7" s="55"/>
-      <c r="E7" s="57" t="n">
-        <f aca="false">SUM(E4:E6)</f>
-        <v>9991.2</v>
+      <c r="A6" s="56"/>
+      <c r="B6" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="56" t="n">
+        <f aca="false">SUM(C4:C5)</f>
+        <v>26</v>
+      </c>
+      <c r="D6" s="56"/>
+      <c r="E6" s="58" t="n">
+        <f aca="false">SUM(E4:E5)</f>
+        <v>1882.4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6367,7 +6343,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>36</v>
@@ -6375,14 +6351,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="58" t="n">
-        <f aca="false">E7</f>
-        <v>9991.2</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>186</v>
+        <v>109</v>
+      </c>
+      <c r="B10" s="59" t="n">
+        <f aca="false">E6</f>
+        <v>1882.4</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="D10" s="14" t="n">
         <f aca="false">베이스!G8</f>
@@ -6393,7 +6369,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="42" t="s">
         <v>249</v>
       </c>
     </row>
@@ -6413,16 +6389,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="0" width="5.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="5.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>250</v>
       </c>
     </row>
@@ -6433,176 +6409,206 @@
       <c r="B3" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="61" t="s">
         <v>253</v>
       </c>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="61" t="s">
         <v>254</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="61" t="s">
         <v>255</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="61" t="s">
         <v>256</v>
       </c>
-      <c r="G3" s="60" t="s">
+      <c r="G3" s="61" t="s">
         <v>257</v>
       </c>
-      <c r="H3" s="60" t="s">
+      <c r="H3" s="61" t="s">
         <v>258</v>
       </c>
-      <c r="I3" s="60" t="s">
+      <c r="I3" s="61" t="s">
         <v>259</v>
       </c>
-      <c r="J3" s="60" t="s">
+      <c r="J3" s="61" t="s">
         <v>260</v>
       </c>
-      <c r="K3" s="60" t="s">
+      <c r="K3" s="61" t="s">
         <v>261</v>
       </c>
-      <c r="L3" s="60" t="s">
+      <c r="L3" s="61" t="s">
         <v>262</v>
       </c>
-      <c r="M3" s="60" t="s">
+      <c r="M3" s="61" t="s">
         <v>263</v>
       </c>
+      <c r="N3" s="61" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="52" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="52" t="s">
+      <c r="A4" s="53" t="s">
         <v>265</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
+      <c r="B4" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="62"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="52" t="s">
+      <c r="A5" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="53" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="53" t="s">
+        <v>271</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="54"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="53" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="62"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="53" t="s">
         <v>266</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="52" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="52" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="52" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="52" t="s">
-        <v>273</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>274</v>
-      </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="61"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="B10" s="52" t="s">
-        <v>265</v>
-      </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="61"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="s">
-        <v>276</v>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="62"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="42" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
